--- a/utilities/Analisis_pestel_Mabel.xlsx
+++ b/utilities/Analisis_pestel_Mabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88776539-4450-41F6-B4CC-EFF3FF42BD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59802193-D0D9-40A5-ADF7-AF2929FCC772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRITERIOS" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="302">
   <si>
     <t>IMPACTO</t>
   </si>
@@ -687,12 +687,6 @@
     <t>MEDIO</t>
   </si>
   <si>
-    <t>O1</t>
-  </si>
-  <si>
-    <t>Reformas LOES: Ajustes en los mecanismos de ingreso y autonomía para que los Institutos Tecnológicos</t>
-  </si>
-  <si>
     <t>FACTOR</t>
   </si>
   <si>
@@ -711,9 +705,6 @@
     <t>Títulos Obtenidos por Mujeres 56.1%</t>
   </si>
   <si>
-    <t>Inserción Laboral Temprana 64% preferencia práctica</t>
-  </si>
-  <si>
     <t>Demanda en Ciberseguridad y Big Data 28.5%</t>
   </si>
   <si>
@@ -1000,17 +991,27 @@
   </si>
   <si>
     <t>https://www.proecuador.gob.ec/incentivos/</t>
+  </si>
+  <si>
+    <t>T11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1137,7 +1138,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1220,6 +1221,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF99FF"/>
         <bgColor rgb="FFE2CFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFDEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFC1"/>
+        <bgColor rgb="FFFBE4D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFFFC1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1437,9 +1456,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1450,35 +1469,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1487,7 +1501,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1500,23 +1514,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1526,194 +1539,78 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1724,17 +1621,169 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1744,6 +1793,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFC1"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
   </colors>
@@ -1973,938 +2023,938 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="108" t="s">
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="62" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="20" t="s">
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="20" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="108" t="s">
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="108" t="s">
+      <c r="E6" s="62" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="20" t="s">
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="20" t="s">
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="73"/>
-      <c r="C10" s="73"/>
-      <c r="D10" s="20" t="s">
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="108" t="s">
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="62" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="108" t="s">
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="108" t="s">
+      <c r="E12" s="62" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="20" t="s">
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="20" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="20" t="s">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="C16" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="22"/>
+      <c r="H16" s="19"/>
     </row>
     <row r="17" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="110" t="s">
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="64" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="21" t="s">
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="18" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="110" t="s">
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="110" t="s">
+      <c r="E19" s="64" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="110" t="s">
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="110" t="s">
+      <c r="E20" s="64" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="21" t="s">
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="21" t="s">
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="21" t="s">
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="21" t="s">
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="110" t="s">
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="110" t="s">
+      <c r="E25" s="64" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="21" t="s">
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="21" t="s">
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="73"/>
-      <c r="C28" s="73"/>
-      <c r="D28" s="21" t="s">
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="21" t="s">
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="21" t="s">
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="21" t="s">
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="18" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="21" t="s">
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="21" t="s">
+      <c r="B33" s="76"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="21" t="s">
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="21" t="s">
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
-      <c r="D36" s="21" t="s">
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="18" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="82" t="s">
+      <c r="B37" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="83" t="s">
+      <c r="C37" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="H37" s="22"/>
+      <c r="H37" s="19"/>
     </row>
     <row r="38" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="23" t="s">
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="23" t="s">
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E39" s="20" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="23" t="s">
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="20" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="23" t="s">
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E41" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="112" t="s">
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="112" t="s">
-        <v>230</v>
+      <c r="E42" s="66" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="23" t="s">
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E43" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="73"/>
-      <c r="C44" s="73"/>
-      <c r="D44" s="23" t="s">
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="20" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="73"/>
-      <c r="C45" s="73"/>
-      <c r="D45" s="23" t="s">
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="20" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="23" t="s">
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="20" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
-      <c r="D47" s="112" t="s">
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="E47" s="112" t="s">
+      <c r="E47" s="66" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="112" t="s">
+      <c r="B48" s="76"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="E48" s="112" t="s">
+      <c r="E48" s="66" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="73"/>
-      <c r="C49" s="73"/>
-      <c r="D49" s="23" t="s">
+      <c r="B49" s="76"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E49" s="23" t="s">
+      <c r="E49" s="20" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="73"/>
-      <c r="C50" s="73"/>
-      <c r="D50" s="23" t="s">
+      <c r="B50" s="76"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="20" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="73"/>
-      <c r="C51" s="73"/>
-      <c r="D51" s="23" t="s">
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="23" t="s">
+      <c r="E51" s="20" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
-      <c r="D52" s="23" t="s">
+      <c r="B52" s="76"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E52" s="23" t="s">
+      <c r="E52" s="20" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="73"/>
-      <c r="C53" s="73"/>
-      <c r="D53" s="23" t="s">
+      <c r="B53" s="76"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="23" t="s">
+      <c r="E53" s="20" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="23" t="s">
+      <c r="B54" s="76"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E54" s="20" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="73"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="23" t="s">
+      <c r="B55" s="76"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="73"/>
-      <c r="C56" s="73"/>
-      <c r="D56" s="23" t="s">
+      <c r="B56" s="76"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E56" s="23" t="s">
+      <c r="E56" s="20" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="112" t="s">
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="E57" s="112" t="s">
+      <c r="E57" s="66" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="73"/>
-      <c r="C58" s="73"/>
-      <c r="D58" s="23" t="s">
+      <c r="B58" s="76"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="E58" s="20" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="59" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="73"/>
-      <c r="C59" s="73"/>
-      <c r="D59" s="23" t="s">
+      <c r="B59" s="76"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E59" s="20" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="74"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="23" t="s">
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="E60" s="23" t="s">
+      <c r="E60" s="20" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="85" t="s">
+      <c r="C61" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="113" t="s">
+      <c r="D61" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="113" t="s">
+      <c r="E61" s="67" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="73"/>
-      <c r="C62" s="73"/>
-      <c r="D62" s="24" t="s">
+      <c r="B62" s="76"/>
+      <c r="C62" s="76"/>
+      <c r="D62" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="73"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="113" t="s">
+      <c r="B63" s="76"/>
+      <c r="C63" s="76"/>
+      <c r="D63" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="113" t="s">
+      <c r="E63" s="67" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="113" t="s">
+      <c r="B64" s="76"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="113" t="s">
+      <c r="E64" s="67" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="73"/>
-      <c r="C65" s="73"/>
-      <c r="D65" s="24" t="s">
+      <c r="B65" s="76"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="21" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="73"/>
-      <c r="C66" s="73"/>
-      <c r="D66" s="24" t="s">
+      <c r="B66" s="76"/>
+      <c r="C66" s="76"/>
+      <c r="D66" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="21" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="24" t="s">
+      <c r="B67" s="76"/>
+      <c r="C67" s="76"/>
+      <c r="D67" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="21" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="73"/>
-      <c r="C68" s="73"/>
-      <c r="D68" s="24" t="s">
+      <c r="B68" s="76"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="21" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="24" t="s">
+      <c r="B69" s="76"/>
+      <c r="C69" s="76"/>
+      <c r="D69" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="73"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="24" t="s">
+      <c r="B70" s="76"/>
+      <c r="C70" s="76"/>
+      <c r="D70" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="113" t="s">
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="E71" s="113" t="s">
+      <c r="E71" s="67" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="76" t="s">
+      <c r="B72" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="77" t="s">
+      <c r="C72" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="114" t="s">
+      <c r="D72" s="68" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="114" t="s">
+      <c r="E72" s="68" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="73"/>
-      <c r="C73" s="73"/>
-      <c r="D73" s="25" t="s">
+      <c r="B73" s="76"/>
+      <c r="C73" s="76"/>
+      <c r="D73" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E73" s="25" t="s">
+      <c r="E73" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="74" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="73"/>
-      <c r="C74" s="73"/>
-      <c r="D74" s="25" t="s">
+      <c r="B74" s="76"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="22" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="75" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="73"/>
-      <c r="C75" s="73"/>
-      <c r="D75" s="114" t="s">
+      <c r="B75" s="76"/>
+      <c r="C75" s="76"/>
+      <c r="D75" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="114" t="s">
+      <c r="E75" s="68" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="76" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="114" t="s">
+      <c r="B76" s="76"/>
+      <c r="C76" s="76"/>
+      <c r="D76" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="114" t="s">
+      <c r="E76" s="68" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="77" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="73"/>
-      <c r="C77" s="73"/>
-      <c r="D77" s="25" t="s">
+      <c r="B77" s="76"/>
+      <c r="C77" s="76"/>
+      <c r="D77" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="E77" s="25" t="s">
+      <c r="E77" s="22" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="78" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="73"/>
-      <c r="C78" s="73"/>
-      <c r="D78" s="25" t="s">
+      <c r="B78" s="76"/>
+      <c r="C78" s="76"/>
+      <c r="D78" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="25" t="s">
+      <c r="E78" s="68" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="73"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="25" t="s">
+      <c r="B79" s="76"/>
+      <c r="C79" s="76"/>
+      <c r="D79" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="E79" s="25" t="s">
+      <c r="E79" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="80" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="73"/>
-      <c r="C80" s="73"/>
-      <c r="D80" s="25" t="s">
+      <c r="B80" s="76"/>
+      <c r="C80" s="76"/>
+      <c r="D80" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="E80" s="25" t="s">
+      <c r="E80" s="22" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="25" t="s">
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E81" s="22" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="82" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="78" t="s">
+      <c r="B82" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="79" t="s">
+      <c r="C82" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="D82" s="26" t="s">
+      <c r="D82" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E82" s="26" t="s">
+      <c r="E82" s="23" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="83" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="73"/>
-      <c r="C83" s="73"/>
-      <c r="D83" s="26" t="s">
+      <c r="B83" s="76"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E83" s="26" t="s">
+      <c r="E83" s="23" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="84" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="73"/>
-      <c r="C84" s="73"/>
-      <c r="D84" s="26" t="s">
+      <c r="B84" s="76"/>
+      <c r="C84" s="76"/>
+      <c r="D84" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="E84" s="26" t="s">
+      <c r="E84" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="85" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="73"/>
-      <c r="C85" s="73"/>
-      <c r="D85" s="115" t="s">
+      <c r="B85" s="76"/>
+      <c r="C85" s="76"/>
+      <c r="D85" s="69" t="s">
         <v>182</v>
       </c>
-      <c r="E85" s="115" t="s">
+      <c r="E85" s="69" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="86" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="73"/>
-      <c r="C86" s="73"/>
-      <c r="D86" s="26" t="s">
+      <c r="B86" s="76"/>
+      <c r="C86" s="76"/>
+      <c r="D86" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="E86" s="26" t="s">
+      <c r="E86" s="23" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="87" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="73"/>
-      <c r="C87" s="73"/>
-      <c r="D87" s="26" t="s">
+      <c r="B87" s="76"/>
+      <c r="C87" s="76"/>
+      <c r="D87" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="26" t="s">
+      <c r="E87" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="88" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="73"/>
-      <c r="C88" s="73"/>
-      <c r="D88" s="115" t="s">
+      <c r="B88" s="76"/>
+      <c r="C88" s="76"/>
+      <c r="D88" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="E88" s="115" t="s">
+      <c r="E88" s="69" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="89" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="73"/>
-      <c r="C89" s="73"/>
-      <c r="D89" s="115" t="s">
+      <c r="B89" s="76"/>
+      <c r="C89" s="76"/>
+      <c r="D89" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="115" t="s">
+      <c r="E89" s="69" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="90" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="73"/>
-      <c r="C90" s="73"/>
-      <c r="D90" s="26" t="s">
+      <c r="B90" s="76"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="E90" s="26" t="s">
+      <c r="E90" s="23" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="91" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="74"/>
-      <c r="C91" s="74"/>
-      <c r="D91" s="26" t="s">
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="E91" s="26" t="s">
+      <c r="E91" s="69" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3817,486 +3867,490 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="63" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="109" t="s">
-        <v>203</v>
-      </c>
-      <c r="F1" s="69" t="s">
-        <v>228</v>
+      <c r="F1" s="59" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="70" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="90"/>
+      <c r="B3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="90"/>
+      <c r="B4" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="90"/>
+      <c r="B5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D5" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="71" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="91"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="60"/>
+    </row>
+    <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E7" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="71" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="90"/>
+      <c r="B8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="F2" s="116" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="87"/>
-      <c r="B3" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="D3" s="43" t="s">
+      <c r="D8" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="E3" s="45" t="s">
-        <v>233</v>
-      </c>
-      <c r="F3" s="116" t="s">
+      <c r="E8" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="90"/>
+      <c r="B9" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="71" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="91"/>
+      <c r="B10" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="74" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="87"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="D4" s="43" t="s">
+      <c r="F11" s="72" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="90"/>
+      <c r="B12" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="F4" s="116" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87"/>
-      <c r="B5" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="D5" s="28" t="s">
+      <c r="E12" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" s="71" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="90"/>
+      <c r="B13" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="E5" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="F5" s="117" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="70"/>
-    </row>
-    <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="E13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" s="71" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="90"/>
+      <c r="B14" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="91"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="25"/>
+      <c r="F15" s="60"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="90"/>
+      <c r="B17" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="90"/>
+      <c r="B18" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="F18" s="71" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="91"/>
+      <c r="B19" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="D7" s="28" t="s">
+      <c r="C20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="F7" s="117" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="87"/>
-      <c r="B8" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="111" t="s">
-        <v>238</v>
-      </c>
-      <c r="D8" s="28" t="s">
+      <c r="E20" t="s">
+        <v>255</v>
+      </c>
+      <c r="F20" s="72" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="90"/>
+      <c r="B21" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" s="72" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="90"/>
+      <c r="B22" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="90"/>
+      <c r="B23" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="F23" s="71" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="90"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="60"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" t="s">
+        <v>258</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8" s="118" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87"/>
-      <c r="B9" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="E25" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" s="72" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="90"/>
+      <c r="B26" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" t="s">
+        <v>261</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="90"/>
+      <c r="B27" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="F9" s="117" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="111" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="28" t="s">
+      <c r="E27" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="91"/>
+      <c r="B28" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D28" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="118" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="111" t="s">
-        <v>279</v>
-      </c>
-      <c r="D11" s="119" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="120" t="s">
-        <v>280</v>
-      </c>
-      <c r="F11" s="118" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87"/>
-      <c r="B12" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" s="117" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
-      <c r="B13" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="117" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87"/>
-      <c r="B14" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="70" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="28"/>
-      <c r="F15" s="70"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>249</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="F16" s="118" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87"/>
-      <c r="B17" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E17" t="s">
-        <v>252</v>
-      </c>
-      <c r="F17" s="117" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87"/>
-      <c r="B18" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="117" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="F19" s="117" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" t="s">
-        <v>257</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E20" t="s">
-        <v>258</v>
-      </c>
-      <c r="F20" s="118" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E21" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21" s="118" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="29"/>
-      <c r="C22" t="s">
-        <v>259</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" t="s">
-        <v>260</v>
-      </c>
-      <c r="F22" s="118" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29" t="s">
-        <v>295</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="F23" s="117" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="70"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
-        <v>261</v>
-      </c>
-      <c r="D25" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" t="s">
-        <v>262</v>
-      </c>
-      <c r="F25" s="118" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" t="s">
-        <v>264</v>
-      </c>
-      <c r="F26" s="118" t="s">
+      <c r="E28" s="26" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" t="s">
-        <v>265</v>
-      </c>
-      <c r="D27" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" t="s">
-        <v>266</v>
-      </c>
-      <c r="F27" s="118" t="s">
+      <c r="F28" s="71" t="s">
         <v>300</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
-      <c r="B28" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="F28" s="117" t="s">
-        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4355,17 +4409,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="95" t="s">
-        <v>229</v>
-      </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
+      <c r="B1" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F2" s="1" t="s">
@@ -4374,22 +4428,22 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="100" t="s">
+      <c r="H2" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="102" t="s">
+      <c r="I2" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="103" t="s">
+      <c r="J2" s="100" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="37" t="s">
+      <c r="C3" s="102"/>
+      <c r="D3" s="33" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -4401,657 +4455,640 @@
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="38" t="s">
-        <v>12</v>
+      <c r="D4" s="34" t="s">
+        <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" s="61">
+        <v>228</v>
+      </c>
+      <c r="F4" s="53">
         <v>3</v>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="41">
         <v>3</v>
       </c>
       <c r="H4" s="6">
         <f t="shared" ref="H4:H29" si="0">F4*G4</f>
         <v>9</v>
       </c>
-      <c r="I4" s="71" t="s">
+      <c r="I4" s="61" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="6"/>
     </row>
     <row r="5" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="62">
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="54">
         <v>2</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="42">
         <v>3</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I5" s="53" t="s">
+      <c r="I5" s="47" t="s">
         <v>14</v>
       </c>
       <c r="J5" s="8"/>
     </row>
     <row r="6" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="105"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="38" t="s">
-        <v>17</v>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="34" t="s">
+        <v>65</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="61">
+        <v>210</v>
+      </c>
+      <c r="F6" s="53">
         <v>3</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="42">
         <v>3</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" s="47" t="s">
         <v>14</v>
       </c>
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="62">
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="54">
         <v>3</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="42">
         <v>2</v>
       </c>
       <c r="H7" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="53" t="s">
+      <c r="I7" s="47" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="97" t="s">
+      <c r="C8" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="F8" s="48">
+      <c r="D8" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="43">
         <v>2</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="43">
         <v>3</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I8" s="54" t="s">
+      <c r="I8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="10"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="96"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" s="48">
+      <c r="B9" s="93"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="43">
         <v>3</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="43">
         <v>2</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="54" t="s">
+      <c r="I9" s="9"/>
+      <c r="J9" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="96"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="48">
+      <c r="B10" s="93"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="43">
         <v>3</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="43">
         <v>3</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="54" t="s">
+      <c r="I10" s="10"/>
+      <c r="J10" s="48" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="96"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="F11" s="48">
+      <c r="B11" s="93"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="43">
         <v>3</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="43">
         <v>2</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I11" s="54" t="s">
+      <c r="I11" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F12" s="63">
+      <c r="D12" s="111" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="112" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="113">
         <v>3</v>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="114">
         <v>3</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="115">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I12" s="54" t="s">
+      <c r="I12" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="10"/>
+      <c r="J12" s="115"/>
     </row>
     <row r="13" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="98"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="F13" s="49">
+      <c r="B13" s="95"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="44">
         <v>3</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="44">
         <v>2</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="55" t="s">
+      <c r="I13" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="13"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="98"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="F14" s="49">
+      <c r="B14" s="95"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14" s="44">
         <v>2</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="44">
         <v>3</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I14" s="55" t="s">
+      <c r="I14" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="J14" s="14"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="98"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="64">
+      <c r="B15" s="95"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" s="55">
         <v>3</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="44">
         <v>3</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="55" t="s">
+      <c r="I15" s="12"/>
+      <c r="J15" s="49" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="98"/>
-      <c r="C16" s="99"/>
-      <c r="D16" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="F16" s="64">
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="55">
         <v>3</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="44">
         <v>2</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I16" s="55" t="s">
+      <c r="I16" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="F17" s="64">
+      <c r="E17" s="118" t="s">
+        <v>217</v>
+      </c>
+      <c r="F17" s="119">
         <v>3</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="120">
         <v>2</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="121">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I17" s="55" t="s">
+      <c r="I17" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="121"/>
     </row>
     <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="93"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="F18" s="64">
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="132" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="118" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="119">
         <v>2</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="120">
         <v>2</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="121">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I18" s="55" t="s">
+      <c r="I18" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="14"/>
+      <c r="J18" s="123"/>
     </row>
     <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="93"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F19" s="64">
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="132" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="118" t="s">
+        <v>206</v>
+      </c>
+      <c r="F19" s="119">
         <v>3</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="120">
         <v>2</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="121">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I19" s="55" t="s">
+      <c r="I19" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="J19" s="13"/>
+      <c r="J19" s="121"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="93"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" s="64">
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="132" t="s">
+        <v>301</v>
+      </c>
+      <c r="E20" s="118" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="119">
         <v>1</v>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="120">
         <v>3</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="121">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="55" t="s">
+      <c r="I20" s="121"/>
+      <c r="J20" s="122" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="92" t="s">
+      <c r="C21" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="F21" s="50">
+      <c r="E21" s="125" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" s="126">
         <v>2</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="126">
         <v>2</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="127">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I21" s="56" t="s">
+      <c r="I21" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="J21" s="16"/>
+      <c r="J21" s="127"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="91"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F22" s="50">
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="125" t="s">
+        <v>221</v>
+      </c>
+      <c r="F22" s="126">
         <v>2</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="126">
         <v>2</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="127">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I22" s="57" t="s">
+      <c r="I22" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="J22" s="16"/>
+      <c r="J22" s="127"/>
     </row>
     <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F23" s="65">
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="133" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="F23" s="131">
         <v>3</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G23" s="126">
         <v>3</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="127">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I23" s="56" t="s">
+      <c r="I23" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="16"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="91"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="F24" s="65">
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="133" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="130" t="s">
+        <v>223</v>
+      </c>
+      <c r="F24" s="131">
         <v>2</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="126">
         <v>2</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="127">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I24" s="56" t="s">
+      <c r="I24" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="J24" s="16"/>
+      <c r="J24" s="127"/>
     </row>
     <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="F25" s="51">
+      <c r="D25" s="134" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="F25" s="45">
         <v>3</v>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="45">
         <v>3</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="14">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="58"/>
+      <c r="J25" s="50"/>
     </row>
     <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="89"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="F26" s="66">
+      <c r="B26" s="109"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="134" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="56">
         <v>3</v>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="45">
         <v>3</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="14">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I26" s="58" t="s">
+      <c r="I26" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="17"/>
+      <c r="J26" s="14"/>
     </row>
     <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="89"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="E27" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="F27" s="27">
+      <c r="B27" s="109"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="134" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="24">
         <v>3</v>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="45">
         <v>2</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I27" s="59" t="s">
+      <c r="I27" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="17"/>
+      <c r="J27" s="14"/>
     </row>
     <row r="28" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="89"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="E28" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="F28" s="67">
+      <c r="B28" s="109"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="134" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28" s="57">
         <v>3</v>
       </c>
-      <c r="G28" s="52">
+      <c r="G28" s="46">
         <v>2</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="15">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I28" s="60" t="s">
+      <c r="I28" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="18"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="89"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="F29" s="68">
-        <v>1</v>
-      </c>
-      <c r="G29" s="52">
-        <v>2</v>
-      </c>
-      <c r="H29" s="18">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="I29" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="19"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5130,938 +5167,938 @@
     <row r="104" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="72" t="s">
+      <c r="B106" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="75" t="s">
+      <c r="C106" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D106" s="20" t="s">
+      <c r="D106" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="20" t="s">
+      <c r="E106" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="73"/>
-      <c r="C107" s="73"/>
-      <c r="D107" s="20" t="s">
+      <c r="B107" s="76"/>
+      <c r="C107" s="76"/>
+      <c r="D107" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E107" s="20" t="s">
+      <c r="E107" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="108" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="73"/>
-      <c r="C108" s="73"/>
-      <c r="D108" s="20" t="s">
+      <c r="B108" s="76"/>
+      <c r="C108" s="76"/>
+      <c r="D108" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E108" s="20" t="s">
+      <c r="E108" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="109" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="73"/>
-      <c r="C109" s="73"/>
-      <c r="D109" s="20" t="s">
+      <c r="B109" s="76"/>
+      <c r="C109" s="76"/>
+      <c r="D109" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E109" s="20" t="s">
+      <c r="E109" s="17" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="110" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="73"/>
-      <c r="C110" s="73"/>
-      <c r="D110" s="20" t="s">
+      <c r="B110" s="76"/>
+      <c r="C110" s="76"/>
+      <c r="D110" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E110" s="20" t="s">
+      <c r="E110" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="111" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="73"/>
-      <c r="C111" s="73"/>
-      <c r="D111" s="20" t="s">
+      <c r="B111" s="76"/>
+      <c r="C111" s="76"/>
+      <c r="D111" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E111" s="20" t="s">
+      <c r="E111" s="17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="112" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="73"/>
-      <c r="C112" s="73"/>
-      <c r="D112" s="20" t="s">
+      <c r="B112" s="76"/>
+      <c r="C112" s="76"/>
+      <c r="D112" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E112" s="20" t="s">
+      <c r="E112" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="73"/>
-      <c r="C113" s="73"/>
-      <c r="D113" s="20" t="s">
+      <c r="B113" s="76"/>
+      <c r="C113" s="76"/>
+      <c r="D113" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E113" s="20" t="s">
+      <c r="E113" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="73"/>
-      <c r="C114" s="73"/>
-      <c r="D114" s="20" t="s">
+      <c r="B114" s="76"/>
+      <c r="C114" s="76"/>
+      <c r="D114" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E114" s="20" t="s">
+      <c r="E114" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="73"/>
-      <c r="C115" s="73"/>
-      <c r="D115" s="20" t="s">
+      <c r="B115" s="76"/>
+      <c r="C115" s="76"/>
+      <c r="D115" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E115" s="20" t="s">
+      <c r="E115" s="17" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="73"/>
-      <c r="C116" s="73"/>
-      <c r="D116" s="20" t="s">
+      <c r="B116" s="76"/>
+      <c r="C116" s="76"/>
+      <c r="D116" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E116" s="20" t="s">
+      <c r="E116" s="17" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="73"/>
-      <c r="C117" s="73"/>
-      <c r="D117" s="20" t="s">
+      <c r="B117" s="76"/>
+      <c r="C117" s="76"/>
+      <c r="D117" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E117" s="20" t="s">
+      <c r="E117" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="73"/>
-      <c r="C118" s="73"/>
-      <c r="D118" s="20" t="s">
+      <c r="B118" s="76"/>
+      <c r="C118" s="76"/>
+      <c r="D118" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E118" s="20" t="s">
+      <c r="E118" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="73"/>
-      <c r="C119" s="73"/>
-      <c r="D119" s="20" t="s">
+      <c r="B119" s="76"/>
+      <c r="C119" s="76"/>
+      <c r="D119" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E119" s="20" t="s">
+      <c r="E119" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="74"/>
-      <c r="C120" s="74"/>
-      <c r="D120" s="20" t="s">
+      <c r="B120" s="77"/>
+      <c r="C120" s="77"/>
+      <c r="D120" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E120" s="20" t="s">
+      <c r="E120" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="121" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="80" t="s">
+      <c r="B121" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="81" t="s">
+      <c r="C121" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="D121" s="21" t="s">
+      <c r="D121" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E121" s="21" t="s">
+      <c r="E121" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H121" s="22"/>
+      <c r="H121" s="19"/>
     </row>
     <row r="122" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="73"/>
-      <c r="C122" s="73"/>
-      <c r="D122" s="21" t="s">
+      <c r="B122" s="76"/>
+      <c r="C122" s="76"/>
+      <c r="D122" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E122" s="21" t="s">
+      <c r="E122" s="18" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="73"/>
-      <c r="C123" s="73"/>
-      <c r="D123" s="21" t="s">
+      <c r="B123" s="76"/>
+      <c r="C123" s="76"/>
+      <c r="D123" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E123" s="21" t="s">
+      <c r="E123" s="18" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="73"/>
-      <c r="C124" s="73"/>
-      <c r="D124" s="21" t="s">
+      <c r="B124" s="76"/>
+      <c r="C124" s="76"/>
+      <c r="D124" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E124" s="21" t="s">
+      <c r="E124" s="18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="73"/>
-      <c r="C125" s="73"/>
-      <c r="D125" s="21" t="s">
+      <c r="B125" s="76"/>
+      <c r="C125" s="76"/>
+      <c r="D125" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E125" s="21" t="s">
+      <c r="E125" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="73"/>
-      <c r="C126" s="73"/>
-      <c r="D126" s="21" t="s">
+      <c r="B126" s="76"/>
+      <c r="C126" s="76"/>
+      <c r="D126" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E126" s="21" t="s">
+      <c r="E126" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="73"/>
-      <c r="C127" s="73"/>
-      <c r="D127" s="21" t="s">
+      <c r="B127" s="76"/>
+      <c r="C127" s="76"/>
+      <c r="D127" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E127" s="21" t="s">
+      <c r="E127" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="73"/>
-      <c r="C128" s="73"/>
-      <c r="D128" s="21" t="s">
+      <c r="B128" s="76"/>
+      <c r="C128" s="76"/>
+      <c r="D128" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E128" s="21" t="s">
+      <c r="E128" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="73"/>
-      <c r="C129" s="73"/>
-      <c r="D129" s="21" t="s">
+      <c r="B129" s="76"/>
+      <c r="C129" s="76"/>
+      <c r="D129" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E129" s="21" t="s">
+      <c r="E129" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="73"/>
-      <c r="C130" s="73"/>
-      <c r="D130" s="21" t="s">
+      <c r="B130" s="76"/>
+      <c r="C130" s="76"/>
+      <c r="D130" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E130" s="21" t="s">
+      <c r="E130" s="18" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="131" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="73"/>
-      <c r="C131" s="73"/>
-      <c r="D131" s="21" t="s">
+      <c r="B131" s="76"/>
+      <c r="C131" s="76"/>
+      <c r="D131" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E131" s="21" t="s">
+      <c r="E131" s="18" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="132" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="73"/>
-      <c r="C132" s="73"/>
-      <c r="D132" s="21" t="s">
+      <c r="B132" s="76"/>
+      <c r="C132" s="76"/>
+      <c r="D132" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E132" s="21" t="s">
+      <c r="E132" s="18" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="133" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="73"/>
-      <c r="C133" s="73"/>
-      <c r="D133" s="21" t="s">
+      <c r="B133" s="76"/>
+      <c r="C133" s="76"/>
+      <c r="D133" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E133" s="21" t="s">
+      <c r="E133" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="134" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="73"/>
-      <c r="C134" s="73"/>
-      <c r="D134" s="21" t="s">
+      <c r="B134" s="76"/>
+      <c r="C134" s="76"/>
+      <c r="D134" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E134" s="21" t="s">
+      <c r="E134" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="135" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="73"/>
-      <c r="C135" s="73"/>
-      <c r="D135" s="21" t="s">
+      <c r="B135" s="76"/>
+      <c r="C135" s="76"/>
+      <c r="D135" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E135" s="21" t="s">
+      <c r="E135" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="136" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="73"/>
-      <c r="C136" s="73"/>
-      <c r="D136" s="21" t="s">
+      <c r="B136" s="76"/>
+      <c r="C136" s="76"/>
+      <c r="D136" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="21" t="s">
+      <c r="E136" s="18" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="137" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="73"/>
-      <c r="C137" s="73"/>
-      <c r="D137" s="21" t="s">
+      <c r="B137" s="76"/>
+      <c r="C137" s="76"/>
+      <c r="D137" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E137" s="21" t="s">
+      <c r="E137" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="138" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="73"/>
-      <c r="C138" s="73"/>
-      <c r="D138" s="21" t="s">
+      <c r="B138" s="76"/>
+      <c r="C138" s="76"/>
+      <c r="D138" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E138" s="21" t="s">
+      <c r="E138" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="139" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="73"/>
-      <c r="C139" s="73"/>
-      <c r="D139" s="21" t="s">
+      <c r="B139" s="76"/>
+      <c r="C139" s="76"/>
+      <c r="D139" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E139" s="21" t="s">
+      <c r="E139" s="18" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="140" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="73"/>
-      <c r="C140" s="73"/>
-      <c r="D140" s="21" t="s">
+      <c r="B140" s="76"/>
+      <c r="C140" s="76"/>
+      <c r="D140" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E140" s="21" t="s">
+      <c r="E140" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="141" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="74"/>
-      <c r="C141" s="74"/>
-      <c r="D141" s="21" t="s">
+      <c r="B141" s="77"/>
+      <c r="C141" s="77"/>
+      <c r="D141" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E141" s="21" t="s">
+      <c r="E141" s="18" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="142" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="82" t="s">
+      <c r="B142" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="C142" s="83" t="s">
+      <c r="C142" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="D142" s="23" t="s">
+      <c r="D142" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E142" s="23" t="s">
+      <c r="E142" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="H142" s="22"/>
+      <c r="H142" s="19"/>
     </row>
     <row r="143" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="73"/>
-      <c r="C143" s="73"/>
-      <c r="D143" s="23" t="s">
+      <c r="B143" s="76"/>
+      <c r="C143" s="76"/>
+      <c r="D143" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E143" s="23" t="s">
+      <c r="E143" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="144" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="73"/>
-      <c r="C144" s="73"/>
-      <c r="D144" s="23" t="s">
+      <c r="B144" s="76"/>
+      <c r="C144" s="76"/>
+      <c r="D144" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="23" t="s">
+      <c r="E144" s="20" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="145" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="73"/>
-      <c r="C145" s="73"/>
-      <c r="D145" s="23" t="s">
+      <c r="B145" s="76"/>
+      <c r="C145" s="76"/>
+      <c r="D145" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E145" s="23" t="s">
+      <c r="E145" s="20" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="146" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="73"/>
-      <c r="C146" s="73"/>
-      <c r="D146" s="23" t="s">
+      <c r="B146" s="76"/>
+      <c r="C146" s="76"/>
+      <c r="D146" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E146" s="23" t="s">
+      <c r="E146" s="20" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="147" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="73"/>
-      <c r="C147" s="73"/>
-      <c r="D147" s="23" t="s">
+      <c r="B147" s="76"/>
+      <c r="C147" s="76"/>
+      <c r="D147" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E147" s="23" t="s">
-        <v>230</v>
+      <c r="E147" s="20" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="73"/>
-      <c r="C148" s="73"/>
-      <c r="D148" s="23" t="s">
+      <c r="B148" s="76"/>
+      <c r="C148" s="76"/>
+      <c r="D148" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E148" s="23" t="s">
+      <c r="E148" s="20" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="149" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="73"/>
-      <c r="C149" s="73"/>
-      <c r="D149" s="23" t="s">
+      <c r="B149" s="76"/>
+      <c r="C149" s="76"/>
+      <c r="D149" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E149" s="23" t="s">
+      <c r="E149" s="20" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="150" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="73"/>
-      <c r="C150" s="73"/>
-      <c r="D150" s="23" t="s">
+      <c r="B150" s="76"/>
+      <c r="C150" s="76"/>
+      <c r="D150" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="E150" s="23" t="s">
+      <c r="E150" s="20" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="151" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="73"/>
-      <c r="C151" s="73"/>
-      <c r="D151" s="23" t="s">
+      <c r="B151" s="76"/>
+      <c r="C151" s="76"/>
+      <c r="D151" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E151" s="23" t="s">
+      <c r="E151" s="20" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="152" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="73"/>
-      <c r="C152" s="73"/>
-      <c r="D152" s="23" t="s">
+      <c r="B152" s="76"/>
+      <c r="C152" s="76"/>
+      <c r="D152" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E152" s="23" t="s">
+      <c r="E152" s="20" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="153" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="73"/>
-      <c r="C153" s="73"/>
-      <c r="D153" s="23" t="s">
+      <c r="B153" s="76"/>
+      <c r="C153" s="76"/>
+      <c r="D153" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E153" s="23" t="s">
+      <c r="E153" s="20" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="154" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="73"/>
-      <c r="C154" s="73"/>
-      <c r="D154" s="23" t="s">
+      <c r="B154" s="76"/>
+      <c r="C154" s="76"/>
+      <c r="D154" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="E154" s="20" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="155" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="73"/>
-      <c r="C155" s="73"/>
-      <c r="D155" s="23" t="s">
+      <c r="B155" s="76"/>
+      <c r="C155" s="76"/>
+      <c r="D155" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E155" s="23" t="s">
+      <c r="E155" s="20" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="156" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="73"/>
-      <c r="C156" s="73"/>
-      <c r="D156" s="23" t="s">
+      <c r="B156" s="76"/>
+      <c r="C156" s="76"/>
+      <c r="D156" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E156" s="23" t="s">
+      <c r="E156" s="20" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="157" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="73"/>
-      <c r="C157" s="73"/>
-      <c r="D157" s="23" t="s">
+      <c r="B157" s="76"/>
+      <c r="C157" s="76"/>
+      <c r="D157" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E157" s="23" t="s">
+      <c r="E157" s="20" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="158" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="23" t="s">
+      <c r="B158" s="76"/>
+      <c r="C158" s="76"/>
+      <c r="D158" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E158" s="23" t="s">
+      <c r="E158" s="20" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="159" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="73"/>
-      <c r="C159" s="73"/>
-      <c r="D159" s="23" t="s">
+      <c r="B159" s="76"/>
+      <c r="C159" s="76"/>
+      <c r="D159" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E159" s="23" t="s">
+      <c r="E159" s="20" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="160" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="73"/>
-      <c r="C160" s="73"/>
-      <c r="D160" s="23" t="s">
+      <c r="B160" s="76"/>
+      <c r="C160" s="76"/>
+      <c r="D160" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E160" s="23" t="s">
+      <c r="E160" s="20" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="161" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="73"/>
-      <c r="C161" s="73"/>
-      <c r="D161" s="23" t="s">
+      <c r="B161" s="76"/>
+      <c r="C161" s="76"/>
+      <c r="D161" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E161" s="23" t="s">
+      <c r="E161" s="20" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="162" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="73"/>
-      <c r="C162" s="73"/>
-      <c r="D162" s="23" t="s">
+      <c r="B162" s="76"/>
+      <c r="C162" s="76"/>
+      <c r="D162" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="E162" s="23" t="s">
+      <c r="E162" s="20" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="163" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="73"/>
-      <c r="C163" s="73"/>
-      <c r="D163" s="23" t="s">
+      <c r="B163" s="76"/>
+      <c r="C163" s="76"/>
+      <c r="D163" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="E163" s="23" t="s">
+      <c r="E163" s="20" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="164" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="73"/>
-      <c r="C164" s="73"/>
-      <c r="D164" s="23" t="s">
+      <c r="B164" s="76"/>
+      <c r="C164" s="76"/>
+      <c r="D164" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E164" s="23" t="s">
+      <c r="E164" s="20" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="165" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="74"/>
-      <c r="C165" s="74"/>
-      <c r="D165" s="23" t="s">
+      <c r="B165" s="77"/>
+      <c r="C165" s="77"/>
+      <c r="D165" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="E165" s="23" t="s">
+      <c r="E165" s="20" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="166" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="84" t="s">
+      <c r="B166" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="C166" s="85" t="s">
+      <c r="C166" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="D166" s="24" t="s">
+      <c r="D166" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E166" s="24" t="s">
+      <c r="E166" s="21" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="167" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="73"/>
-      <c r="C167" s="73"/>
-      <c r="D167" s="24" t="s">
+      <c r="B167" s="76"/>
+      <c r="C167" s="76"/>
+      <c r="D167" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E167" s="24" t="s">
+      <c r="E167" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="168" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="73"/>
-      <c r="C168" s="73"/>
-      <c r="D168" s="24" t="s">
+      <c r="B168" s="76"/>
+      <c r="C168" s="76"/>
+      <c r="D168" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E168" s="24" t="s">
+      <c r="E168" s="21" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="169" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="73"/>
-      <c r="C169" s="73"/>
-      <c r="D169" s="24" t="s">
+      <c r="B169" s="76"/>
+      <c r="C169" s="76"/>
+      <c r="D169" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E169" s="24" t="s">
+      <c r="E169" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="170" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="73"/>
-      <c r="C170" s="73"/>
-      <c r="D170" s="24" t="s">
+      <c r="B170" s="76"/>
+      <c r="C170" s="76"/>
+      <c r="D170" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E170" s="24" t="s">
+      <c r="E170" s="21" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="171" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="73"/>
-      <c r="C171" s="73"/>
-      <c r="D171" s="24" t="s">
+      <c r="B171" s="76"/>
+      <c r="C171" s="76"/>
+      <c r="D171" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E171" s="24" t="s">
+      <c r="E171" s="21" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="172" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="73"/>
-      <c r="C172" s="73"/>
-      <c r="D172" s="24" t="s">
+      <c r="B172" s="76"/>
+      <c r="C172" s="76"/>
+      <c r="D172" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E172" s="24" t="s">
+      <c r="E172" s="21" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="173" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="73"/>
-      <c r="C173" s="73"/>
-      <c r="D173" s="24" t="s">
+      <c r="B173" s="76"/>
+      <c r="C173" s="76"/>
+      <c r="D173" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E173" s="24" t="s">
+      <c r="E173" s="21" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="174" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="73"/>
-      <c r="C174" s="73"/>
-      <c r="D174" s="24" t="s">
+      <c r="B174" s="76"/>
+      <c r="C174" s="76"/>
+      <c r="D174" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="175" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="73"/>
-      <c r="C175" s="73"/>
-      <c r="D175" s="24" t="s">
+      <c r="B175" s="76"/>
+      <c r="C175" s="76"/>
+      <c r="D175" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E175" s="24" t="s">
+      <c r="E175" s="21" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="176" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="74"/>
-      <c r="C176" s="74"/>
-      <c r="D176" s="24" t="s">
+      <c r="B176" s="77"/>
+      <c r="C176" s="77"/>
+      <c r="D176" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E176" s="24" t="s">
+      <c r="E176" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="177" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="76" t="s">
+      <c r="B177" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C177" s="77" t="s">
+      <c r="C177" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="D177" s="25" t="s">
+      <c r="D177" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="E177" s="25" t="s">
+      <c r="E177" s="22" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="73"/>
-      <c r="C178" s="73"/>
-      <c r="D178" s="25" t="s">
+      <c r="B178" s="76"/>
+      <c r="C178" s="76"/>
+      <c r="D178" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E178" s="25" t="s">
+      <c r="E178" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="179" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="73"/>
-      <c r="C179" s="73"/>
-      <c r="D179" s="25" t="s">
+      <c r="B179" s="76"/>
+      <c r="C179" s="76"/>
+      <c r="D179" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E179" s="25" t="s">
+      <c r="E179" s="22" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="180" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="25" t="s">
+      <c r="B180" s="76"/>
+      <c r="C180" s="76"/>
+      <c r="D180" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="E180" s="25" t="s">
+      <c r="E180" s="22" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="181" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="73"/>
-      <c r="C181" s="73"/>
-      <c r="D181" s="25" t="s">
+      <c r="B181" s="76"/>
+      <c r="C181" s="76"/>
+      <c r="D181" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="E181" s="25" t="s">
+      <c r="E181" s="22" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="73"/>
-      <c r="C182" s="73"/>
-      <c r="D182" s="25" t="s">
+      <c r="B182" s="76"/>
+      <c r="C182" s="76"/>
+      <c r="D182" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="E182" s="25" t="s">
+      <c r="E182" s="22" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="183" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="73"/>
-      <c r="C183" s="73"/>
-      <c r="D183" s="25" t="s">
+      <c r="B183" s="76"/>
+      <c r="C183" s="76"/>
+      <c r="D183" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="E183" s="25" t="s">
+      <c r="E183" s="22" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="73"/>
-      <c r="C184" s="73"/>
-      <c r="D184" s="25" t="s">
+      <c r="B184" s="76"/>
+      <c r="C184" s="76"/>
+      <c r="D184" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="E184" s="25" t="s">
+      <c r="E184" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="185" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="73"/>
-      <c r="C185" s="73"/>
-      <c r="D185" s="25" t="s">
+      <c r="B185" s="76"/>
+      <c r="C185" s="76"/>
+      <c r="D185" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="E185" s="25" t="s">
+      <c r="E185" s="22" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="186" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="74"/>
-      <c r="C186" s="74"/>
-      <c r="D186" s="25" t="s">
+      <c r="B186" s="77"/>
+      <c r="C186" s="77"/>
+      <c r="D186" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="E186" s="25" t="s">
+      <c r="E186" s="22" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="78" t="s">
+      <c r="B187" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="C187" s="79" t="s">
+      <c r="C187" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="D187" s="26" t="s">
+      <c r="D187" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="E187" s="26" t="s">
+      <c r="E187" s="23" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="188" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="73"/>
-      <c r="C188" s="73"/>
-      <c r="D188" s="26" t="s">
+      <c r="B188" s="76"/>
+      <c r="C188" s="76"/>
+      <c r="D188" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E188" s="26" t="s">
+      <c r="E188" s="23" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="189" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="73"/>
-      <c r="C189" s="73"/>
-      <c r="D189" s="26" t="s">
+      <c r="B189" s="76"/>
+      <c r="C189" s="76"/>
+      <c r="D189" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="E189" s="26" t="s">
+      <c r="E189" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="73"/>
-      <c r="C190" s="73"/>
-      <c r="D190" s="26" t="s">
+      <c r="B190" s="76"/>
+      <c r="C190" s="76"/>
+      <c r="D190" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="E190" s="26" t="s">
+      <c r="E190" s="23" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="191" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="73"/>
-      <c r="C191" s="73"/>
-      <c r="D191" s="26" t="s">
+      <c r="B191" s="76"/>
+      <c r="C191" s="76"/>
+      <c r="D191" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="E191" s="26" t="s">
+      <c r="E191" s="23" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="192" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="73"/>
-      <c r="C192" s="73"/>
-      <c r="D192" s="26" t="s">
+      <c r="B192" s="76"/>
+      <c r="C192" s="76"/>
+      <c r="D192" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="E192" s="26" t="s">
+      <c r="E192" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="193" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="73"/>
-      <c r="C193" s="73"/>
-      <c r="D193" s="26" t="s">
+      <c r="B193" s="76"/>
+      <c r="C193" s="76"/>
+      <c r="D193" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="E193" s="26" t="s">
+      <c r="E193" s="23" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="194" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="73"/>
-      <c r="C194" s="73"/>
-      <c r="D194" s="26" t="s">
+      <c r="B194" s="76"/>
+      <c r="C194" s="76"/>
+      <c r="D194" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="E194" s="26" t="s">
+      <c r="E194" s="23" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="195" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="73"/>
-      <c r="C195" s="73"/>
-      <c r="D195" s="26" t="s">
+      <c r="B195" s="76"/>
+      <c r="C195" s="76"/>
+      <c r="D195" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="E195" s="26" t="s">
+      <c r="E195" s="23" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="196" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="74"/>
-      <c r="C196" s="74"/>
-      <c r="D196" s="26" t="s">
+      <c r="B196" s="77"/>
+      <c r="C196" s="77"/>
+      <c r="D196" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="E196" s="26" t="s">
+      <c r="E196" s="23" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6942,22 +6979,6 @@
     <row r="1071" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B142:B165"/>
     <mergeCell ref="B166:B176"/>
     <mergeCell ref="B177:B186"/>
     <mergeCell ref="B25:B29"/>
@@ -6971,8 +6992,24 @@
     <mergeCell ref="B121:B141"/>
     <mergeCell ref="C121:C141"/>
     <mergeCell ref="C142:C165"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B142:B165"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/utilities/Analisis_pestel_Mabel.xlsx
+++ b/utilities/Analisis_pestel_Mabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59802193-D0D9-40A5-ADF7-AF2929FCC772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64998743-2016-411E-8566-E1B395343E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="278">
   <si>
     <t>IMPACTO</t>
   </si>
@@ -696,75 +696,6 @@
     <t>JUSTIFICACIÓN TÉCNICA</t>
   </si>
   <si>
-    <t>Auge de Manufactura y Finanzas Crecimiento &gt;8%</t>
-  </si>
-  <si>
-    <t>Crecimiento de Matrícula Técnica 25.03% semestral</t>
-  </si>
-  <si>
-    <t>Títulos Obtenidos por Mujeres 56.1%</t>
-  </si>
-  <si>
-    <t>Demanda en Ciberseguridad y Big Data 28.5%</t>
-  </si>
-  <si>
-    <t>Acceso a Internet en Hogares 71.3%</t>
-  </si>
-  <si>
-    <t>Brecha Rural Acceso de solo el 45.3%</t>
-  </si>
-  <si>
-    <t>Maestrías Tecnológicas Crecimiento del 25%</t>
-  </si>
-  <si>
-    <t>Escalafón Docente 70% de cumplimiento CES</t>
-  </si>
-  <si>
-    <t>Incentivos para Bachillerato Técnico para 33k nuevos alumnos</t>
-  </si>
-  <si>
-    <t>Inversión en Educación Pública genera un ajuste presupuestario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Política pública en formación en linea </t>
-  </si>
-  <si>
-    <t>Crecimiento del PIB con una proyección 1.8% para 2026</t>
-  </si>
-  <si>
-    <t>Desempleo Juvenil del 80.1% con dificultades de inserción</t>
-  </si>
-  <si>
-    <t>Consumo de Hogares con un crecimiento del 10.2%</t>
-  </si>
-  <si>
-    <t>Deserción en el Primer Año con una meta de reducción al 19.8%</t>
-  </si>
-  <si>
-    <t>Adopción de IA en currículo en el 47.3% de programas</t>
-  </si>
-  <si>
-    <t>Aspirantes SENESCYT 250000 alumnos por periodo</t>
-  </si>
-  <si>
-    <t>Demanda Insatisfecha 150000 jóvenes sin cupo público</t>
-  </si>
-  <si>
-    <t>Conciencia ambiental institucional</t>
-  </si>
-  <si>
-    <t>Inclusión de temas ambientales en la formación</t>
-  </si>
-  <si>
-    <t>La sostenibilidad se ha convertido en un valor social relevante</t>
-  </si>
-  <si>
-    <t>Responsabilidad social ambiental</t>
-  </si>
-  <si>
-    <t>Ley de Acceso Universal a la Educación</t>
-  </si>
-  <si>
     <t>FUENTE</t>
   </si>
   <si>
@@ -774,18 +705,12 @@
     <t>Preferencia de los ecuatorianos a comprar por internet</t>
   </si>
   <si>
-    <t>Ley de Regulación a Contrabando de Tecnología SENAE 2026</t>
-  </si>
-  <si>
     <t>Alta informalidad en venta de alimentos callejeros.</t>
   </si>
   <si>
     <t>Genera competencia desleal en precios para negocios formales.</t>
   </si>
   <si>
-    <t>Posibles impuestos o permisos municipales para negocios de comida.</t>
-  </si>
-  <si>
     <t>Incrementa costos operativos iniciales.</t>
   </si>
   <si>
@@ -994,24 +919,20 @@
   </si>
   <si>
     <t>T11</t>
+  </si>
+  <si>
+    <t>Impuestos o permisos municipales para negocios de comida.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1123,22 +1044,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1239,6 +1171,18 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFFFC1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2CFF1"/>
+        <bgColor rgb="FFE2EFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2CFF1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1456,9 +1400,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1469,39 +1413,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1511,25 +1431,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1539,78 +1456,30 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1621,169 +1490,208 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1793,6 +1701,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE2CFF1"/>
       <color rgb="FFFFFFC1"/>
       <color rgb="FFFF99FF"/>
     </mruColors>
@@ -2023,938 +1932,938 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="62" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="37" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="17" t="s">
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="17" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="62" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="37" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="17" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="17" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="17" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="17" t="s">
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="76"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="62" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="37" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="76"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="62" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="37" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="17" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="17" t="s">
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="17" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H16" s="19"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="76"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="64" t="s">
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="39" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="18" t="s">
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="64" t="s">
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="64" t="s">
+      <c r="E19" s="39" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="64" t="s">
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="76"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="18" t="s">
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="18" t="s">
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="18" t="s">
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="10" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="18" t="s">
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="64" t="s">
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="64" t="s">
+      <c r="E25" s="39" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="18" t="s">
+      <c r="B26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="18" t="s">
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="18" t="s">
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="18" t="s">
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="18" t="s">
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="10" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="18" t="s">
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="76"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="18" t="s">
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="18" t="s">
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="18" t="s">
+      <c r="B34" s="61"/>
+      <c r="C34" s="61"/>
+      <c r="D34" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="18" t="s">
+      <c r="B35" s="61"/>
+      <c r="C35" s="61"/>
+      <c r="D35" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="18" t="s">
+      <c r="B36" s="62"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="86" t="s">
+      <c r="C37" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H37" s="19"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="76"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="20" t="s">
+      <c r="B38" s="61"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="76"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="20" t="s">
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="76"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="20" t="s">
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="76"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="20" t="s">
+      <c r="B41" s="61"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="66" t="s">
+      <c r="B42" s="61"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="66" t="s">
-        <v>227</v>
+      <c r="E42" s="41" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="20" t="s">
+      <c r="B43" s="61"/>
+      <c r="C43" s="61"/>
+      <c r="D43" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="12" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="76"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="20" t="s">
+      <c r="B44" s="61"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="76"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="20" t="s">
+      <c r="B45" s="61"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="76"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="20" t="s">
+      <c r="B46" s="61"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="66" t="s">
+      <c r="B47" s="61"/>
+      <c r="C47" s="61"/>
+      <c r="D47" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="E47" s="66" t="s">
+      <c r="E47" s="41" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="66" t="s">
+      <c r="B48" s="61"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="E48" s="66" t="s">
+      <c r="E48" s="41" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="76"/>
-      <c r="C49" s="76"/>
-      <c r="D49" s="20" t="s">
+      <c r="B49" s="61"/>
+      <c r="C49" s="61"/>
+      <c r="D49" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="12" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="76"/>
-      <c r="C50" s="76"/>
-      <c r="D50" s="20" t="s">
+      <c r="B50" s="61"/>
+      <c r="C50" s="61"/>
+      <c r="D50" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="76"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="20" t="s">
+      <c r="B51" s="61"/>
+      <c r="C51" s="61"/>
+      <c r="D51" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="20" t="s">
+      <c r="B52" s="61"/>
+      <c r="C52" s="61"/>
+      <c r="D52" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="76"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="20" t="s">
+      <c r="B53" s="61"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="20" t="s">
+      <c r="B54" s="61"/>
+      <c r="C54" s="61"/>
+      <c r="D54" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="76"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="20" t="s">
+      <c r="B55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="12" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="76"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="20" t="s">
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="12" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="66" t="s">
+      <c r="B57" s="61"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="E57" s="66" t="s">
+      <c r="E57" s="41" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="76"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="20" t="s">
+      <c r="B58" s="61"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="12" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="59" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="76"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="20" t="s">
+      <c r="B59" s="61"/>
+      <c r="C59" s="61"/>
+      <c r="D59" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="12" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="77"/>
-      <c r="C60" s="77"/>
-      <c r="D60" s="20" t="s">
+      <c r="B60" s="62"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="12" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="87" t="s">
+      <c r="B61" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="88" t="s">
+      <c r="C61" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="67" t="s">
+      <c r="D61" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="42" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="76"/>
-      <c r="C62" s="76"/>
-      <c r="D62" s="21" t="s">
+      <c r="B62" s="61"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="13" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="76"/>
-      <c r="C63" s="76"/>
-      <c r="D63" s="67" t="s">
+      <c r="B63" s="61"/>
+      <c r="C63" s="61"/>
+      <c r="D63" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="67" t="s">
+      <c r="E63" s="42" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="67" t="s">
+      <c r="B64" s="61"/>
+      <c r="C64" s="61"/>
+      <c r="D64" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="67" t="s">
+      <c r="E64" s="42" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="76"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="21" t="s">
+      <c r="B65" s="61"/>
+      <c r="C65" s="61"/>
+      <c r="D65" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="21" t="s">
+      <c r="E65" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="76"/>
-      <c r="C66" s="76"/>
-      <c r="D66" s="21" t="s">
+      <c r="B66" s="61"/>
+      <c r="C66" s="61"/>
+      <c r="D66" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E66" s="21" t="s">
+      <c r="E66" s="13" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="76"/>
-      <c r="C67" s="76"/>
-      <c r="D67" s="21" t="s">
+      <c r="B67" s="61"/>
+      <c r="C67" s="61"/>
+      <c r="D67" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E67" s="21" t="s">
+      <c r="E67" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="76"/>
-      <c r="C68" s="76"/>
-      <c r="D68" s="21" t="s">
+      <c r="B68" s="61"/>
+      <c r="C68" s="61"/>
+      <c r="D68" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E68" s="21" t="s">
+      <c r="E68" s="13" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="21" t="s">
+      <c r="B69" s="61"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E69" s="21" t="s">
+      <c r="E69" s="13" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="76"/>
-      <c r="C70" s="76"/>
-      <c r="D70" s="21" t="s">
+      <c r="B70" s="61"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="21" t="s">
+      <c r="E70" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="77"/>
-      <c r="C71" s="77"/>
-      <c r="D71" s="67" t="s">
+      <c r="B71" s="62"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E71" s="67" t="s">
+      <c r="E71" s="42" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="79" t="s">
+      <c r="B72" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="80" t="s">
+      <c r="C72" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="68" t="s">
+      <c r="D72" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="68" t="s">
+      <c r="E72" s="43" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="76"/>
-      <c r="C73" s="76"/>
-      <c r="D73" s="22" t="s">
+      <c r="B73" s="61"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="14" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="74" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="76"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="22" t="s">
+      <c r="B74" s="61"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="14" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="75" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="76"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="68" t="s">
+      <c r="B75" s="61"/>
+      <c r="C75" s="61"/>
+      <c r="D75" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="68" t="s">
+      <c r="E75" s="43" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="76" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="76"/>
-      <c r="C76" s="76"/>
-      <c r="D76" s="68" t="s">
+      <c r="B76" s="61"/>
+      <c r="C76" s="61"/>
+      <c r="D76" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="68" t="s">
+      <c r="E76" s="43" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="77" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="76"/>
-      <c r="C77" s="76"/>
-      <c r="D77" s="22" t="s">
+      <c r="B77" s="61"/>
+      <c r="C77" s="61"/>
+      <c r="D77" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="14" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="78" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="76"/>
-      <c r="C78" s="76"/>
-      <c r="D78" s="68" t="s">
+      <c r="B78" s="61"/>
+      <c r="C78" s="61"/>
+      <c r="D78" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="68" t="s">
+      <c r="E78" s="43" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="76"/>
-      <c r="C79" s="76"/>
-      <c r="D79" s="22" t="s">
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="80" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="76"/>
-      <c r="C80" s="76"/>
-      <c r="D80" s="22" t="s">
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="14" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="77"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="22" t="s">
+      <c r="B81" s="62"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E81" s="22" t="s">
+      <c r="E81" s="14" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="82" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="81" t="s">
+      <c r="B82" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="82" t="s">
+      <c r="C82" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D82" s="23" t="s">
+      <c r="D82" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E82" s="23" t="s">
+      <c r="E82" s="15" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="83" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="76"/>
-      <c r="C83" s="76"/>
-      <c r="D83" s="23" t="s">
+      <c r="B83" s="61"/>
+      <c r="C83" s="61"/>
+      <c r="D83" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E83" s="23" t="s">
+      <c r="E83" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="84" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="76"/>
-      <c r="C84" s="76"/>
-      <c r="D84" s="23" t="s">
+      <c r="B84" s="61"/>
+      <c r="C84" s="61"/>
+      <c r="D84" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="E84" s="23" t="s">
+      <c r="E84" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="85" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="76"/>
-      <c r="C85" s="76"/>
-      <c r="D85" s="69" t="s">
+      <c r="B85" s="61"/>
+      <c r="C85" s="61"/>
+      <c r="D85" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="E85" s="69" t="s">
+      <c r="E85" s="44" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="86" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="76"/>
-      <c r="C86" s="76"/>
-      <c r="D86" s="23" t="s">
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="E86" s="23" t="s">
+      <c r="E86" s="15" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="87" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="76"/>
-      <c r="C87" s="76"/>
-      <c r="D87" s="23" t="s">
+      <c r="B87" s="61"/>
+      <c r="C87" s="61"/>
+      <c r="D87" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="23" t="s">
+      <c r="E87" s="15" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="88" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="76"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="69" t="s">
+      <c r="B88" s="61"/>
+      <c r="C88" s="61"/>
+      <c r="D88" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="E88" s="69" t="s">
+      <c r="E88" s="44" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="89" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="76"/>
-      <c r="C89" s="76"/>
-      <c r="D89" s="69" t="s">
+      <c r="B89" s="61"/>
+      <c r="C89" s="61"/>
+      <c r="D89" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="69" t="s">
+      <c r="E89" s="44" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="90" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="76"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="23" t="s">
+      <c r="B90" s="61"/>
+      <c r="C90" s="61"/>
+      <c r="D90" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="E90" s="23" t="s">
+      <c r="E90" s="15" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="91" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="77"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="69" t="s">
+      <c r="B91" s="62"/>
+      <c r="C91" s="62"/>
+      <c r="D91" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="E91" s="69" t="s">
+      <c r="E91" s="44" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3867,490 +3776,490 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="75"/>
+      <c r="B3" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="75"/>
+      <c r="B4" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="75"/>
+      <c r="B5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="76"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="36"/>
+    </row>
+    <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75"/>
+      <c r="B8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="75"/>
+      <c r="B9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="76"/>
+      <c r="B10" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75"/>
+      <c r="B12" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="75"/>
+      <c r="B13" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="75"/>
+      <c r="B14" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="76"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="16"/>
+      <c r="F15" s="36"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="75"/>
+      <c r="B17" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" t="s">
+        <v>224</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="75"/>
+      <c r="B18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="89" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="D18" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="76"/>
+      <c r="B19" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="75"/>
+      <c r="B21" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="75"/>
+      <c r="B22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D22" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E22" t="s">
         <v>232</v>
       </c>
-      <c r="F2" s="70" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="90"/>
-      <c r="B3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="D3" s="38" t="s">
+      <c r="F22" s="47" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="75"/>
+      <c r="B23" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="75"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="36"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="E3" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="F3" s="70" t="s">
+      <c r="E25" t="s">
+        <v>234</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="75"/>
+      <c r="B26" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="75"/>
+      <c r="B27" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" t="s">
+        <v>238</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="76"/>
+      <c r="B28" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="90"/>
-      <c r="B5" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="71" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="91"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="60"/>
-    </row>
-    <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="89" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="F7" s="71" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>235</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="72" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>238</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="65" t="s">
-        <v>273</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="32" t="s">
+      <c r="F28" s="46" t="s">
         <v>275</v>
-      </c>
-      <c r="F10" s="72" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>276</v>
-      </c>
-      <c r="D11" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>277</v>
-      </c>
-      <c r="F11" s="72" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F12" s="71" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F13" s="71" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="F14" s="60" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="25"/>
-      <c r="F15" s="60"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="72" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="90"/>
-      <c r="B17" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F17" s="71" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="90"/>
-      <c r="B18" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
-      <c r="B19" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="F19" s="71" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E20" t="s">
-        <v>255</v>
-      </c>
-      <c r="F20" s="72" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="90"/>
-      <c r="B21" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E21" t="s">
-        <v>253</v>
-      </c>
-      <c r="F21" s="72" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="90"/>
-      <c r="B22" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>256</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" t="s">
-        <v>257</v>
-      </c>
-      <c r="F22" s="72" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="90"/>
-      <c r="B23" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="F23" s="71" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="90"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="60"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" t="s">
-        <v>258</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E25" t="s">
-        <v>259</v>
-      </c>
-      <c r="F25" s="72" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="90"/>
-      <c r="B26" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" t="s">
-        <v>260</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" t="s">
-        <v>261</v>
-      </c>
-      <c r="F26" s="72" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="90"/>
-      <c r="B27" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s">
-        <v>262</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" t="s">
-        <v>263</v>
-      </c>
-      <c r="F27" s="72" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="91"/>
-      <c r="B28" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="F28" s="71" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4409,17 +4318,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="92" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
+      <c r="B1" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F2" s="1" t="s">
@@ -4428,22 +4337,22 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="97" t="s">
+      <c r="H2" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="99" t="s">
+      <c r="I2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="100" t="s">
+      <c r="J2" s="91" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="33" t="s">
+      <c r="C3" s="93"/>
+      <c r="D3" s="24" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -4455,640 +4364,640 @@
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="104" t="s">
+      <c r="C4" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="25" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F4" s="53">
+        <v>277</v>
+      </c>
+      <c r="F4" s="104">
+        <v>2</v>
+      </c>
+      <c r="G4" s="105">
         <v>3</v>
       </c>
-      <c r="G4" s="41">
+      <c r="H4" s="106">
+        <f t="shared" ref="H4:H28" si="0">F4*G4</f>
+        <v>6</v>
+      </c>
+      <c r="I4" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="106"/>
+    </row>
+    <row r="5" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="104">
         <v>3</v>
       </c>
-      <c r="H4" s="6">
-        <f t="shared" ref="H4:H29" si="0">F4*G4</f>
+      <c r="G5" s="107">
+        <v>3</v>
+      </c>
+      <c r="H5" s="106">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I4" s="61" t="s">
+      <c r="I5" s="108"/>
+      <c r="J5" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="F5" s="54">
+    </row>
+    <row r="6" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" s="104">
+        <v>3</v>
+      </c>
+      <c r="G6" s="107">
+        <v>3</v>
+      </c>
+      <c r="H6" s="106">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="104">
+        <v>3</v>
+      </c>
+      <c r="G7" s="107">
         <v>2</v>
       </c>
-      <c r="G5" s="42">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="H7" s="106">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I7" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="J7" s="108"/>
+    </row>
+    <row r="8" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F8" s="109">
+        <v>2</v>
+      </c>
+      <c r="G8" s="109">
+        <v>3</v>
+      </c>
+      <c r="H8" s="110">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="84"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F6" s="53">
+      <c r="F9" s="109">
         <v>3</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G9" s="109">
+        <v>2</v>
+      </c>
+      <c r="H9" s="110">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I9" s="110"/>
+      <c r="J9" s="110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="84"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="109">
+        <v>2</v>
+      </c>
+      <c r="G10" s="109">
         <v>3</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H10" s="110">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I10" s="111" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="110"/>
+    </row>
+    <row r="11" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="84"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="109">
+        <v>3</v>
+      </c>
+      <c r="G11" s="109">
+        <v>2</v>
+      </c>
+      <c r="H11" s="110">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="112">
+        <v>3</v>
+      </c>
+      <c r="G12" s="112">
+        <v>3</v>
+      </c>
+      <c r="H12" s="113">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I12" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="54">
+      <c r="J12" s="113"/>
+    </row>
+    <row r="13" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="114">
         <v>3</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G13" s="114">
         <v>2</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H13" s="115">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="47" t="s">
+      <c r="I13" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="43">
+      <c r="J13" s="115"/>
+    </row>
+    <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="86"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="114">
         <v>2</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G14" s="114">
         <v>3</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H14" s="115">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I14" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="93"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="F9" s="43">
+      <c r="J14" s="116"/>
+    </row>
+    <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="86"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="114">
         <v>3</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G15" s="114">
+        <v>3</v>
+      </c>
+      <c r="H15" s="115">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="86"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="114">
+        <v>3</v>
+      </c>
+      <c r="G16" s="114">
         <v>2</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H16" s="115">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="48" t="s">
+      <c r="I16" s="115" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="93"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" s="43">
+      <c r="J16" s="115"/>
+    </row>
+    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="117">
+        <v>2</v>
+      </c>
+      <c r="G17" s="117">
+        <v>2</v>
+      </c>
+      <c r="H17" s="118">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I17" s="118" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="118"/>
+    </row>
+    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="117">
+        <v>2</v>
+      </c>
+      <c r="G18" s="117">
+        <v>2</v>
+      </c>
+      <c r="H18" s="118">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I18" s="118" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="119"/>
+    </row>
+    <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" s="117">
         <v>3</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G19" s="117">
+        <v>2</v>
+      </c>
+      <c r="H19" s="118">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I19" s="118" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="118"/>
+    </row>
+    <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="117">
         <v>3</v>
       </c>
-      <c r="H10" s="9">
+      <c r="G20" s="117">
+        <v>3</v>
+      </c>
+      <c r="H20" s="118">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="48" t="s">
+      <c r="I20" s="118"/>
+      <c r="J20" s="118" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="93"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="F11" s="43">
+    <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" s="120">
+        <v>2</v>
+      </c>
+      <c r="G21" s="120">
+        <v>2</v>
+      </c>
+      <c r="H21" s="121">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I21" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="121"/>
+    </row>
+    <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="79"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="120">
+        <v>2</v>
+      </c>
+      <c r="G22" s="120">
+        <v>2</v>
+      </c>
+      <c r="H22" s="121">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I22" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="121"/>
+    </row>
+    <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="79"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="56" t="s">
+        <v>231</v>
+      </c>
+      <c r="F23" s="120">
+        <v>2</v>
+      </c>
+      <c r="G23" s="120">
         <v>3</v>
       </c>
-      <c r="G11" s="43">
-        <v>2</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="H23" s="121">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I23" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="95" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="96" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="111" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="112" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" s="113">
+      <c r="J23" s="121"/>
+    </row>
+    <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="79"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" s="120">
+        <v>2</v>
+      </c>
+      <c r="G24" s="120">
+        <v>2</v>
+      </c>
+      <c r="H24" s="121">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I24" s="121" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="121"/>
+    </row>
+    <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="100">
         <v>3</v>
       </c>
-      <c r="G12" s="114">
+      <c r="G25" s="100">
         <v>3</v>
       </c>
-      <c r="H12" s="115">
+      <c r="H25" s="101">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I12" s="116" t="s">
+      <c r="I25" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="115"/>
-    </row>
-    <row r="13" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="44">
+      <c r="J25" s="101"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="100">
         <v>3</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G26" s="100">
+        <v>3</v>
+      </c>
+      <c r="H26" s="101">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I26" s="101" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="101"/>
+    </row>
+    <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="F27" s="102">
         <v>2</v>
       </c>
-      <c r="H13" s="12">
+      <c r="G27" s="100">
+        <v>2</v>
+      </c>
+      <c r="H27" s="101">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I27" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="101"/>
+    </row>
+    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="77"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="59" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="F28" s="97">
+        <v>3</v>
+      </c>
+      <c r="G28" s="98">
+        <v>2</v>
+      </c>
+      <c r="H28" s="99">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="49" t="s">
+      <c r="I28" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14" s="44">
-        <v>2</v>
-      </c>
-      <c r="G14" s="44">
-        <v>3</v>
-      </c>
-      <c r="H14" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F15" s="55">
-        <v>3</v>
-      </c>
-      <c r="G15" s="44">
-        <v>3</v>
-      </c>
-      <c r="H15" s="12">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="55">
-        <v>3</v>
-      </c>
-      <c r="G16" s="44">
-        <v>2</v>
-      </c>
-      <c r="H16" s="12">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="108" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="117" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="118" t="s">
-        <v>217</v>
-      </c>
-      <c r="F17" s="119">
-        <v>3</v>
-      </c>
-      <c r="G17" s="120">
-        <v>2</v>
-      </c>
-      <c r="H17" s="121">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I17" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="121"/>
-    </row>
-    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="132" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="118" t="s">
-        <v>205</v>
-      </c>
-      <c r="F18" s="119">
-        <v>2</v>
-      </c>
-      <c r="G18" s="120">
-        <v>2</v>
-      </c>
-      <c r="H18" s="121">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I18" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="123"/>
-    </row>
-    <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="132" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="118" t="s">
-        <v>206</v>
-      </c>
-      <c r="F19" s="119">
-        <v>3</v>
-      </c>
-      <c r="G19" s="120">
-        <v>2</v>
-      </c>
-      <c r="H19" s="121">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I19" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="121"/>
-    </row>
-    <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="107"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="132" t="s">
-        <v>301</v>
-      </c>
-      <c r="E20" s="118" t="s">
-        <v>207</v>
-      </c>
-      <c r="F20" s="119">
-        <v>1</v>
-      </c>
-      <c r="G20" s="120">
-        <v>3</v>
-      </c>
-      <c r="H20" s="121">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="I20" s="121"/>
-      <c r="J20" s="122" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="105" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="106" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="125" t="s">
-        <v>220</v>
-      </c>
-      <c r="F21" s="126">
-        <v>2</v>
-      </c>
-      <c r="G21" s="126">
-        <v>2</v>
-      </c>
-      <c r="H21" s="127">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I21" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="127"/>
-    </row>
-    <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="133" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="125" t="s">
-        <v>221</v>
-      </c>
-      <c r="F22" s="126">
-        <v>2</v>
-      </c>
-      <c r="G22" s="126">
-        <v>2</v>
-      </c>
-      <c r="H22" s="127">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I22" s="129" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="127"/>
-    </row>
-    <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="133" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="130" t="s">
-        <v>222</v>
-      </c>
-      <c r="F23" s="131">
-        <v>3</v>
-      </c>
-      <c r="G23" s="126">
-        <v>3</v>
-      </c>
-      <c r="H23" s="127">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I23" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="127"/>
-    </row>
-    <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="133" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="130" t="s">
-        <v>223</v>
-      </c>
-      <c r="F24" s="131">
-        <v>2</v>
-      </c>
-      <c r="G24" s="126">
-        <v>2</v>
-      </c>
-      <c r="H24" s="127">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I24" s="128" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="127"/>
-    </row>
-    <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="110" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="134" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="F25" s="45">
-        <v>3</v>
-      </c>
-      <c r="G25" s="45">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="50"/>
-    </row>
-    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="109"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="134" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="F26" s="56">
-        <v>3</v>
-      </c>
-      <c r="G26" s="45">
-        <v>3</v>
-      </c>
-      <c r="H26" s="14">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="14"/>
-    </row>
-    <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="109"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="134" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="24">
-        <v>3</v>
-      </c>
-      <c r="G27" s="45">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="14"/>
-    </row>
-    <row r="28" spans="2:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="109"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="134" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="F28" s="57">
-        <v>3</v>
-      </c>
-      <c r="G28" s="46">
-        <v>2</v>
-      </c>
-      <c r="H28" s="15">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I28" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="15"/>
+      <c r="J28" s="99"/>
     </row>
     <row r="29" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="109"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="16"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5167,938 +5076,938 @@
     <row r="104" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="75" t="s">
+      <c r="B106" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="78" t="s">
+      <c r="C106" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="17" t="s">
+      <c r="E106" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="107" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="76"/>
-      <c r="C107" s="76"/>
-      <c r="D107" s="17" t="s">
+      <c r="B107" s="61"/>
+      <c r="C107" s="61"/>
+      <c r="D107" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="108" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="76"/>
-      <c r="C108" s="76"/>
-      <c r="D108" s="17" t="s">
+      <c r="B108" s="61"/>
+      <c r="C108" s="61"/>
+      <c r="D108" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="109" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="76"/>
-      <c r="C109" s="76"/>
-      <c r="D109" s="17" t="s">
+      <c r="B109" s="61"/>
+      <c r="C109" s="61"/>
+      <c r="D109" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E109" s="17" t="s">
+      <c r="E109" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="110" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="76"/>
-      <c r="C110" s="76"/>
-      <c r="D110" s="17" t="s">
+      <c r="B110" s="61"/>
+      <c r="C110" s="61"/>
+      <c r="D110" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E110" s="17" t="s">
+      <c r="E110" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="111" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="76"/>
-      <c r="C111" s="76"/>
-      <c r="D111" s="17" t="s">
+      <c r="B111" s="61"/>
+      <c r="C111" s="61"/>
+      <c r="D111" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="112" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="76"/>
-      <c r="C112" s="76"/>
-      <c r="D112" s="17" t="s">
+      <c r="B112" s="61"/>
+      <c r="C112" s="61"/>
+      <c r="D112" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E112" s="17" t="s">
+      <c r="E112" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="113" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="76"/>
-      <c r="C113" s="76"/>
-      <c r="D113" s="17" t="s">
+      <c r="B113" s="61"/>
+      <c r="C113" s="61"/>
+      <c r="D113" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="114" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="76"/>
-      <c r="C114" s="76"/>
-      <c r="D114" s="17" t="s">
+      <c r="B114" s="61"/>
+      <c r="C114" s="61"/>
+      <c r="D114" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E114" s="17" t="s">
+      <c r="E114" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="115" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="76"/>
-      <c r="C115" s="76"/>
-      <c r="D115" s="17" t="s">
+      <c r="B115" s="61"/>
+      <c r="C115" s="61"/>
+      <c r="D115" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="116" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="76"/>
-      <c r="C116" s="76"/>
-      <c r="D116" s="17" t="s">
+      <c r="B116" s="61"/>
+      <c r="C116" s="61"/>
+      <c r="D116" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="9" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="76"/>
-      <c r="C117" s="76"/>
-      <c r="D117" s="17" t="s">
+      <c r="B117" s="61"/>
+      <c r="C117" s="61"/>
+      <c r="D117" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E117" s="17" t="s">
+      <c r="E117" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="76"/>
-      <c r="C118" s="76"/>
-      <c r="D118" s="17" t="s">
+      <c r="B118" s="61"/>
+      <c r="C118" s="61"/>
+      <c r="D118" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E118" s="17" t="s">
+      <c r="E118" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="76"/>
-      <c r="C119" s="76"/>
-      <c r="D119" s="17" t="s">
+      <c r="B119" s="61"/>
+      <c r="C119" s="61"/>
+      <c r="D119" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="77"/>
-      <c r="C120" s="77"/>
-      <c r="D120" s="17" t="s">
+      <c r="B120" s="62"/>
+      <c r="C120" s="62"/>
+      <c r="D120" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E120" s="17" t="s">
+      <c r="E120" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="121" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="83" t="s">
+      <c r="B121" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="84" t="s">
+      <c r="C121" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="D121" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E121" s="18" t="s">
+      <c r="E121" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H121" s="19"/>
+      <c r="H121" s="11"/>
     </row>
     <row r="122" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="76"/>
-      <c r="C122" s="76"/>
-      <c r="D122" s="18" t="s">
+      <c r="B122" s="61"/>
+      <c r="C122" s="61"/>
+      <c r="D122" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E122" s="18" t="s">
+      <c r="E122" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="76"/>
-      <c r="C123" s="76"/>
-      <c r="D123" s="18" t="s">
+      <c r="B123" s="61"/>
+      <c r="C123" s="61"/>
+      <c r="D123" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E123" s="18" t="s">
+      <c r="E123" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="76"/>
-      <c r="C124" s="76"/>
-      <c r="D124" s="18" t="s">
+      <c r="B124" s="61"/>
+      <c r="C124" s="61"/>
+      <c r="D124" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E124" s="18" t="s">
+      <c r="E124" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="125" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="76"/>
-      <c r="C125" s="76"/>
-      <c r="D125" s="18" t="s">
+      <c r="B125" s="61"/>
+      <c r="C125" s="61"/>
+      <c r="D125" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E125" s="18" t="s">
+      <c r="E125" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="126" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="76"/>
-      <c r="C126" s="76"/>
-      <c r="D126" s="18" t="s">
+      <c r="B126" s="61"/>
+      <c r="C126" s="61"/>
+      <c r="D126" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E126" s="18" t="s">
+      <c r="E126" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="127" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="76"/>
-      <c r="C127" s="76"/>
-      <c r="D127" s="18" t="s">
+      <c r="B127" s="61"/>
+      <c r="C127" s="61"/>
+      <c r="D127" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E127" s="18" t="s">
+      <c r="E127" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="128" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="76"/>
-      <c r="C128" s="76"/>
-      <c r="D128" s="18" t="s">
+      <c r="B128" s="61"/>
+      <c r="C128" s="61"/>
+      <c r="D128" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E128" s="18" t="s">
+      <c r="E128" s="10" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="129" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="76"/>
-      <c r="C129" s="76"/>
-      <c r="D129" s="18" t="s">
+      <c r="B129" s="61"/>
+      <c r="C129" s="61"/>
+      <c r="D129" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E129" s="18" t="s">
+      <c r="E129" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="130" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="76"/>
-      <c r="C130" s="76"/>
-      <c r="D130" s="18" t="s">
+      <c r="B130" s="61"/>
+      <c r="C130" s="61"/>
+      <c r="D130" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E130" s="18" t="s">
+      <c r="E130" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="131" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="76"/>
-      <c r="C131" s="76"/>
-      <c r="D131" s="18" t="s">
+      <c r="B131" s="61"/>
+      <c r="C131" s="61"/>
+      <c r="D131" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E131" s="18" t="s">
+      <c r="E131" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="132" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="76"/>
-      <c r="C132" s="76"/>
-      <c r="D132" s="18" t="s">
+      <c r="B132" s="61"/>
+      <c r="C132" s="61"/>
+      <c r="D132" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E132" s="18" t="s">
+      <c r="E132" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="133" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="76"/>
-      <c r="C133" s="76"/>
-      <c r="D133" s="18" t="s">
+      <c r="B133" s="61"/>
+      <c r="C133" s="61"/>
+      <c r="D133" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E133" s="18" t="s">
+      <c r="E133" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="134" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="76"/>
-      <c r="C134" s="76"/>
-      <c r="D134" s="18" t="s">
+      <c r="B134" s="61"/>
+      <c r="C134" s="61"/>
+      <c r="D134" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E134" s="18" t="s">
+      <c r="E134" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="135" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="76"/>
-      <c r="C135" s="76"/>
-      <c r="D135" s="18" t="s">
+      <c r="B135" s="61"/>
+      <c r="C135" s="61"/>
+      <c r="D135" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E135" s="18" t="s">
+      <c r="E135" s="10" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="136" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="76"/>
-      <c r="C136" s="76"/>
-      <c r="D136" s="18" t="s">
+      <c r="B136" s="61"/>
+      <c r="C136" s="61"/>
+      <c r="D136" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E136" s="18" t="s">
+      <c r="E136" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="137" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="76"/>
-      <c r="C137" s="76"/>
-      <c r="D137" s="18" t="s">
+      <c r="B137" s="61"/>
+      <c r="C137" s="61"/>
+      <c r="D137" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E137" s="18" t="s">
+      <c r="E137" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="138" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="76"/>
-      <c r="C138" s="76"/>
-      <c r="D138" s="18" t="s">
+      <c r="B138" s="61"/>
+      <c r="C138" s="61"/>
+      <c r="D138" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E138" s="18" t="s">
+      <c r="E138" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="139" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="76"/>
-      <c r="C139" s="76"/>
-      <c r="D139" s="18" t="s">
+      <c r="B139" s="61"/>
+      <c r="C139" s="61"/>
+      <c r="D139" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E139" s="18" t="s">
+      <c r="E139" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="140" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="76"/>
-      <c r="C140" s="76"/>
-      <c r="D140" s="18" t="s">
+      <c r="B140" s="61"/>
+      <c r="C140" s="61"/>
+      <c r="D140" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E140" s="18" t="s">
+      <c r="E140" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="141" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="77"/>
-      <c r="C141" s="77"/>
-      <c r="D141" s="18" t="s">
+      <c r="B141" s="62"/>
+      <c r="C141" s="62"/>
+      <c r="D141" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E141" s="18" t="s">
+      <c r="E141" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="142" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="85" t="s">
+      <c r="B142" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C142" s="86" t="s">
+      <c r="C142" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D142" s="20" t="s">
+      <c r="D142" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E142" s="20" t="s">
+      <c r="E142" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H142" s="19"/>
+      <c r="H142" s="11"/>
     </row>
     <row r="143" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="76"/>
-      <c r="C143" s="76"/>
-      <c r="D143" s="20" t="s">
+      <c r="B143" s="61"/>
+      <c r="C143" s="61"/>
+      <c r="D143" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E143" s="20" t="s">
+      <c r="E143" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="144" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="76"/>
-      <c r="C144" s="76"/>
-      <c r="D144" s="20" t="s">
+      <c r="B144" s="61"/>
+      <c r="C144" s="61"/>
+      <c r="D144" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="20" t="s">
+      <c r="E144" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="145" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="76"/>
-      <c r="C145" s="76"/>
-      <c r="D145" s="20" t="s">
+      <c r="B145" s="61"/>
+      <c r="C145" s="61"/>
+      <c r="D145" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E145" s="20" t="s">
+      <c r="E145" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="146" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="76"/>
-      <c r="C146" s="76"/>
-      <c r="D146" s="20" t="s">
+      <c r="B146" s="61"/>
+      <c r="C146" s="61"/>
+      <c r="D146" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E146" s="20" t="s">
+      <c r="E146" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="147" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="76"/>
-      <c r="C147" s="76"/>
-      <c r="D147" s="20" t="s">
+      <c r="B147" s="61"/>
+      <c r="C147" s="61"/>
+      <c r="D147" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E147" s="20" t="s">
-        <v>227</v>
+      <c r="E147" s="12" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="148" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="76"/>
-      <c r="C148" s="76"/>
-      <c r="D148" s="20" t="s">
+      <c r="B148" s="61"/>
+      <c r="C148" s="61"/>
+      <c r="D148" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E148" s="20" t="s">
+      <c r="E148" s="12" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="149" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="76"/>
-      <c r="C149" s="76"/>
-      <c r="D149" s="20" t="s">
+      <c r="B149" s="61"/>
+      <c r="C149" s="61"/>
+      <c r="D149" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E149" s="20" t="s">
+      <c r="E149" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="150" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="76"/>
-      <c r="C150" s="76"/>
-      <c r="D150" s="20" t="s">
+      <c r="B150" s="61"/>
+      <c r="C150" s="61"/>
+      <c r="D150" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E150" s="20" t="s">
+      <c r="E150" s="12" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="151" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="76"/>
-      <c r="C151" s="76"/>
-      <c r="D151" s="20" t="s">
+      <c r="B151" s="61"/>
+      <c r="C151" s="61"/>
+      <c r="D151" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E151" s="20" t="s">
+      <c r="E151" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="152" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="76"/>
-      <c r="C152" s="76"/>
-      <c r="D152" s="20" t="s">
+      <c r="B152" s="61"/>
+      <c r="C152" s="61"/>
+      <c r="D152" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="E152" s="20" t="s">
+      <c r="E152" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="153" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="76"/>
-      <c r="C153" s="76"/>
-      <c r="D153" s="20" t="s">
+      <c r="B153" s="61"/>
+      <c r="C153" s="61"/>
+      <c r="D153" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E153" s="20" t="s">
+      <c r="E153" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="154" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="76"/>
-      <c r="C154" s="76"/>
-      <c r="D154" s="20" t="s">
+      <c r="B154" s="61"/>
+      <c r="C154" s="61"/>
+      <c r="D154" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E154" s="20" t="s">
+      <c r="E154" s="12" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="155" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="76"/>
-      <c r="C155" s="76"/>
-      <c r="D155" s="20" t="s">
+      <c r="B155" s="61"/>
+      <c r="C155" s="61"/>
+      <c r="D155" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E155" s="20" t="s">
+      <c r="E155" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="156" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="76"/>
-      <c r="C156" s="76"/>
-      <c r="D156" s="20" t="s">
+      <c r="B156" s="61"/>
+      <c r="C156" s="61"/>
+      <c r="D156" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E156" s="20" t="s">
+      <c r="E156" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="157" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="76"/>
-      <c r="C157" s="76"/>
-      <c r="D157" s="20" t="s">
+      <c r="B157" s="61"/>
+      <c r="C157" s="61"/>
+      <c r="D157" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E157" s="20" t="s">
+      <c r="E157" s="12" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="158" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="76"/>
-      <c r="C158" s="76"/>
-      <c r="D158" s="20" t="s">
+      <c r="B158" s="61"/>
+      <c r="C158" s="61"/>
+      <c r="D158" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E158" s="20" t="s">
+      <c r="E158" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="159" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="76"/>
-      <c r="C159" s="76"/>
-      <c r="D159" s="20" t="s">
+      <c r="B159" s="61"/>
+      <c r="C159" s="61"/>
+      <c r="D159" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E159" s="20" t="s">
+      <c r="E159" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="160" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="76"/>
-      <c r="C160" s="76"/>
-      <c r="D160" s="20" t="s">
+      <c r="B160" s="61"/>
+      <c r="C160" s="61"/>
+      <c r="D160" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E160" s="20" t="s">
+      <c r="E160" s="12" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="161" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="76"/>
-      <c r="C161" s="76"/>
-      <c r="D161" s="20" t="s">
+      <c r="B161" s="61"/>
+      <c r="C161" s="61"/>
+      <c r="D161" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E161" s="20" t="s">
+      <c r="E161" s="12" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="162" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="76"/>
-      <c r="C162" s="76"/>
-      <c r="D162" s="20" t="s">
+      <c r="B162" s="61"/>
+      <c r="C162" s="61"/>
+      <c r="D162" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E162" s="20" t="s">
+      <c r="E162" s="12" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="163" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="76"/>
-      <c r="C163" s="76"/>
-      <c r="D163" s="20" t="s">
+      <c r="B163" s="61"/>
+      <c r="C163" s="61"/>
+      <c r="D163" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E163" s="20" t="s">
+      <c r="E163" s="12" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="164" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="76"/>
-      <c r="C164" s="76"/>
-      <c r="D164" s="20" t="s">
+      <c r="B164" s="61"/>
+      <c r="C164" s="61"/>
+      <c r="D164" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E164" s="20" t="s">
+      <c r="E164" s="12" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="165" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="77"/>
-      <c r="C165" s="77"/>
-      <c r="D165" s="20" t="s">
+      <c r="B165" s="62"/>
+      <c r="C165" s="62"/>
+      <c r="D165" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E165" s="20" t="s">
+      <c r="E165" s="12" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="166" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="87" t="s">
+      <c r="B166" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="C166" s="88" t="s">
+      <c r="C166" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D166" s="21" t="s">
+      <c r="D166" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E166" s="21" t="s">
+      <c r="E166" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="167" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="76"/>
-      <c r="C167" s="76"/>
-      <c r="D167" s="21" t="s">
+      <c r="B167" s="61"/>
+      <c r="C167" s="61"/>
+      <c r="D167" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E167" s="21" t="s">
+      <c r="E167" s="13" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="168" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="76"/>
-      <c r="C168" s="76"/>
-      <c r="D168" s="21" t="s">
+      <c r="B168" s="61"/>
+      <c r="C168" s="61"/>
+      <c r="D168" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E168" s="21" t="s">
+      <c r="E168" s="13" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="169" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="76"/>
-      <c r="C169" s="76"/>
-      <c r="D169" s="21" t="s">
+      <c r="B169" s="61"/>
+      <c r="C169" s="61"/>
+      <c r="D169" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E169" s="21" t="s">
+      <c r="E169" s="13" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="170" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="76"/>
-      <c r="C170" s="76"/>
-      <c r="D170" s="21" t="s">
+      <c r="B170" s="61"/>
+      <c r="C170" s="61"/>
+      <c r="D170" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E170" s="21" t="s">
+      <c r="E170" s="13" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="171" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="76"/>
-      <c r="C171" s="76"/>
-      <c r="D171" s="21" t="s">
+      <c r="B171" s="61"/>
+      <c r="C171" s="61"/>
+      <c r="D171" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E171" s="21" t="s">
+      <c r="E171" s="13" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="172" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="76"/>
-      <c r="C172" s="76"/>
-      <c r="D172" s="21" t="s">
+      <c r="B172" s="61"/>
+      <c r="C172" s="61"/>
+      <c r="D172" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E172" s="21" t="s">
+      <c r="E172" s="13" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="173" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="76"/>
-      <c r="C173" s="76"/>
-      <c r="D173" s="21" t="s">
+      <c r="B173" s="61"/>
+      <c r="C173" s="61"/>
+      <c r="D173" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E173" s="21" t="s">
+      <c r="E173" s="13" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="174" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="76"/>
-      <c r="C174" s="76"/>
-      <c r="D174" s="21" t="s">
+      <c r="B174" s="61"/>
+      <c r="C174" s="61"/>
+      <c r="D174" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E174" s="21" t="s">
+      <c r="E174" s="13" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="175" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="76"/>
-      <c r="C175" s="76"/>
-      <c r="D175" s="21" t="s">
+      <c r="B175" s="61"/>
+      <c r="C175" s="61"/>
+      <c r="D175" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E175" s="21" t="s">
+      <c r="E175" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="176" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="77"/>
-      <c r="C176" s="77"/>
-      <c r="D176" s="21" t="s">
+      <c r="B176" s="62"/>
+      <c r="C176" s="62"/>
+      <c r="D176" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E176" s="21" t="s">
+      <c r="E176" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="177" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="79" t="s">
+      <c r="B177" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C177" s="80" t="s">
+      <c r="C177" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="D177" s="22" t="s">
+      <c r="D177" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E177" s="22" t="s">
+      <c r="E177" s="14" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="76"/>
-      <c r="C178" s="76"/>
-      <c r="D178" s="22" t="s">
+      <c r="B178" s="61"/>
+      <c r="C178" s="61"/>
+      <c r="D178" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E178" s="22" t="s">
+      <c r="E178" s="14" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="179" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="76"/>
-      <c r="C179" s="76"/>
-      <c r="D179" s="22" t="s">
+      <c r="B179" s="61"/>
+      <c r="C179" s="61"/>
+      <c r="D179" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E179" s="22" t="s">
+      <c r="E179" s="14" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="180" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="76"/>
-      <c r="C180" s="76"/>
-      <c r="D180" s="22" t="s">
+      <c r="B180" s="61"/>
+      <c r="C180" s="61"/>
+      <c r="D180" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E180" s="22" t="s">
+      <c r="E180" s="14" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="181" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="76"/>
-      <c r="C181" s="76"/>
-      <c r="D181" s="22" t="s">
+      <c r="B181" s="61"/>
+      <c r="C181" s="61"/>
+      <c r="D181" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="E181" s="22" t="s">
+      <c r="E181" s="14" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="76"/>
-      <c r="C182" s="76"/>
-      <c r="D182" s="22" t="s">
+      <c r="B182" s="61"/>
+      <c r="C182" s="61"/>
+      <c r="D182" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E182" s="22" t="s">
+      <c r="E182" s="14" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="183" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="76"/>
-      <c r="C183" s="76"/>
-      <c r="D183" s="22" t="s">
+      <c r="B183" s="61"/>
+      <c r="C183" s="61"/>
+      <c r="D183" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E183" s="22" t="s">
+      <c r="E183" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="76"/>
-      <c r="C184" s="76"/>
-      <c r="D184" s="22" t="s">
+      <c r="B184" s="61"/>
+      <c r="C184" s="61"/>
+      <c r="D184" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E184" s="22" t="s">
+      <c r="E184" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="185" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="76"/>
-      <c r="C185" s="76"/>
-      <c r="D185" s="22" t="s">
+      <c r="B185" s="61"/>
+      <c r="C185" s="61"/>
+      <c r="D185" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E185" s="22" t="s">
+      <c r="E185" s="14" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="186" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="77"/>
-      <c r="C186" s="77"/>
-      <c r="D186" s="22" t="s">
+      <c r="B186" s="62"/>
+      <c r="C186" s="62"/>
+      <c r="D186" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E186" s="22" t="s">
+      <c r="E186" s="14" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="187" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="81" t="s">
+      <c r="B187" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C187" s="82" t="s">
+      <c r="C187" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D187" s="23" t="s">
+      <c r="D187" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E187" s="23" t="s">
+      <c r="E187" s="15" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="188" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="76"/>
-      <c r="C188" s="76"/>
-      <c r="D188" s="23" t="s">
+      <c r="B188" s="61"/>
+      <c r="C188" s="61"/>
+      <c r="D188" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E188" s="23" t="s">
+      <c r="E188" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="189" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="76"/>
-      <c r="C189" s="76"/>
-      <c r="D189" s="23" t="s">
+      <c r="B189" s="61"/>
+      <c r="C189" s="61"/>
+      <c r="D189" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="E189" s="23" t="s">
+      <c r="E189" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="76"/>
-      <c r="C190" s="76"/>
-      <c r="D190" s="23" t="s">
+      <c r="B190" s="61"/>
+      <c r="C190" s="61"/>
+      <c r="D190" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E190" s="23" t="s">
+      <c r="E190" s="15" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="191" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="76"/>
-      <c r="C191" s="76"/>
-      <c r="D191" s="23" t="s">
+      <c r="B191" s="61"/>
+      <c r="C191" s="61"/>
+      <c r="D191" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="E191" s="23" t="s">
+      <c r="E191" s="15" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="192" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="76"/>
-      <c r="C192" s="76"/>
-      <c r="D192" s="23" t="s">
+      <c r="B192" s="61"/>
+      <c r="C192" s="61"/>
+      <c r="D192" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E192" s="23" t="s">
+      <c r="E192" s="15" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="193" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="76"/>
-      <c r="C193" s="76"/>
-      <c r="D193" s="23" t="s">
+      <c r="B193" s="61"/>
+      <c r="C193" s="61"/>
+      <c r="D193" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="E193" s="23" t="s">
+      <c r="E193" s="15" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="194" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="76"/>
-      <c r="C194" s="76"/>
-      <c r="D194" s="23" t="s">
+      <c r="B194" s="61"/>
+      <c r="C194" s="61"/>
+      <c r="D194" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="E194" s="23" t="s">
+      <c r="E194" s="15" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="195" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="76"/>
-      <c r="C195" s="76"/>
-      <c r="D195" s="23" t="s">
+      <c r="B195" s="61"/>
+      <c r="C195" s="61"/>
+      <c r="D195" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="E195" s="23" t="s">
+      <c r="E195" s="15" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="196" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="77"/>
-      <c r="C196" s="77"/>
-      <c r="D196" s="23" t="s">
+      <c r="B196" s="62"/>
+      <c r="C196" s="62"/>
+      <c r="D196" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="E196" s="23" t="s">
+      <c r="E196" s="15" t="s">
         <v>195</v>
       </c>
     </row>
@@ -6979,6 +6888,22 @@
     <row r="1071" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B142:B165"/>
     <mergeCell ref="B166:B176"/>
     <mergeCell ref="B177:B186"/>
     <mergeCell ref="B25:B29"/>
@@ -6992,22 +6917,6 @@
     <mergeCell ref="B121:B141"/>
     <mergeCell ref="C121:C141"/>
     <mergeCell ref="C142:C165"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B142:B165"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/utilities/Analisis_pestel_Mabel.xlsx
+++ b/utilities/Analisis_pestel_Mabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64998743-2016-411E-8566-E1B395343E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B2B735-B884-47F1-BD88-E22916129064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="279">
   <si>
     <t>IMPACTO</t>
   </si>
@@ -922,6 +922,9 @@
   </si>
   <si>
     <t>Impuestos o permisos municipales para negocios de comida.</t>
+  </si>
+  <si>
+    <t>Transferencia tecnológica en fase de maduración y enfocada en crear productos que se pueden vender desde la web.</t>
   </si>
 </sst>
 </file>
@@ -1402,7 +1405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1493,8 +1496,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -1511,6 +1512,87 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1558,24 +1640,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1611,87 +1675,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1932,10 +1943,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="88" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -1946,8 +1957,8 @@
       </c>
     </row>
     <row r="2" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
       <c r="D2" s="37" t="s">
         <v>15</v>
       </c>
@@ -1956,8 +1967,8 @@
       </c>
     </row>
     <row r="3" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
@@ -1966,8 +1977,8 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
@@ -1976,8 +1987,8 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
       <c r="D5" s="9" t="s">
         <v>55</v>
       </c>
@@ -1986,8 +1997,8 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="37" t="s">
         <v>57</v>
       </c>
@@ -1996,8 +2007,8 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="86"/>
       <c r="D7" s="9" t="s">
         <v>58</v>
       </c>
@@ -2006,8 +2017,8 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="9" t="s">
         <v>60</v>
       </c>
@@ -2016,8 +2027,8 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="9" t="s">
         <v>62</v>
       </c>
@@ -2026,8 +2037,8 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="9" t="s">
         <v>64</v>
       </c>
@@ -2036,8 +2047,8 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="37" t="s">
         <v>65</v>
       </c>
@@ -2046,8 +2057,8 @@
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="37" t="s">
         <v>67</v>
       </c>
@@ -2056,8 +2067,8 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="9" t="s">
         <v>69</v>
       </c>
@@ -2066,8 +2077,8 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="9" t="s">
         <v>71</v>
       </c>
@@ -2076,8 +2087,8 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="9" t="s">
         <v>73</v>
       </c>
@@ -2086,10 +2097,10 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="94" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -2101,8 +2112,8 @@
       <c r="H16" s="11"/>
     </row>
     <row r="17" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="86"/>
+      <c r="C17" s="86"/>
       <c r="D17" s="39" t="s">
         <v>24</v>
       </c>
@@ -2111,8 +2122,8 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="10" t="s">
         <v>25</v>
       </c>
@@ -2121,8 +2132,8 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="39" t="s">
         <v>26</v>
       </c>
@@ -2131,8 +2142,8 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="39" t="s">
         <v>79</v>
       </c>
@@ -2141,8 +2152,8 @@
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="10" t="s">
         <v>27</v>
       </c>
@@ -2151,8 +2162,8 @@
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="10" t="s">
         <v>82</v>
       </c>
@@ -2161,8 +2172,8 @@
       </c>
     </row>
     <row r="23" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
       <c r="D23" s="10" t="s">
         <v>84</v>
       </c>
@@ -2171,8 +2182,8 @@
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="10" t="s">
         <v>86</v>
       </c>
@@ -2181,8 +2192,8 @@
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
       <c r="D25" s="39" t="s">
         <v>88</v>
       </c>
@@ -2191,8 +2202,8 @@
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="61"/>
-      <c r="C26" s="61"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
       <c r="D26" s="10" t="s">
         <v>90</v>
       </c>
@@ -2201,8 +2212,8 @@
       </c>
     </row>
     <row r="27" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
       <c r="D27" s="10" t="s">
         <v>92</v>
       </c>
@@ -2211,8 +2222,8 @@
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
       <c r="D28" s="10" t="s">
         <v>94</v>
       </c>
@@ -2221,8 +2232,8 @@
       </c>
     </row>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
       <c r="D29" s="10" t="s">
         <v>96</v>
       </c>
@@ -2231,8 +2242,8 @@
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="10" t="s">
         <v>98</v>
       </c>
@@ -2241,8 +2252,8 @@
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="86"/>
       <c r="D31" s="10" t="s">
         <v>100</v>
       </c>
@@ -2251,8 +2262,8 @@
       </c>
     </row>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="10" t="s">
         <v>102</v>
       </c>
@@ -2261,8 +2272,8 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
       <c r="D33" s="10" t="s">
         <v>104</v>
       </c>
@@ -2271,8 +2282,8 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
       <c r="D34" s="10" t="s">
         <v>106</v>
       </c>
@@ -2281,8 +2292,8 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="61"/>
-      <c r="C35" s="61"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
       <c r="D35" s="10" t="s">
         <v>108</v>
       </c>
@@ -2291,8 +2302,8 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="62"/>
-      <c r="C36" s="62"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="10" t="s">
         <v>110</v>
       </c>
@@ -2301,10 +2312,10 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="71" t="s">
+      <c r="C37" s="96" t="s">
         <v>29</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2316,8 +2327,8 @@
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
       <c r="D38" s="12" t="s">
         <v>31</v>
       </c>
@@ -2326,8 +2337,8 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="86"/>
       <c r="D39" s="12" t="s">
         <v>32</v>
       </c>
@@ -2336,8 +2347,8 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
       <c r="D40" s="12" t="s">
         <v>33</v>
       </c>
@@ -2346,8 +2357,8 @@
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
       <c r="D41" s="12" t="s">
         <v>35</v>
       </c>
@@ -2356,8 +2367,8 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
       <c r="D42" s="41" t="s">
         <v>36</v>
       </c>
@@ -2366,8 +2377,8 @@
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
+      <c r="B43" s="86"/>
+      <c r="C43" s="86"/>
       <c r="D43" s="12" t="s">
         <v>37</v>
       </c>
@@ -2376,8 +2387,8 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="86"/>
       <c r="D44" s="12" t="s">
         <v>38</v>
       </c>
@@ -2386,8 +2397,8 @@
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
+      <c r="B45" s="86"/>
+      <c r="C45" s="86"/>
       <c r="D45" s="12" t="s">
         <v>118</v>
       </c>
@@ -2396,8 +2407,8 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="61"/>
-      <c r="C46" s="61"/>
+      <c r="B46" s="86"/>
+      <c r="C46" s="86"/>
       <c r="D46" s="12" t="s">
         <v>120</v>
       </c>
@@ -2406,8 +2417,8 @@
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
       <c r="D47" s="41" t="s">
         <v>122</v>
       </c>
@@ -2416,8 +2427,8 @@
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
       <c r="D48" s="41" t="s">
         <v>124</v>
       </c>
@@ -2426,8 +2437,8 @@
       </c>
     </row>
     <row r="49" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="86"/>
       <c r="D49" s="12" t="s">
         <v>126</v>
       </c>
@@ -2436,8 +2447,8 @@
       </c>
     </row>
     <row r="50" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
       <c r="D50" s="12" t="s">
         <v>128</v>
       </c>
@@ -2446,8 +2457,8 @@
       </c>
     </row>
     <row r="51" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
+      <c r="B51" s="86"/>
+      <c r="C51" s="86"/>
       <c r="D51" s="12" t="s">
         <v>130</v>
       </c>
@@ -2456,8 +2467,8 @@
       </c>
     </row>
     <row r="52" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
+      <c r="B52" s="86"/>
+      <c r="C52" s="86"/>
       <c r="D52" s="12" t="s">
         <v>132</v>
       </c>
@@ -2466,8 +2477,8 @@
       </c>
     </row>
     <row r="53" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
       <c r="D53" s="12" t="s">
         <v>134</v>
       </c>
@@ -2476,8 +2487,8 @@
       </c>
     </row>
     <row r="54" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="61"/>
-      <c r="C54" s="61"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="86"/>
       <c r="D54" s="12" t="s">
         <v>136</v>
       </c>
@@ -2486,8 +2497,8 @@
       </c>
     </row>
     <row r="55" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
+      <c r="B55" s="86"/>
+      <c r="C55" s="86"/>
       <c r="D55" s="12" t="s">
         <v>138</v>
       </c>
@@ -2496,8 +2507,8 @@
       </c>
     </row>
     <row r="56" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
+      <c r="B56" s="86"/>
+      <c r="C56" s="86"/>
       <c r="D56" s="12" t="s">
         <v>140</v>
       </c>
@@ -2506,8 +2517,8 @@
       </c>
     </row>
     <row r="57" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
+      <c r="B57" s="86"/>
+      <c r="C57" s="86"/>
       <c r="D57" s="41" t="s">
         <v>142</v>
       </c>
@@ -2516,8 +2527,8 @@
       </c>
     </row>
     <row r="58" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
       <c r="D58" s="12" t="s">
         <v>144</v>
       </c>
@@ -2526,8 +2537,8 @@
       </c>
     </row>
     <row r="59" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
+      <c r="B59" s="86"/>
+      <c r="C59" s="86"/>
       <c r="D59" s="12" t="s">
         <v>146</v>
       </c>
@@ -2536,8 +2547,8 @@
       </c>
     </row>
     <row r="60" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="62"/>
-      <c r="C60" s="62"/>
+      <c r="B60" s="87"/>
+      <c r="C60" s="87"/>
       <c r="D60" s="12" t="s">
         <v>148</v>
       </c>
@@ -2546,10 +2557,10 @@
       </c>
     </row>
     <row r="61" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="72" t="s">
+      <c r="B61" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="73" t="s">
+      <c r="C61" s="98" t="s">
         <v>40</v>
       </c>
       <c r="D61" s="42" t="s">
@@ -2560,8 +2571,8 @@
       </c>
     </row>
     <row r="62" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="86"/>
       <c r="D62" s="13" t="s">
         <v>42</v>
       </c>
@@ -2570,8 +2581,8 @@
       </c>
     </row>
     <row r="63" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="61"/>
-      <c r="C63" s="61"/>
+      <c r="B63" s="86"/>
+      <c r="C63" s="86"/>
       <c r="D63" s="42" t="s">
         <v>43</v>
       </c>
@@ -2580,8 +2591,8 @@
       </c>
     </row>
     <row r="64" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="61"/>
-      <c r="C64" s="61"/>
+      <c r="B64" s="86"/>
+      <c r="C64" s="86"/>
       <c r="D64" s="42" t="s">
         <v>44</v>
       </c>
@@ -2590,8 +2601,8 @@
       </c>
     </row>
     <row r="65" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="61"/>
-      <c r="C65" s="61"/>
+      <c r="B65" s="86"/>
+      <c r="C65" s="86"/>
       <c r="D65" s="13" t="s">
         <v>41</v>
       </c>
@@ -2600,8 +2611,8 @@
       </c>
     </row>
     <row r="66" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="61"/>
-      <c r="C66" s="61"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="86"/>
       <c r="D66" s="13" t="s">
         <v>42</v>
       </c>
@@ -2610,8 +2621,8 @@
       </c>
     </row>
     <row r="67" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="61"/>
-      <c r="C67" s="61"/>
+      <c r="B67" s="86"/>
+      <c r="C67" s="86"/>
       <c r="D67" s="13" t="s">
         <v>43</v>
       </c>
@@ -2620,8 +2631,8 @@
       </c>
     </row>
     <row r="68" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="61"/>
-      <c r="C68" s="61"/>
+      <c r="B68" s="86"/>
+      <c r="C68" s="86"/>
       <c r="D68" s="13" t="s">
         <v>44</v>
       </c>
@@ -2630,8 +2641,8 @@
       </c>
     </row>
     <row r="69" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
+      <c r="B69" s="86"/>
+      <c r="C69" s="86"/>
       <c r="D69" s="13" t="s">
         <v>41</v>
       </c>
@@ -2640,8 +2651,8 @@
       </c>
     </row>
     <row r="70" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
+      <c r="B70" s="86"/>
+      <c r="C70" s="86"/>
       <c r="D70" s="13" t="s">
         <v>42</v>
       </c>
@@ -2650,8 +2661,8 @@
       </c>
     </row>
     <row r="71" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="62"/>
-      <c r="C71" s="62"/>
+      <c r="B71" s="87"/>
+      <c r="C71" s="87"/>
       <c r="D71" s="42" t="s">
         <v>43</v>
       </c>
@@ -2660,10 +2671,10 @@
       </c>
     </row>
     <row r="72" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="64" t="s">
+      <c r="B72" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="65" t="s">
+      <c r="C72" s="90" t="s">
         <v>46</v>
       </c>
       <c r="D72" s="43" t="s">
@@ -2674,8 +2685,8 @@
       </c>
     </row>
     <row r="73" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="61"/>
-      <c r="C73" s="61"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="86"/>
       <c r="D73" s="14" t="s">
         <v>162</v>
       </c>
@@ -2684,8 +2695,8 @@
       </c>
     </row>
     <row r="74" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
+      <c r="B74" s="86"/>
+      <c r="C74" s="86"/>
       <c r="D74" s="14" t="s">
         <v>164</v>
       </c>
@@ -2694,8 +2705,8 @@
       </c>
     </row>
     <row r="75" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
+      <c r="B75" s="86"/>
+      <c r="C75" s="86"/>
       <c r="D75" s="43" t="s">
         <v>166</v>
       </c>
@@ -2704,8 +2715,8 @@
       </c>
     </row>
     <row r="76" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="86"/>
       <c r="D76" s="43" t="s">
         <v>168</v>
       </c>
@@ -2714,8 +2725,8 @@
       </c>
     </row>
     <row r="77" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="61"/>
-      <c r="C77" s="61"/>
+      <c r="B77" s="86"/>
+      <c r="C77" s="86"/>
       <c r="D77" s="14" t="s">
         <v>170</v>
       </c>
@@ -2724,8 +2735,8 @@
       </c>
     </row>
     <row r="78" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
+      <c r="B78" s="86"/>
+      <c r="C78" s="86"/>
       <c r="D78" s="43" t="s">
         <v>172</v>
       </c>
@@ -2734,8 +2745,8 @@
       </c>
     </row>
     <row r="79" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
+      <c r="B79" s="86"/>
+      <c r="C79" s="86"/>
       <c r="D79" s="14" t="s">
         <v>174</v>
       </c>
@@ -2744,8 +2755,8 @@
       </c>
     </row>
     <row r="80" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
+      <c r="B80" s="86"/>
+      <c r="C80" s="86"/>
       <c r="D80" s="14" t="s">
         <v>175</v>
       </c>
@@ -2754,8 +2765,8 @@
       </c>
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="62"/>
-      <c r="C81" s="62"/>
+      <c r="B81" s="87"/>
+      <c r="C81" s="87"/>
       <c r="D81" s="14" t="s">
         <v>177</v>
       </c>
@@ -2764,10 +2775,10 @@
       </c>
     </row>
     <row r="82" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="66" t="s">
+      <c r="B82" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="67" t="s">
+      <c r="C82" s="92" t="s">
         <v>49</v>
       </c>
       <c r="D82" s="15" t="s">
@@ -2778,8 +2789,8 @@
       </c>
     </row>
     <row r="83" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
+      <c r="B83" s="86"/>
+      <c r="C83" s="86"/>
       <c r="D83" s="15" t="s">
         <v>52</v>
       </c>
@@ -2788,8 +2799,8 @@
       </c>
     </row>
     <row r="84" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="86"/>
       <c r="D84" s="15" t="s">
         <v>181</v>
       </c>
@@ -2798,8 +2809,8 @@
       </c>
     </row>
     <row r="85" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="86"/>
       <c r="D85" s="44" t="s">
         <v>182</v>
       </c>
@@ -2808,8 +2819,8 @@
       </c>
     </row>
     <row r="86" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
+      <c r="B86" s="86"/>
+      <c r="C86" s="86"/>
       <c r="D86" s="15" t="s">
         <v>184</v>
       </c>
@@ -2818,8 +2829,8 @@
       </c>
     </row>
     <row r="87" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
+      <c r="B87" s="86"/>
+      <c r="C87" s="86"/>
       <c r="D87" s="15" t="s">
         <v>186</v>
       </c>
@@ -2828,8 +2839,8 @@
       </c>
     </row>
     <row r="88" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
+      <c r="B88" s="86"/>
+      <c r="C88" s="86"/>
       <c r="D88" s="44" t="s">
         <v>188</v>
       </c>
@@ -2838,8 +2849,8 @@
       </c>
     </row>
     <row r="89" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
+      <c r="B89" s="86"/>
+      <c r="C89" s="86"/>
       <c r="D89" s="44" t="s">
         <v>190</v>
       </c>
@@ -2848,8 +2859,8 @@
       </c>
     </row>
     <row r="90" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="61"/>
-      <c r="C90" s="61"/>
+      <c r="B90" s="86"/>
+      <c r="C90" s="86"/>
       <c r="D90" s="15" t="s">
         <v>192</v>
       </c>
@@ -2858,8 +2869,8 @@
       </c>
     </row>
     <row r="91" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="62"/>
-      <c r="C91" s="62"/>
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
       <c r="D91" s="44" t="s">
         <v>194</v>
       </c>
@@ -3796,7 +3807,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="99" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -3816,7 +3827,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
+      <c r="A3" s="100"/>
       <c r="B3" s="17" t="s">
         <v>57</v>
       </c>
@@ -3834,7 +3845,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
+      <c r="A4" s="100"/>
       <c r="B4" s="17" t="s">
         <v>65</v>
       </c>
@@ -3851,8 +3862,8 @@
         <v>243</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
+    <row r="5" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="100"/>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
@@ -3865,20 +3876,20 @@
       <c r="E5" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="121" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="16"/>
       <c r="E6" s="17"/>
       <c r="F6" s="36"/>
     </row>
-    <row r="7" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="74" t="s">
+    <row r="7" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="99" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="17" t="s">
@@ -3893,12 +3904,12 @@
       <c r="E7" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="121" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
+    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="100"/>
       <c r="B8" s="17" t="s">
         <v>26</v>
       </c>
@@ -3911,12 +3922,12 @@
       <c r="E8" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="122" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
+    <row r="9" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="100"/>
       <c r="B9" s="17" t="s">
         <v>79</v>
       </c>
@@ -3929,12 +3940,12 @@
       <c r="E9" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="121" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
+    <row r="10" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="101"/>
       <c r="B10" s="17" t="s">
         <v>88</v>
       </c>
@@ -3947,12 +3958,12 @@
       <c r="E10" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="122" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="74" t="s">
+    <row r="11" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="99" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="17" t="s">
@@ -3961,18 +3972,18 @@
       <c r="C11" s="40" t="s">
         <v>251</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="122" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
+    <row r="12" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="100"/>
       <c r="B12" s="17" t="s">
         <v>122</v>
       </c>
@@ -3985,12 +3996,12 @@
       <c r="E12" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="121" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
+    <row r="13" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="100"/>
       <c r="B13" s="17" t="s">
         <v>124</v>
       </c>
@@ -4003,12 +4014,12 @@
       <c r="E13" t="s">
         <v>216</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="121" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
+    <row r="14" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="100"/>
       <c r="B14" s="17" t="s">
         <v>142</v>
       </c>
@@ -4021,19 +4032,19 @@
       <c r="E14" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="123" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="76"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="16"/>
-      <c r="F15" s="36"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="74" t="s">
+      <c r="F15" s="123"/>
+    </row>
+    <row r="16" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="99" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="17" t="s">
@@ -4048,12 +4059,12 @@
       <c r="E16" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="122" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
+    <row r="17" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="100"/>
       <c r="B17" s="17" t="s">
         <v>43</v>
       </c>
@@ -4066,12 +4077,12 @@
       <c r="E17" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="121" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
+    <row r="18" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="100"/>
       <c r="B18" s="17" t="s">
         <v>44</v>
       </c>
@@ -4084,12 +4095,12 @@
       <c r="E18" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="121" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="76"/>
+    <row r="19" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="101"/>
       <c r="B19" s="17" t="s">
         <v>276</v>
       </c>
@@ -4102,12 +4113,12 @@
       <c r="E19" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="121" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="99" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="17" t="s">
@@ -4122,12 +4133,12 @@
       <c r="E20" t="s">
         <v>230</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="122" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="17" t="s">
         <v>26</v>
       </c>
@@ -4140,12 +4151,12 @@
       <c r="E21" t="s">
         <v>228</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="122" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
+      <c r="A22" s="100"/>
       <c r="B22" s="17" t="s">
         <v>79</v>
       </c>
@@ -4158,12 +4169,12 @@
       <c r="E22" t="s">
         <v>232</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="122" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
+      <c r="A23" s="100"/>
       <c r="B23" s="17" t="s">
         <v>82</v>
       </c>
@@ -4176,20 +4187,20 @@
       <c r="E23" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="121" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
+      <c r="A24" s="100"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
       <c r="D24" s="29"/>
       <c r="E24" s="31"/>
-      <c r="F24" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="74" t="s">
+      <c r="F24" s="123"/>
+    </row>
+    <row r="25" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="99" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="17" t="s">
@@ -4204,12 +4215,12 @@
       <c r="E25" t="s">
         <v>234</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="122" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
+    <row r="26" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="100"/>
       <c r="B26" s="17" t="s">
         <v>188</v>
       </c>
@@ -4222,12 +4233,12 @@
       <c r="E26" t="s">
         <v>236</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="122" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
+    <row r="27" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="100"/>
       <c r="B27" s="17" t="s">
         <v>190</v>
       </c>
@@ -4240,12 +4251,12 @@
       <c r="E27" t="s">
         <v>238</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="122" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="76"/>
+    <row r="28" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="101"/>
       <c r="B28" s="17" t="s">
         <v>194</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="E28" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="F28" s="46" t="s">
+      <c r="F28" s="121" t="s">
         <v>275</v>
       </c>
     </row>
@@ -4318,17 +4329,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F2" s="1" t="s">
@@ -4337,21 +4348,21 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="88" t="s">
+      <c r="H2" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="91" t="s">
+      <c r="J2" s="110" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="93"/>
+      <c r="C3" s="112"/>
       <c r="D3" s="24" t="s">
         <v>6</v>
       </c>
@@ -4364,15 +4375,15 @@
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C4" s="114" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -4381,98 +4392,98 @@
       <c r="E4" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F4" s="104">
+      <c r="F4" s="66">
         <v>2</v>
       </c>
-      <c r="G4" s="105">
+      <c r="G4" s="67">
         <v>3</v>
       </c>
-      <c r="H4" s="106">
+      <c r="H4" s="68">
         <f t="shared" ref="H4:H28" si="0">F4*G4</f>
         <v>6</v>
       </c>
-      <c r="I4" s="106" t="s">
+      <c r="I4" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="106"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
       <c r="D5" s="25" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="104">
+      <c r="F5" s="66">
         <v>3</v>
       </c>
-      <c r="G5" s="107">
+      <c r="G5" s="69">
         <v>3</v>
       </c>
-      <c r="H5" s="106">
+      <c r="H5" s="68">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I5" s="108"/>
-      <c r="J5" s="96" t="s">
+      <c r="I5" s="70"/>
+      <c r="J5" s="58" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="112"/>
       <c r="D6" s="25" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="F6" s="104">
+      <c r="F6" s="66">
         <v>3</v>
       </c>
-      <c r="G6" s="107">
+      <c r="G6" s="69">
         <v>3</v>
       </c>
-      <c r="H6" s="106">
+      <c r="H6" s="68">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="112"/>
       <c r="D7" s="25" t="s">
         <v>67</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="104">
+      <c r="F7" s="66">
         <v>3</v>
       </c>
-      <c r="G7" s="107">
+      <c r="G7" s="69">
         <v>2</v>
       </c>
-      <c r="H7" s="106">
+      <c r="H7" s="68">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="108" t="s">
+      <c r="I7" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="108"/>
+      <c r="J7" s="70"/>
     </row>
     <row r="8" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="104" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="26" t="s">
@@ -4481,516 +4492,507 @@
       <c r="E8" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F8" s="109">
+      <c r="F8" s="71">
         <v>2</v>
       </c>
-      <c r="G8" s="109">
+      <c r="G8" s="71">
         <v>3</v>
       </c>
-      <c r="H8" s="110">
+      <c r="H8" s="72">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110" t="s">
+      <c r="I8" s="72"/>
+      <c r="J8" s="72" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="84"/>
-      <c r="C9" s="85"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="104"/>
       <c r="D9" s="26" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="109">
+      <c r="F9" s="71">
         <v>3</v>
       </c>
-      <c r="G9" s="109">
+      <c r="G9" s="71">
         <v>2</v>
       </c>
-      <c r="H9" s="110">
+      <c r="H9" s="72">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110" t="s">
+      <c r="I9" s="72"/>
+      <c r="J9" s="72" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="84"/>
-      <c r="C10" s="85"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="104"/>
       <c r="D10" s="26" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="F10" s="109">
+      <c r="F10" s="71">
         <v>2</v>
       </c>
-      <c r="G10" s="109">
+      <c r="G10" s="71">
         <v>3</v>
       </c>
-      <c r="H10" s="110">
+      <c r="H10" s="72">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I10" s="111" t="s">
+      <c r="I10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="110"/>
+      <c r="J10" s="72"/>
     </row>
     <row r="11" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="84"/>
-      <c r="C11" s="85"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="104"/>
       <c r="D11" s="26" t="s">
         <v>88</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="109">
+      <c r="F11" s="71">
         <v>3</v>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="71">
         <v>2</v>
       </c>
-      <c r="H11" s="110">
+      <c r="H11" s="72">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110" t="s">
+      <c r="I11" s="72"/>
+      <c r="J11" s="72" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="F12" s="112">
+      <c r="F12" s="74">
         <v>3</v>
       </c>
-      <c r="G12" s="112">
+      <c r="G12" s="74">
         <v>3</v>
       </c>
-      <c r="H12" s="113">
+      <c r="H12" s="75">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I12" s="113" t="s">
+      <c r="I12" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="113"/>
+      <c r="J12" s="75"/>
     </row>
     <row r="13" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
       <c r="D13" s="27" t="s">
         <v>122</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="F13" s="114">
+      <c r="F13" s="76">
         <v>3</v>
       </c>
-      <c r="G13" s="114">
+      <c r="G13" s="76">
         <v>2</v>
       </c>
-      <c r="H13" s="115">
+      <c r="H13" s="77">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="115" t="s">
+      <c r="I13" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="115"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="86"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="106"/>
       <c r="D14" s="27" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="F14" s="114">
+      <c r="F14" s="76">
         <v>2</v>
       </c>
-      <c r="G14" s="114">
+      <c r="G14" s="76">
         <v>3</v>
       </c>
-      <c r="H14" s="115">
+      <c r="H14" s="77">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I14" s="115" t="s">
+      <c r="I14" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="J14" s="116"/>
+      <c r="J14" s="78"/>
     </row>
     <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="86"/>
-      <c r="C15" s="87"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
       <c r="D15" s="27" t="s">
         <v>142</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F15" s="114">
+      <c r="F15" s="76">
         <v>3</v>
       </c>
-      <c r="G15" s="114">
+      <c r="G15" s="76">
         <v>3</v>
       </c>
-      <c r="H15" s="115">
+      <c r="H15" s="77">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115" t="s">
+      <c r="I15" s="77" t="s">
         <v>14</v>
       </c>
+      <c r="J15" s="77"/>
     </row>
     <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="86"/>
-      <c r="C16" s="87"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
       <c r="D16" s="27"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="114">
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+    </row>
+    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="118" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="F17" s="79">
         <v>3</v>
       </c>
-      <c r="G16" s="114">
+      <c r="G17" s="79">
         <v>2</v>
       </c>
-      <c r="H16" s="115">
+      <c r="H17" s="80">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I16" s="115" t="s">
+      <c r="I17" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="115"/>
-    </row>
-    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="117">
+      <c r="J17" s="80"/>
+    </row>
+    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="117"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="55" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="79">
         <v>2</v>
       </c>
-      <c r="G17" s="117">
+      <c r="G18" s="79">
         <v>2</v>
       </c>
-      <c r="H17" s="118">
+      <c r="H18" s="80">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I17" s="118" t="s">
+      <c r="I18" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="118"/>
-    </row>
-    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="81"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18" s="117">
+      <c r="J18" s="81"/>
+    </row>
+    <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="117"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="F19" s="79">
+        <v>3</v>
+      </c>
+      <c r="G19" s="79">
         <v>2</v>
       </c>
-      <c r="G18" s="117">
+      <c r="H19" s="80">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I19" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="80"/>
+    </row>
+    <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="117"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="55" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="124" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" s="79">
+        <v>3</v>
+      </c>
+      <c r="G20" s="79">
+        <v>3</v>
+      </c>
+      <c r="H20" s="80">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I20" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="80"/>
+    </row>
+    <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="115" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" s="82">
         <v>2</v>
       </c>
-      <c r="H18" s="118">
+      <c r="G21" s="82">
+        <v>2</v>
+      </c>
+      <c r="H21" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I18" s="118" t="s">
+      <c r="I21" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="119"/>
-    </row>
-    <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="81"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="F19" s="117">
+      <c r="J21" s="83"/>
+    </row>
+    <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="82">
+        <v>2</v>
+      </c>
+      <c r="G22" s="82">
+        <v>2</v>
+      </c>
+      <c r="H22" s="83">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I22" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="83"/>
+    </row>
+    <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="F23" s="82">
+        <v>2</v>
+      </c>
+      <c r="G23" s="82">
         <v>3</v>
       </c>
-      <c r="G19" s="117">
-        <v>2</v>
-      </c>
-      <c r="H19" s="118">
+      <c r="H23" s="83">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I19" s="118" t="s">
+      <c r="I23" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="J19" s="118"/>
-    </row>
-    <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="57" t="s">
-        <v>276</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>261</v>
-      </c>
-      <c r="F20" s="117">
+      <c r="J23" s="83"/>
+    </row>
+    <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="115"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" s="82">
+        <v>2</v>
+      </c>
+      <c r="G24" s="82">
+        <v>2</v>
+      </c>
+      <c r="H24" s="83">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I24" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="83"/>
+    </row>
+    <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="119" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="120" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="62">
         <v>3</v>
       </c>
-      <c r="G20" s="117">
+      <c r="G25" s="62">
         <v>3</v>
       </c>
-      <c r="H20" s="118">
+      <c r="H25" s="63">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118" t="s">
+      <c r="I25" s="63" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="54" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="F21" s="120">
+      <c r="J25" s="63"/>
+    </row>
+    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="119"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="62">
+        <v>3</v>
+      </c>
+      <c r="G26" s="62">
+        <v>3</v>
+      </c>
+      <c r="H26" s="63">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="I26" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="63"/>
+    </row>
+    <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="119"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="F27" s="64">
         <v>2</v>
       </c>
-      <c r="G21" s="120">
+      <c r="G27" s="62">
         <v>2</v>
       </c>
-      <c r="H21" s="121">
+      <c r="H27" s="63">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I21" s="121" t="s">
+      <c r="I27" s="65"/>
+      <c r="J27" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="J21" s="121"/>
-    </row>
-    <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="F22" s="120">
+    </row>
+    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="119"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="F28" s="59">
+        <v>3</v>
+      </c>
+      <c r="G28" s="60">
         <v>2</v>
       </c>
-      <c r="G22" s="120">
-        <v>2</v>
-      </c>
-      <c r="H22" s="121">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I22" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="121"/>
-    </row>
-    <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="79"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="58" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>231</v>
-      </c>
-      <c r="F23" s="120">
-        <v>2</v>
-      </c>
-      <c r="G23" s="120">
-        <v>3</v>
-      </c>
-      <c r="H23" s="121">
+      <c r="H28" s="61">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I23" s="121" t="s">
+      <c r="I28" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="121"/>
-    </row>
-    <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="79"/>
-      <c r="C24" s="80"/>
-      <c r="D24" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="56" t="s">
-        <v>267</v>
-      </c>
-      <c r="F24" s="120">
-        <v>2</v>
-      </c>
-      <c r="G24" s="120">
-        <v>2</v>
-      </c>
-      <c r="H24" s="121">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I24" s="121" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="121"/>
-    </row>
-    <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="77" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="F25" s="100">
-        <v>3</v>
-      </c>
-      <c r="G25" s="100">
-        <v>3</v>
-      </c>
-      <c r="H25" s="101">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I25" s="101" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="101"/>
-    </row>
-    <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="77"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="F26" s="100">
-        <v>3</v>
-      </c>
-      <c r="G26" s="100">
-        <v>3</v>
-      </c>
-      <c r="H26" s="101">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I26" s="101" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="101"/>
-    </row>
-    <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="77"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" s="102">
-        <v>2</v>
-      </c>
-      <c r="G27" s="100">
-        <v>2</v>
-      </c>
-      <c r="H27" s="101">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I27" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="101"/>
-    </row>
-    <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="77"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="F28" s="97">
-        <v>3</v>
-      </c>
-      <c r="G28" s="98">
-        <v>2</v>
-      </c>
-      <c r="H28" s="99">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I28" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="99"/>
+      <c r="J28" s="61"/>
     </row>
     <row r="29" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="77"/>
-      <c r="C29" s="78"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="120"/>
       <c r="D29" s="28"/>
       <c r="E29" s="21"/>
       <c r="F29" s="34"/>
@@ -5076,10 +5078,10 @@
     <row r="104" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="60" t="s">
+      <c r="B106" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="63" t="s">
+      <c r="C106" s="88" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="9" t="s">
@@ -5090,8 +5092,8 @@
       </c>
     </row>
     <row r="107" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="61"/>
-      <c r="C107" s="61"/>
+      <c r="B107" s="86"/>
+      <c r="C107" s="86"/>
       <c r="D107" s="9" t="s">
         <v>15</v>
       </c>
@@ -5100,8 +5102,8 @@
       </c>
     </row>
     <row r="108" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="61"/>
-      <c r="C108" s="61"/>
+      <c r="B108" s="86"/>
+      <c r="C108" s="86"/>
       <c r="D108" s="9" t="s">
         <v>17</v>
       </c>
@@ -5110,8 +5112,8 @@
       </c>
     </row>
     <row r="109" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="61"/>
-      <c r="C109" s="61"/>
+      <c r="B109" s="86"/>
+      <c r="C109" s="86"/>
       <c r="D109" s="9" t="s">
         <v>19</v>
       </c>
@@ -5120,8 +5122,8 @@
       </c>
     </row>
     <row r="110" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="61"/>
-      <c r="C110" s="61"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="86"/>
       <c r="D110" s="9" t="s">
         <v>55</v>
       </c>
@@ -5130,8 +5132,8 @@
       </c>
     </row>
     <row r="111" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="61"/>
-      <c r="C111" s="61"/>
+      <c r="B111" s="86"/>
+      <c r="C111" s="86"/>
       <c r="D111" s="9" t="s">
         <v>57</v>
       </c>
@@ -5140,8 +5142,8 @@
       </c>
     </row>
     <row r="112" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="61"/>
-      <c r="C112" s="61"/>
+      <c r="B112" s="86"/>
+      <c r="C112" s="86"/>
       <c r="D112" s="9" t="s">
         <v>58</v>
       </c>
@@ -5150,8 +5152,8 @@
       </c>
     </row>
     <row r="113" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="61"/>
-      <c r="C113" s="61"/>
+      <c r="B113" s="86"/>
+      <c r="C113" s="86"/>
       <c r="D113" s="9" t="s">
         <v>60</v>
       </c>
@@ -5160,8 +5162,8 @@
       </c>
     </row>
     <row r="114" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="61"/>
-      <c r="C114" s="61"/>
+      <c r="B114" s="86"/>
+      <c r="C114" s="86"/>
       <c r="D114" s="9" t="s">
         <v>62</v>
       </c>
@@ -5170,8 +5172,8 @@
       </c>
     </row>
     <row r="115" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="61"/>
-      <c r="C115" s="61"/>
+      <c r="B115" s="86"/>
+      <c r="C115" s="86"/>
       <c r="D115" s="9" t="s">
         <v>64</v>
       </c>
@@ -5180,8 +5182,8 @@
       </c>
     </row>
     <row r="116" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="61"/>
-      <c r="C116" s="61"/>
+      <c r="B116" s="86"/>
+      <c r="C116" s="86"/>
       <c r="D116" s="9" t="s">
         <v>65</v>
       </c>
@@ -5190,8 +5192,8 @@
       </c>
     </row>
     <row r="117" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="61"/>
-      <c r="C117" s="61"/>
+      <c r="B117" s="86"/>
+      <c r="C117" s="86"/>
       <c r="D117" s="9" t="s">
         <v>67</v>
       </c>
@@ -5200,8 +5202,8 @@
       </c>
     </row>
     <row r="118" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="61"/>
-      <c r="C118" s="61"/>
+      <c r="B118" s="86"/>
+      <c r="C118" s="86"/>
       <c r="D118" s="9" t="s">
         <v>69</v>
       </c>
@@ -5210,8 +5212,8 @@
       </c>
     </row>
     <row r="119" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="61"/>
-      <c r="C119" s="61"/>
+      <c r="B119" s="86"/>
+      <c r="C119" s="86"/>
       <c r="D119" s="9" t="s">
         <v>71</v>
       </c>
@@ -5220,8 +5222,8 @@
       </c>
     </row>
     <row r="120" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="62"/>
-      <c r="C120" s="62"/>
+      <c r="B120" s="87"/>
+      <c r="C120" s="87"/>
       <c r="D120" s="9" t="s">
         <v>73</v>
       </c>
@@ -5230,10 +5232,10 @@
       </c>
     </row>
     <row r="121" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="68" t="s">
+      <c r="B121" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="69" t="s">
+      <c r="C121" s="94" t="s">
         <v>22</v>
       </c>
       <c r="D121" s="10" t="s">
@@ -5245,8 +5247,8 @@
       <c r="H121" s="11"/>
     </row>
     <row r="122" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="61"/>
-      <c r="C122" s="61"/>
+      <c r="B122" s="86"/>
+      <c r="C122" s="86"/>
       <c r="D122" s="10" t="s">
         <v>24</v>
       </c>
@@ -5255,8 +5257,8 @@
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="61"/>
-      <c r="C123" s="61"/>
+      <c r="B123" s="86"/>
+      <c r="C123" s="86"/>
       <c r="D123" s="10" t="s">
         <v>25</v>
       </c>
@@ -5265,8 +5267,8 @@
       </c>
     </row>
     <row r="124" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="61"/>
-      <c r="C124" s="61"/>
+      <c r="B124" s="86"/>
+      <c r="C124" s="86"/>
       <c r="D124" s="10" t="s">
         <v>26</v>
       </c>
@@ -5275,8 +5277,8 @@
       </c>
     </row>
     <row r="125" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="61"/>
-      <c r="C125" s="61"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="86"/>
       <c r="D125" s="10" t="s">
         <v>79</v>
       </c>
@@ -5285,8 +5287,8 @@
       </c>
     </row>
     <row r="126" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="61"/>
-      <c r="C126" s="61"/>
+      <c r="B126" s="86"/>
+      <c r="C126" s="86"/>
       <c r="D126" s="10" t="s">
         <v>27</v>
       </c>
@@ -5295,8 +5297,8 @@
       </c>
     </row>
     <row r="127" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="61"/>
-      <c r="C127" s="61"/>
+      <c r="B127" s="86"/>
+      <c r="C127" s="86"/>
       <c r="D127" s="10" t="s">
         <v>82</v>
       </c>
@@ -5305,8 +5307,8 @@
       </c>
     </row>
     <row r="128" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="61"/>
-      <c r="C128" s="61"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
       <c r="D128" s="10" t="s">
         <v>84</v>
       </c>
@@ -5315,8 +5317,8 @@
       </c>
     </row>
     <row r="129" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="61"/>
-      <c r="C129" s="61"/>
+      <c r="B129" s="86"/>
+      <c r="C129" s="86"/>
       <c r="D129" s="10" t="s">
         <v>86</v>
       </c>
@@ -5325,8 +5327,8 @@
       </c>
     </row>
     <row r="130" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="61"/>
-      <c r="C130" s="61"/>
+      <c r="B130" s="86"/>
+      <c r="C130" s="86"/>
       <c r="D130" s="10" t="s">
         <v>88</v>
       </c>
@@ -5335,8 +5337,8 @@
       </c>
     </row>
     <row r="131" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="61"/>
-      <c r="C131" s="61"/>
+      <c r="B131" s="86"/>
+      <c r="C131" s="86"/>
       <c r="D131" s="10" t="s">
         <v>90</v>
       </c>
@@ -5345,8 +5347,8 @@
       </c>
     </row>
     <row r="132" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="61"/>
-      <c r="C132" s="61"/>
+      <c r="B132" s="86"/>
+      <c r="C132" s="86"/>
       <c r="D132" s="10" t="s">
         <v>92</v>
       </c>
@@ -5355,8 +5357,8 @@
       </c>
     </row>
     <row r="133" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="61"/>
-      <c r="C133" s="61"/>
+      <c r="B133" s="86"/>
+      <c r="C133" s="86"/>
       <c r="D133" s="10" t="s">
         <v>94</v>
       </c>
@@ -5365,8 +5367,8 @@
       </c>
     </row>
     <row r="134" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="61"/>
-      <c r="C134" s="61"/>
+      <c r="B134" s="86"/>
+      <c r="C134" s="86"/>
       <c r="D134" s="10" t="s">
         <v>96</v>
       </c>
@@ -5375,8 +5377,8 @@
       </c>
     </row>
     <row r="135" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="61"/>
-      <c r="C135" s="61"/>
+      <c r="B135" s="86"/>
+      <c r="C135" s="86"/>
       <c r="D135" s="10" t="s">
         <v>98</v>
       </c>
@@ -5385,8 +5387,8 @@
       </c>
     </row>
     <row r="136" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="61"/>
-      <c r="C136" s="61"/>
+      <c r="B136" s="86"/>
+      <c r="C136" s="86"/>
       <c r="D136" s="10" t="s">
         <v>100</v>
       </c>
@@ -5395,8 +5397,8 @@
       </c>
     </row>
     <row r="137" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="61"/>
-      <c r="C137" s="61"/>
+      <c r="B137" s="86"/>
+      <c r="C137" s="86"/>
       <c r="D137" s="10" t="s">
         <v>102</v>
       </c>
@@ -5405,8 +5407,8 @@
       </c>
     </row>
     <row r="138" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="61"/>
-      <c r="C138" s="61"/>
+      <c r="B138" s="86"/>
+      <c r="C138" s="86"/>
       <c r="D138" s="10" t="s">
         <v>104</v>
       </c>
@@ -5415,8 +5417,8 @@
       </c>
     </row>
     <row r="139" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="61"/>
-      <c r="C139" s="61"/>
+      <c r="B139" s="86"/>
+      <c r="C139" s="86"/>
       <c r="D139" s="10" t="s">
         <v>106</v>
       </c>
@@ -5425,8 +5427,8 @@
       </c>
     </row>
     <row r="140" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="61"/>
-      <c r="C140" s="61"/>
+      <c r="B140" s="86"/>
+      <c r="C140" s="86"/>
       <c r="D140" s="10" t="s">
         <v>108</v>
       </c>
@@ -5435,8 +5437,8 @@
       </c>
     </row>
     <row r="141" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="62"/>
-      <c r="C141" s="62"/>
+      <c r="B141" s="87"/>
+      <c r="C141" s="87"/>
       <c r="D141" s="10" t="s">
         <v>110</v>
       </c>
@@ -5445,10 +5447,10 @@
       </c>
     </row>
     <row r="142" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="70" t="s">
+      <c r="B142" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="C142" s="71" t="s">
+      <c r="C142" s="96" t="s">
         <v>29</v>
       </c>
       <c r="D142" s="12" t="s">
@@ -5460,8 +5462,8 @@
       <c r="H142" s="11"/>
     </row>
     <row r="143" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="61"/>
-      <c r="C143" s="61"/>
+      <c r="B143" s="86"/>
+      <c r="C143" s="86"/>
       <c r="D143" s="12" t="s">
         <v>31</v>
       </c>
@@ -5470,8 +5472,8 @@
       </c>
     </row>
     <row r="144" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="61"/>
-      <c r="C144" s="61"/>
+      <c r="B144" s="86"/>
+      <c r="C144" s="86"/>
       <c r="D144" s="12" t="s">
         <v>32</v>
       </c>
@@ -5480,8 +5482,8 @@
       </c>
     </row>
     <row r="145" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="61"/>
-      <c r="C145" s="61"/>
+      <c r="B145" s="86"/>
+      <c r="C145" s="86"/>
       <c r="D145" s="12" t="s">
         <v>33</v>
       </c>
@@ -5490,8 +5492,8 @@
       </c>
     </row>
     <row r="146" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="61"/>
-      <c r="C146" s="61"/>
+      <c r="B146" s="86"/>
+      <c r="C146" s="86"/>
       <c r="D146" s="12" t="s">
         <v>35</v>
       </c>
@@ -5500,8 +5502,8 @@
       </c>
     </row>
     <row r="147" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="61"/>
-      <c r="C147" s="61"/>
+      <c r="B147" s="86"/>
+      <c r="C147" s="86"/>
       <c r="D147" s="12" t="s">
         <v>36</v>
       </c>
@@ -5510,8 +5512,8 @@
       </c>
     </row>
     <row r="148" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="61"/>
-      <c r="C148" s="61"/>
+      <c r="B148" s="86"/>
+      <c r="C148" s="86"/>
       <c r="D148" s="12" t="s">
         <v>37</v>
       </c>
@@ -5520,8 +5522,8 @@
       </c>
     </row>
     <row r="149" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="61"/>
-      <c r="C149" s="61"/>
+      <c r="B149" s="86"/>
+      <c r="C149" s="86"/>
       <c r="D149" s="12" t="s">
         <v>38</v>
       </c>
@@ -5530,8 +5532,8 @@
       </c>
     </row>
     <row r="150" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="61"/>
-      <c r="C150" s="61"/>
+      <c r="B150" s="86"/>
+      <c r="C150" s="86"/>
       <c r="D150" s="12" t="s">
         <v>118</v>
       </c>
@@ -5540,8 +5542,8 @@
       </c>
     </row>
     <row r="151" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="61"/>
-      <c r="C151" s="61"/>
+      <c r="B151" s="86"/>
+      <c r="C151" s="86"/>
       <c r="D151" s="12" t="s">
         <v>120</v>
       </c>
@@ -5550,8 +5552,8 @@
       </c>
     </row>
     <row r="152" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="61"/>
-      <c r="C152" s="61"/>
+      <c r="B152" s="86"/>
+      <c r="C152" s="86"/>
       <c r="D152" s="12" t="s">
         <v>122</v>
       </c>
@@ -5560,8 +5562,8 @@
       </c>
     </row>
     <row r="153" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="61"/>
-      <c r="C153" s="61"/>
+      <c r="B153" s="86"/>
+      <c r="C153" s="86"/>
       <c r="D153" s="12" t="s">
         <v>124</v>
       </c>
@@ -5570,8 +5572,8 @@
       </c>
     </row>
     <row r="154" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="61"/>
-      <c r="C154" s="61"/>
+      <c r="B154" s="86"/>
+      <c r="C154" s="86"/>
       <c r="D154" s="12" t="s">
         <v>126</v>
       </c>
@@ -5580,8 +5582,8 @@
       </c>
     </row>
     <row r="155" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="61"/>
-      <c r="C155" s="61"/>
+      <c r="B155" s="86"/>
+      <c r="C155" s="86"/>
       <c r="D155" s="12" t="s">
         <v>128</v>
       </c>
@@ -5590,8 +5592,8 @@
       </c>
     </row>
     <row r="156" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="61"/>
-      <c r="C156" s="61"/>
+      <c r="B156" s="86"/>
+      <c r="C156" s="86"/>
       <c r="D156" s="12" t="s">
         <v>130</v>
       </c>
@@ -5600,8 +5602,8 @@
       </c>
     </row>
     <row r="157" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="61"/>
-      <c r="C157" s="61"/>
+      <c r="B157" s="86"/>
+      <c r="C157" s="86"/>
       <c r="D157" s="12" t="s">
         <v>132</v>
       </c>
@@ -5610,8 +5612,8 @@
       </c>
     </row>
     <row r="158" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="61"/>
-      <c r="C158" s="61"/>
+      <c r="B158" s="86"/>
+      <c r="C158" s="86"/>
       <c r="D158" s="12" t="s">
         <v>134</v>
       </c>
@@ -5620,8 +5622,8 @@
       </c>
     </row>
     <row r="159" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="61"/>
-      <c r="C159" s="61"/>
+      <c r="B159" s="86"/>
+      <c r="C159" s="86"/>
       <c r="D159" s="12" t="s">
         <v>136</v>
       </c>
@@ -5630,8 +5632,8 @@
       </c>
     </row>
     <row r="160" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="61"/>
-      <c r="C160" s="61"/>
+      <c r="B160" s="86"/>
+      <c r="C160" s="86"/>
       <c r="D160" s="12" t="s">
         <v>138</v>
       </c>
@@ -5640,8 +5642,8 @@
       </c>
     </row>
     <row r="161" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="61"/>
-      <c r="C161" s="61"/>
+      <c r="B161" s="86"/>
+      <c r="C161" s="86"/>
       <c r="D161" s="12" t="s">
         <v>140</v>
       </c>
@@ -5650,8 +5652,8 @@
       </c>
     </row>
     <row r="162" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="61"/>
-      <c r="C162" s="61"/>
+      <c r="B162" s="86"/>
+      <c r="C162" s="86"/>
       <c r="D162" s="12" t="s">
         <v>142</v>
       </c>
@@ -5660,8 +5662,8 @@
       </c>
     </row>
     <row r="163" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="61"/>
-      <c r="C163" s="61"/>
+      <c r="B163" s="86"/>
+      <c r="C163" s="86"/>
       <c r="D163" s="12" t="s">
         <v>144</v>
       </c>
@@ -5670,8 +5672,8 @@
       </c>
     </row>
     <row r="164" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="61"/>
-      <c r="C164" s="61"/>
+      <c r="B164" s="86"/>
+      <c r="C164" s="86"/>
       <c r="D164" s="12" t="s">
         <v>146</v>
       </c>
@@ -5680,8 +5682,8 @@
       </c>
     </row>
     <row r="165" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="62"/>
-      <c r="C165" s="62"/>
+      <c r="B165" s="87"/>
+      <c r="C165" s="87"/>
       <c r="D165" s="12" t="s">
         <v>148</v>
       </c>
@@ -5690,10 +5692,10 @@
       </c>
     </row>
     <row r="166" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="72" t="s">
+      <c r="B166" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="C166" s="73" t="s">
+      <c r="C166" s="98" t="s">
         <v>40</v>
       </c>
       <c r="D166" s="13" t="s">
@@ -5704,8 +5706,8 @@
       </c>
     </row>
     <row r="167" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="61"/>
-      <c r="C167" s="61"/>
+      <c r="B167" s="86"/>
+      <c r="C167" s="86"/>
       <c r="D167" s="13" t="s">
         <v>42</v>
       </c>
@@ -5714,8 +5716,8 @@
       </c>
     </row>
     <row r="168" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="61"/>
-      <c r="C168" s="61"/>
+      <c r="B168" s="86"/>
+      <c r="C168" s="86"/>
       <c r="D168" s="13" t="s">
         <v>43</v>
       </c>
@@ -5724,8 +5726,8 @@
       </c>
     </row>
     <row r="169" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="61"/>
-      <c r="C169" s="61"/>
+      <c r="B169" s="86"/>
+      <c r="C169" s="86"/>
       <c r="D169" s="13" t="s">
         <v>44</v>
       </c>
@@ -5734,8 +5736,8 @@
       </c>
     </row>
     <row r="170" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="61"/>
-      <c r="C170" s="61"/>
+      <c r="B170" s="86"/>
+      <c r="C170" s="86"/>
       <c r="D170" s="13" t="s">
         <v>41</v>
       </c>
@@ -5744,8 +5746,8 @@
       </c>
     </row>
     <row r="171" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="61"/>
-      <c r="C171" s="61"/>
+      <c r="B171" s="86"/>
+      <c r="C171" s="86"/>
       <c r="D171" s="13" t="s">
         <v>42</v>
       </c>
@@ -5754,8 +5756,8 @@
       </c>
     </row>
     <row r="172" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="61"/>
-      <c r="C172" s="61"/>
+      <c r="B172" s="86"/>
+      <c r="C172" s="86"/>
       <c r="D172" s="13" t="s">
         <v>43</v>
       </c>
@@ -5764,8 +5766,8 @@
       </c>
     </row>
     <row r="173" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="61"/>
-      <c r="C173" s="61"/>
+      <c r="B173" s="86"/>
+      <c r="C173" s="86"/>
       <c r="D173" s="13" t="s">
         <v>44</v>
       </c>
@@ -5774,8 +5776,8 @@
       </c>
     </row>
     <row r="174" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="61"/>
-      <c r="C174" s="61"/>
+      <c r="B174" s="86"/>
+      <c r="C174" s="86"/>
       <c r="D174" s="13" t="s">
         <v>41</v>
       </c>
@@ -5784,8 +5786,8 @@
       </c>
     </row>
     <row r="175" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="61"/>
-      <c r="C175" s="61"/>
+      <c r="B175" s="86"/>
+      <c r="C175" s="86"/>
       <c r="D175" s="13" t="s">
         <v>42</v>
       </c>
@@ -5794,8 +5796,8 @@
       </c>
     </row>
     <row r="176" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="62"/>
-      <c r="C176" s="62"/>
+      <c r="B176" s="87"/>
+      <c r="C176" s="87"/>
       <c r="D176" s="13" t="s">
         <v>43</v>
       </c>
@@ -5804,10 +5806,10 @@
       </c>
     </row>
     <row r="177" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="64" t="s">
+      <c r="B177" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C177" s="65" t="s">
+      <c r="C177" s="90" t="s">
         <v>46</v>
       </c>
       <c r="D177" s="14" t="s">
@@ -5818,8 +5820,8 @@
       </c>
     </row>
     <row r="178" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="61"/>
-      <c r="C178" s="61"/>
+      <c r="B178" s="86"/>
+      <c r="C178" s="86"/>
       <c r="D178" s="14" t="s">
         <v>162</v>
       </c>
@@ -5828,8 +5830,8 @@
       </c>
     </row>
     <row r="179" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="61"/>
-      <c r="C179" s="61"/>
+      <c r="B179" s="86"/>
+      <c r="C179" s="86"/>
       <c r="D179" s="14" t="s">
         <v>164</v>
       </c>
@@ -5838,8 +5840,8 @@
       </c>
     </row>
     <row r="180" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="61"/>
-      <c r="C180" s="61"/>
+      <c r="B180" s="86"/>
+      <c r="C180" s="86"/>
       <c r="D180" s="14" t="s">
         <v>166</v>
       </c>
@@ -5848,8 +5850,8 @@
       </c>
     </row>
     <row r="181" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="61"/>
-      <c r="C181" s="61"/>
+      <c r="B181" s="86"/>
+      <c r="C181" s="86"/>
       <c r="D181" s="14" t="s">
         <v>168</v>
       </c>
@@ -5858,8 +5860,8 @@
       </c>
     </row>
     <row r="182" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="61"/>
-      <c r="C182" s="61"/>
+      <c r="B182" s="86"/>
+      <c r="C182" s="86"/>
       <c r="D182" s="14" t="s">
         <v>170</v>
       </c>
@@ -5868,8 +5870,8 @@
       </c>
     </row>
     <row r="183" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="61"/>
-      <c r="C183" s="61"/>
+      <c r="B183" s="86"/>
+      <c r="C183" s="86"/>
       <c r="D183" s="14" t="s">
         <v>172</v>
       </c>
@@ -5878,8 +5880,8 @@
       </c>
     </row>
     <row r="184" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="61"/>
-      <c r="C184" s="61"/>
+      <c r="B184" s="86"/>
+      <c r="C184" s="86"/>
       <c r="D184" s="14" t="s">
         <v>174</v>
       </c>
@@ -5888,8 +5890,8 @@
       </c>
     </row>
     <row r="185" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="61"/>
-      <c r="C185" s="61"/>
+      <c r="B185" s="86"/>
+      <c r="C185" s="86"/>
       <c r="D185" s="14" t="s">
         <v>175</v>
       </c>
@@ -5898,8 +5900,8 @@
       </c>
     </row>
     <row r="186" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="62"/>
-      <c r="C186" s="62"/>
+      <c r="B186" s="87"/>
+      <c r="C186" s="87"/>
       <c r="D186" s="14" t="s">
         <v>177</v>
       </c>
@@ -5908,10 +5910,10 @@
       </c>
     </row>
     <row r="187" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="66" t="s">
+      <c r="B187" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C187" s="67" t="s">
+      <c r="C187" s="92" t="s">
         <v>49</v>
       </c>
       <c r="D187" s="15" t="s">
@@ -5922,8 +5924,8 @@
       </c>
     </row>
     <row r="188" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="61"/>
-      <c r="C188" s="61"/>
+      <c r="B188" s="86"/>
+      <c r="C188" s="86"/>
       <c r="D188" s="15" t="s">
         <v>52</v>
       </c>
@@ -5932,8 +5934,8 @@
       </c>
     </row>
     <row r="189" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="61"/>
-      <c r="C189" s="61"/>
+      <c r="B189" s="86"/>
+      <c r="C189" s="86"/>
       <c r="D189" s="15" t="s">
         <v>181</v>
       </c>
@@ -5942,8 +5944,8 @@
       </c>
     </row>
     <row r="190" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="61"/>
-      <c r="C190" s="61"/>
+      <c r="B190" s="86"/>
+      <c r="C190" s="86"/>
       <c r="D190" s="15" t="s">
         <v>182</v>
       </c>
@@ -5952,8 +5954,8 @@
       </c>
     </row>
     <row r="191" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="61"/>
-      <c r="C191" s="61"/>
+      <c r="B191" s="86"/>
+      <c r="C191" s="86"/>
       <c r="D191" s="15" t="s">
         <v>184</v>
       </c>
@@ -5962,8 +5964,8 @@
       </c>
     </row>
     <row r="192" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="61"/>
-      <c r="C192" s="61"/>
+      <c r="B192" s="86"/>
+      <c r="C192" s="86"/>
       <c r="D192" s="15" t="s">
         <v>186</v>
       </c>
@@ -5972,8 +5974,8 @@
       </c>
     </row>
     <row r="193" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="61"/>
-      <c r="C193" s="61"/>
+      <c r="B193" s="86"/>
+      <c r="C193" s="86"/>
       <c r="D193" s="15" t="s">
         <v>188</v>
       </c>
@@ -5982,8 +5984,8 @@
       </c>
     </row>
     <row r="194" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="61"/>
-      <c r="C194" s="61"/>
+      <c r="B194" s="86"/>
+      <c r="C194" s="86"/>
       <c r="D194" s="15" t="s">
         <v>190</v>
       </c>
@@ -5992,8 +5994,8 @@
       </c>
     </row>
     <row r="195" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="61"/>
-      <c r="C195" s="61"/>
+      <c r="B195" s="86"/>
+      <c r="C195" s="86"/>
       <c r="D195" s="15" t="s">
         <v>192</v>
       </c>
@@ -6002,8 +6004,8 @@
       </c>
     </row>
     <row r="196" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="62"/>
-      <c r="C196" s="62"/>
+      <c r="B196" s="87"/>
+      <c r="C196" s="87"/>
       <c r="D196" s="15" t="s">
         <v>194</v>
       </c>
@@ -6888,22 +6890,6 @@
     <row r="1071" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B142:B165"/>
     <mergeCell ref="B166:B176"/>
     <mergeCell ref="B177:B186"/>
     <mergeCell ref="B25:B29"/>
@@ -6917,6 +6903,22 @@
     <mergeCell ref="B121:B141"/>
     <mergeCell ref="C121:C141"/>
     <mergeCell ref="C142:C165"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B142:B165"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/utilities/Analisis_pestel_Mabel.xlsx
+++ b/utilities/Analisis_pestel_Mabel.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MaBel\utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B2B735-B884-47F1-BD88-E22916129064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB6C32-4BA3-484A-93EC-6FBA03E2C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRITERIOS" sheetId="4" r:id="rId1"/>
     <sheet name="ELEMENTOS" sheetId="3" r:id="rId2"/>
     <sheet name="PESTEL" sheetId="1" r:id="rId3"/>
+    <sheet name="PROYECTO" sheetId="6" r:id="rId4"/>
+    <sheet name="Hoja3" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,14 +35,14 @@
       <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mgb8ggKiiGqaDDxs7VbhGlVsOGbkg=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataSignature="AMtx7mgb8ggKiiGqaDDxs7VbhGlVsOGbkg=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="299">
   <si>
     <t>IMPACTO</t>
   </si>
@@ -926,12 +928,90 @@
   <si>
     <t>Transferencia tecnológica en fase de maduración y enfocada en crear productos que se pueden vender desde la web.</t>
   </si>
+  <si>
+    <t>ELEMENTOS DEL ENTORNO</t>
+  </si>
+  <si>
+    <t>ANÁLISIS DEL IMPACTO EN EL PROYECTO</t>
+  </si>
+  <si>
+    <t>Político</t>
+  </si>
+  <si>
+    <t>Las regulaciones municipales y sanitarias obligan a cumplir requisitos formales para operar, lo que puede incrementar los costos iniciales del negocio. Además, la presencia de informalidad en la venta de alimentos genera competencia en precios. Sin embargo, cumplir con las normas sanitarias puede convertirse en una ventaja al ofrecer mayor confianza y seguridad a los clientes.</t>
+  </si>
+  <si>
+    <t>Económico</t>
+  </si>
+  <si>
+    <t>Las condiciones económicas influyen directamente en la capacidad de compra de los consumidores y en los costos de producción del negocio. El incremento en el precio de insumos como pan, frutas o huevos puede afectar la rentabilidad. Sin embargo, los bajos costos laborales en microemprendimientos pueden facilitar la contratación de personal para la preparación y distribución de los desayunos.</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Las tendencias sociales favorecen el desarrollo de Easy Breakfast, ya que cada vez más personas buscan opciones de alimentación saludable y rápidas. El estilo de vida acelerado y la falta de tiempo para preparar desayunos en casa generan una demanda creciente por soluciones prácticas que puedan adquirirse fácilmente a través de internet.</t>
+  </si>
+  <si>
+    <t>Tecnológico</t>
+  </si>
+  <si>
+    <t>La tecnología facilita la promoción, comercialización y distribución de los productos. El uso de redes sociales y plataformas digitales permite promocionar Easy Breakfast a bajo costo, mientras que los sistemas de pago online y aplicaciones de delivery mejoran la experiencia del cliente y amplían el alcance del negocio.</t>
+  </si>
+  <si>
+    <t>Ecológico (Ambiental)</t>
+  </si>
+  <si>
+    <t>La creciente preocupación por el medio ambiente impulsa a los consumidores a preferir negocios responsables con el entorno. Easy Breakfast puede aprovechar esta tendencia utilizando empaques biodegradables y promoviendo prácticas sostenibles en la gestión de residuos, lo cual también mejora la imagen del emprendimiento.</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>El cumplimiento de las normativas legales permite operar de manera formal y generar confianza en los clientes. Además, la existencia de incentivos fiscales para pymes puede representar un beneficio para el crecimiento del emprendimiento, siempre que se cumplan las regulaciones sanitarias y laborales correspondientes.</t>
+  </si>
+  <si>
+    <t>Impuestos o permisos municipales para negocios de comida.
+Alta informalidad en venta de alimentos callejeros.
+Baja inversión y apoyo del Estado en desarrollo social y emprendimiento.
+Regulaciones sanitarias para manipulación de alimentos.</t>
+  </si>
+  <si>
+    <t>Bajo poder adquisitivo en algunos segmentos de la población.
+Incremento del precio de alimentos básicos.
+Bajo costo de mano de obra en microemprendimientos.
+Riesgos derivados de la crisis de seguridad nacional.</t>
+  </si>
+  <si>
+    <t>Incremento de la preferencia por comprar online.
+Mayor interés por la alimentación saludable.
+Estilo de vida acelerado de estudiantes y trabajadores.
+Poco tiempo para preparar desayuno en casa.</t>
+  </si>
+  <si>
+    <t>Desarrollo de aplicaciones de delivery.
+Uso de sistemas de pago digital.
+Uso de internet y redes sociales para promoción.
+Transferencia tecnológica enfocada en productos que pueden venderse desde la web.</t>
+  </si>
+  <si>
+    <t>Preferencia por productos sostenibles.
+Cultura creciente de reciclaje.
+Manejo adecuado de residuos de alimentos.
+Conciencia ambiental y movimientos ambientalistas.</t>
+  </si>
+  <si>
+    <t>Normas sanitarias para la venta de alimentos.
+Certificaciones de manipulación de alimentos.
+Legislación laboral para contratación de empleados.
+Deducción de Impuesto a la Renta para pymes.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1072,6 +1152,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1189,7 +1276,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1400,12 +1487,170 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1480,7 +1725,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1593,6 +1837,16 @@
     <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1640,6 +1894,24 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1675,34 +1947,59 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1943,10 +2240,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="91" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="9" t="s">
@@ -1957,18 +2254,18 @@
       </c>
     </row>
     <row r="2" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="37" t="s">
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="36" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
       <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
@@ -1977,8 +2274,8 @@
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
@@ -1987,8 +2284,8 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
       <c r="D5" s="9" t="s">
         <v>55</v>
       </c>
@@ -1997,18 +2294,18 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="37" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="36" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
       <c r="D7" s="9" t="s">
         <v>58</v>
       </c>
@@ -2017,8 +2314,8 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="9" t="s">
         <v>60</v>
       </c>
@@ -2027,8 +2324,8 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="9" t="s">
         <v>62</v>
       </c>
@@ -2037,8 +2334,8 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="9" t="s">
         <v>64</v>
       </c>
@@ -2047,28 +2344,28 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="37" t="s">
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="36" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="37" t="s">
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="36" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="89"/>
       <c r="D13" s="9" t="s">
         <v>69</v>
       </c>
@@ -2077,8 +2374,8 @@
       </c>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
       <c r="D14" s="9" t="s">
         <v>71</v>
       </c>
@@ -2087,8 +2384,8 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="87"/>
-      <c r="C15" s="87"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="9" t="s">
         <v>73</v>
       </c>
@@ -2097,10 +2394,10 @@
       </c>
     </row>
     <row r="16" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="97" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -2112,18 +2409,18 @@
       <c r="H16" s="11"/>
     </row>
     <row r="17" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="39" t="s">
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="38" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="10" t="s">
         <v>25</v>
       </c>
@@ -2132,28 +2429,28 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="39" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="38" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="39" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="38" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="10" t="s">
         <v>27</v>
       </c>
@@ -2162,8 +2459,8 @@
       </c>
     </row>
     <row r="22" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="10" t="s">
         <v>82</v>
       </c>
@@ -2172,8 +2469,8 @@
       </c>
     </row>
     <row r="23" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="10" t="s">
         <v>84</v>
       </c>
@@ -2182,8 +2479,8 @@
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="10" t="s">
         <v>86</v>
       </c>
@@ -2192,18 +2489,18 @@
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="86"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="39" t="s">
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="38" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="10" t="s">
         <v>90</v>
       </c>
@@ -2212,8 +2509,8 @@
       </c>
     </row>
     <row r="27" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="10" t="s">
         <v>92</v>
       </c>
@@ -2222,8 +2519,8 @@
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="10" t="s">
         <v>94</v>
       </c>
@@ -2232,8 +2529,8 @@
       </c>
     </row>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="10" t="s">
         <v>96</v>
       </c>
@@ -2242,8 +2539,8 @@
       </c>
     </row>
     <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
       <c r="D30" s="10" t="s">
         <v>98</v>
       </c>
@@ -2252,8 +2549,8 @@
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
       <c r="D31" s="10" t="s">
         <v>100</v>
       </c>
@@ -2262,8 +2559,8 @@
       </c>
     </row>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
       <c r="D32" s="10" t="s">
         <v>102</v>
       </c>
@@ -2272,8 +2569,8 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="10" t="s">
         <v>104</v>
       </c>
@@ -2282,8 +2579,8 @@
       </c>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="10" t="s">
         <v>106</v>
       </c>
@@ -2292,8 +2589,8 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="10" t="s">
         <v>108</v>
       </c>
@@ -2302,8 +2599,8 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="90"/>
       <c r="D36" s="10" t="s">
         <v>110</v>
       </c>
@@ -2312,10 +2609,10 @@
       </c>
     </row>
     <row r="37" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="96" t="s">
+      <c r="C37" s="99" t="s">
         <v>29</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2327,8 +2624,8 @@
       <c r="H37" s="11"/>
     </row>
     <row r="38" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
       <c r="D38" s="12" t="s">
         <v>31</v>
       </c>
@@ -2337,8 +2634,8 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
       <c r="D39" s="12" t="s">
         <v>32</v>
       </c>
@@ -2347,8 +2644,8 @@
       </c>
     </row>
     <row r="40" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
       <c r="D40" s="12" t="s">
         <v>33</v>
       </c>
@@ -2357,8 +2654,8 @@
       </c>
     </row>
     <row r="41" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
       <c r="D41" s="12" t="s">
         <v>35</v>
       </c>
@@ -2367,18 +2664,18 @@
       </c>
     </row>
     <row r="42" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="41" t="s">
+      <c r="B42" s="89"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="41" t="s">
+      <c r="E42" s="40" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="89"/>
       <c r="D43" s="12" t="s">
         <v>37</v>
       </c>
@@ -2387,8 +2684,8 @@
       </c>
     </row>
     <row r="44" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
       <c r="D44" s="12" t="s">
         <v>38</v>
       </c>
@@ -2397,8 +2694,8 @@
       </c>
     </row>
     <row r="45" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="86"/>
-      <c r="C45" s="86"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="89"/>
       <c r="D45" s="12" t="s">
         <v>118</v>
       </c>
@@ -2407,8 +2704,8 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="89"/>
       <c r="D46" s="12" t="s">
         <v>120</v>
       </c>
@@ -2417,28 +2714,28 @@
       </c>
     </row>
     <row r="47" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
-      <c r="D47" s="41" t="s">
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="E47" s="40" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="41" t="s">
+      <c r="B48" s="89"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="E48" s="41" t="s">
+      <c r="E48" s="40" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="12" t="s">
         <v>126</v>
       </c>
@@ -2447,8 +2744,8 @@
       </c>
     </row>
     <row r="50" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="89"/>
       <c r="D50" s="12" t="s">
         <v>128</v>
       </c>
@@ -2457,8 +2754,8 @@
       </c>
     </row>
     <row r="51" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="86"/>
-      <c r="C51" s="86"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="89"/>
       <c r="D51" s="12" t="s">
         <v>130</v>
       </c>
@@ -2467,8 +2764,8 @@
       </c>
     </row>
     <row r="52" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="86"/>
-      <c r="C52" s="86"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="89"/>
       <c r="D52" s="12" t="s">
         <v>132</v>
       </c>
@@ -2477,8 +2774,8 @@
       </c>
     </row>
     <row r="53" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="89"/>
       <c r="D53" s="12" t="s">
         <v>134</v>
       </c>
@@ -2487,8 +2784,8 @@
       </c>
     </row>
     <row r="54" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
       <c r="D54" s="12" t="s">
         <v>136</v>
       </c>
@@ -2497,8 +2794,8 @@
       </c>
     </row>
     <row r="55" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="86"/>
-      <c r="C55" s="86"/>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
       <c r="D55" s="12" t="s">
         <v>138</v>
       </c>
@@ -2507,8 +2804,8 @@
       </c>
     </row>
     <row r="56" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
+      <c r="B56" s="89"/>
+      <c r="C56" s="89"/>
       <c r="D56" s="12" t="s">
         <v>140</v>
       </c>
@@ -2517,18 +2814,18 @@
       </c>
     </row>
     <row r="57" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="41" t="s">
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="E57" s="41" t="s">
+      <c r="E57" s="40" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
       <c r="D58" s="12" t="s">
         <v>144</v>
       </c>
@@ -2537,8 +2834,8 @@
       </c>
     </row>
     <row r="59" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
+      <c r="B59" s="89"/>
+      <c r="C59" s="89"/>
       <c r="D59" s="12" t="s">
         <v>146</v>
       </c>
@@ -2547,8 +2844,8 @@
       </c>
     </row>
     <row r="60" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="87"/>
-      <c r="C60" s="87"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
       <c r="D60" s="12" t="s">
         <v>148</v>
       </c>
@@ -2557,22 +2854,22 @@
       </c>
     </row>
     <row r="61" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="97" t="s">
+      <c r="B61" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="98" t="s">
+      <c r="C61" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="D61" s="42" t="s">
+      <c r="D61" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="42" t="s">
+      <c r="E61" s="41" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="89"/>
       <c r="D62" s="13" t="s">
         <v>42</v>
       </c>
@@ -2581,28 +2878,28 @@
       </c>
     </row>
     <row r="63" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="86"/>
-      <c r="C63" s="86"/>
-      <c r="D63" s="42" t="s">
+      <c r="B63" s="89"/>
+      <c r="C63" s="89"/>
+      <c r="D63" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="42" t="s">
+      <c r="E63" s="41" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="86"/>
-      <c r="C64" s="86"/>
-      <c r="D64" s="42" t="s">
+      <c r="B64" s="89"/>
+      <c r="C64" s="89"/>
+      <c r="D64" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E64" s="42" t="s">
+      <c r="E64" s="41" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="86"/>
-      <c r="C65" s="86"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
       <c r="D65" s="13" t="s">
         <v>41</v>
       </c>
@@ -2611,8 +2908,8 @@
       </c>
     </row>
     <row r="66" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="86"/>
-      <c r="C66" s="86"/>
+      <c r="B66" s="89"/>
+      <c r="C66" s="89"/>
       <c r="D66" s="13" t="s">
         <v>42</v>
       </c>
@@ -2621,8 +2918,8 @@
       </c>
     </row>
     <row r="67" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="86"/>
-      <c r="C67" s="86"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="89"/>
       <c r="D67" s="13" t="s">
         <v>43</v>
       </c>
@@ -2631,8 +2928,8 @@
       </c>
     </row>
     <row r="68" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="86"/>
-      <c r="C68" s="86"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="89"/>
       <c r="D68" s="13" t="s">
         <v>44</v>
       </c>
@@ -2641,8 +2938,8 @@
       </c>
     </row>
     <row r="69" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="86"/>
-      <c r="C69" s="86"/>
+      <c r="B69" s="89"/>
+      <c r="C69" s="89"/>
       <c r="D69" s="13" t="s">
         <v>41</v>
       </c>
@@ -2651,8 +2948,8 @@
       </c>
     </row>
     <row r="70" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
+      <c r="B70" s="89"/>
+      <c r="C70" s="89"/>
       <c r="D70" s="13" t="s">
         <v>42</v>
       </c>
@@ -2661,32 +2958,32 @@
       </c>
     </row>
     <row r="71" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="87"/>
-      <c r="C71" s="87"/>
-      <c r="D71" s="42" t="s">
+      <c r="B71" s="90"/>
+      <c r="C71" s="90"/>
+      <c r="D71" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E71" s="42" t="s">
+      <c r="E71" s="41" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="89" t="s">
+      <c r="B72" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="90" t="s">
+      <c r="C72" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="43" t="s">
+      <c r="D72" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="43" t="s">
+      <c r="E72" s="42" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
+      <c r="B73" s="89"/>
+      <c r="C73" s="89"/>
       <c r="D73" s="14" t="s">
         <v>162</v>
       </c>
@@ -2695,8 +2992,8 @@
       </c>
     </row>
     <row r="74" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="86"/>
-      <c r="C74" s="86"/>
+      <c r="B74" s="89"/>
+      <c r="C74" s="89"/>
       <c r="D74" s="14" t="s">
         <v>164</v>
       </c>
@@ -2705,28 +3002,28 @@
       </c>
     </row>
     <row r="75" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="86"/>
-      <c r="C75" s="86"/>
-      <c r="D75" s="43" t="s">
+      <c r="B75" s="89"/>
+      <c r="C75" s="89"/>
+      <c r="D75" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="43" t="s">
+      <c r="E75" s="42" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="76" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
-      <c r="D76" s="43" t="s">
+      <c r="B76" s="89"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="43" t="s">
+      <c r="E76" s="42" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="77" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="86"/>
-      <c r="C77" s="86"/>
+      <c r="B77" s="89"/>
+      <c r="C77" s="89"/>
       <c r="D77" s="14" t="s">
         <v>170</v>
       </c>
@@ -2735,18 +3032,18 @@
       </c>
     </row>
     <row r="78" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="43" t="s">
+      <c r="B78" s="89"/>
+      <c r="C78" s="89"/>
+      <c r="D78" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="43" t="s">
+      <c r="E78" s="42" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="86"/>
-      <c r="C79" s="86"/>
+      <c r="B79" s="89"/>
+      <c r="C79" s="89"/>
       <c r="D79" s="14" t="s">
         <v>174</v>
       </c>
@@ -2755,8 +3052,8 @@
       </c>
     </row>
     <row r="80" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
+      <c r="B80" s="89"/>
+      <c r="C80" s="89"/>
       <c r="D80" s="14" t="s">
         <v>175</v>
       </c>
@@ -2765,8 +3062,8 @@
       </c>
     </row>
     <row r="81" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="87"/>
-      <c r="C81" s="87"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="90"/>
       <c r="D81" s="14" t="s">
         <v>177</v>
       </c>
@@ -2775,10 +3072,10 @@
       </c>
     </row>
     <row r="82" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="91" t="s">
+      <c r="B82" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="C82" s="92" t="s">
+      <c r="C82" s="95" t="s">
         <v>49</v>
       </c>
       <c r="D82" s="15" t="s">
@@ -2789,8 +3086,8 @@
       </c>
     </row>
     <row r="83" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="86"/>
-      <c r="C83" s="86"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="89"/>
       <c r="D83" s="15" t="s">
         <v>52</v>
       </c>
@@ -2799,8 +3096,8 @@
       </c>
     </row>
     <row r="84" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="86"/>
-      <c r="C84" s="86"/>
+      <c r="B84" s="89"/>
+      <c r="C84" s="89"/>
       <c r="D84" s="15" t="s">
         <v>181</v>
       </c>
@@ -2809,18 +3106,18 @@
       </c>
     </row>
     <row r="85" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="86"/>
-      <c r="C85" s="86"/>
-      <c r="D85" s="44" t="s">
+      <c r="B85" s="89"/>
+      <c r="C85" s="89"/>
+      <c r="D85" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="E85" s="44" t="s">
+      <c r="E85" s="43" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="86" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="86"/>
-      <c r="C86" s="86"/>
+      <c r="B86" s="89"/>
+      <c r="C86" s="89"/>
       <c r="D86" s="15" t="s">
         <v>184</v>
       </c>
@@ -2829,8 +3126,8 @@
       </c>
     </row>
     <row r="87" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="86"/>
-      <c r="C87" s="86"/>
+      <c r="B87" s="89"/>
+      <c r="C87" s="89"/>
       <c r="D87" s="15" t="s">
         <v>186</v>
       </c>
@@ -2839,28 +3136,28 @@
       </c>
     </row>
     <row r="88" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="86"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="44" t="s">
+      <c r="B88" s="89"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="E88" s="44" t="s">
+      <c r="E88" s="43" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="89" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="86"/>
-      <c r="C89" s="86"/>
-      <c r="D89" s="44" t="s">
+      <c r="B89" s="89"/>
+      <c r="C89" s="89"/>
+      <c r="D89" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="44" t="s">
+      <c r="E89" s="43" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="90" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="86"/>
-      <c r="C90" s="86"/>
+      <c r="B90" s="89"/>
+      <c r="C90" s="89"/>
       <c r="D90" s="15" t="s">
         <v>192</v>
       </c>
@@ -2869,12 +3166,12 @@
       </c>
     </row>
     <row r="91" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="87"/>
-      <c r="C91" s="87"/>
-      <c r="D91" s="44" t="s">
+      <c r="B91" s="90"/>
+      <c r="C91" s="90"/>
+      <c r="D91" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="E91" s="44" t="s">
+      <c r="E91" s="43" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3775,7 +4072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1038C4-DEF6-4FD1-B0FA-345FACC2F83A}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -3783,7 +4080,7 @@
     <col min="3" max="3" width="49.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="45.5703125" customWidth="1"/>
-    <col min="6" max="6" width="37.5703125" customWidth="1"/>
+    <col min="6" max="6" width="67.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3799,7 +4096,7 @@
       <c r="D1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="37" t="s">
         <v>201</v>
       </c>
       <c r="F1" s="35" t="s">
@@ -3807,7 +4104,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="102" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -3822,12 +4119,12 @@
       <c r="E2" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="44" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100"/>
+      <c r="A3" s="103"/>
       <c r="B3" s="17" t="s">
         <v>57</v>
       </c>
@@ -3840,12 +4137,12 @@
       <c r="E3" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="44" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="100"/>
+      <c r="A4" s="103"/>
       <c r="B4" s="17" t="s">
         <v>65</v>
       </c>
@@ -3858,12 +4155,12 @@
       <c r="E4" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="44" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="100"/>
+      <c r="A5" s="103"/>
       <c r="B5" s="17" t="s">
         <v>67</v>
       </c>
@@ -3876,435 +4173,427 @@
       <c r="E5" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F5" s="121" t="s">
+      <c r="F5" s="84" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="101"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="99" t="s">
+    <row r="6" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="102" t="s">
         <v>22</v>
       </c>
+      <c r="B6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" s="84" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="103"/>
       <c r="B7" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>212</v>
+        <v>26</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>210</v>
       </c>
       <c r="D7" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F7" s="85" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="103"/>
+      <c r="B8" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" s="121" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="100"/>
-      <c r="B8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="E8" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="84" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="104"/>
+      <c r="B9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="122" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="100"/>
-      <c r="B9" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>213</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F9" s="121" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="101"/>
+      <c r="E9" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="85" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="102" t="s">
+        <v>29</v>
+      </c>
       <c r="B10" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="F10" s="122" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="99" t="s">
-        <v>29</v>
-      </c>
+      <c r="E10" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="F10" s="85" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="103"/>
       <c r="B11" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="F11" s="122" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="100"/>
+      <c r="E11" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="84" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="103"/>
       <c r="B12" s="17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="F12" s="121" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="100"/>
+      <c r="E12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="84" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="103"/>
       <c r="B13" s="17" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E13" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="121" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="100"/>
-      <c r="B14" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="E13" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F14" s="123" t="s">
+      <c r="F13" s="86" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="101"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16"/>
-      <c r="F15" s="123"/>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="104"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="16"/>
+      <c r="F14" s="86"/>
+    </row>
+    <row r="15" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="85" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="99" t="s">
-        <v>40</v>
-      </c>
+      <c r="A16" s="103"/>
       <c r="B16" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>221</v>
+        <v>43</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E16" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="F16" s="122" t="s">
-        <v>258</v>
+      <c r="E16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="100"/>
+      <c r="A17" s="103"/>
       <c r="B17" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D17" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="84" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="104"/>
+      <c r="B18" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="84" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E17" t="s">
-        <v>224</v>
-      </c>
-      <c r="F17" s="121" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="100"/>
-      <c r="B18" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="F18" s="121" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="101"/>
-      <c r="B19" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="F19" s="121" t="s">
-        <v>263</v>
+      <c r="E19" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="85" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="99" t="s">
-        <v>46</v>
-      </c>
+      <c r="A20" s="103"/>
       <c r="B20" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>229</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="D20" s="29" t="s">
         <v>198</v>
       </c>
       <c r="E20" t="s">
-        <v>230</v>
-      </c>
-      <c r="F20" s="122" t="s">
-        <v>264</v>
+        <v>228</v>
+      </c>
+      <c r="F20" s="85" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="100"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>227</v>
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>231</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>198</v>
       </c>
       <c r="E21" t="s">
-        <v>228</v>
-      </c>
-      <c r="F21" s="122" t="s">
-        <v>265</v>
+        <v>232</v>
+      </c>
+      <c r="F21" s="85" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="100"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>231</v>
+        <v>82</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>267</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="E22" t="s">
-        <v>232</v>
-      </c>
-      <c r="F22" s="122" t="s">
-        <v>266</v>
+      <c r="E22" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="F22" s="84" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="100"/>
-      <c r="B23" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="D23" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="F23" s="121" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="100"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="99" t="s">
+      <c r="A23" s="103"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="86"/>
+    </row>
+    <row r="24" spans="1:6" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="102" t="s">
         <v>49</v>
       </c>
+      <c r="B24" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F24" s="85" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="103"/>
       <c r="B25" s="17" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>197</v>
       </c>
       <c r="E25" t="s">
-        <v>234</v>
-      </c>
-      <c r="F25" s="122" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="100"/>
+        <v>236</v>
+      </c>
+      <c r="F25" s="85" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="103"/>
       <c r="B26" s="17" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D26" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F26" s="85" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="104"/>
+      <c r="B27" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E26" t="s">
-        <v>236</v>
-      </c>
-      <c r="F26" s="122" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="100"/>
-      <c r="B27" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s">
-        <v>237</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" t="s">
-        <v>238</v>
-      </c>
-      <c r="F27" s="122" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="101"/>
-      <c r="B28" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="E27" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="F28" s="121" t="s">
+      <c r="F27" s="84" t="s">
         <v>275</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{B9B0E923-C530-4854-B15F-90B9FDE9031B}"/>
     <hyperlink ref="F5" r:id="rId2" xr:uid="{911121F1-4F26-4DCD-9033-361BBC4E0546}"/>
     <hyperlink ref="F4" r:id="rId3" xr:uid="{AAE4BEF9-6B31-4E9E-9C00-E1DBB4F4654E}"/>
-    <hyperlink ref="F7" r:id="rId4" display="https://www.ecuadorencifras.gob.ec/canasta/" xr:uid="{23F81829-6DE3-495B-B791-0DDACB12758C}"/>
-    <hyperlink ref="F8" r:id="rId5" display="https://scioteca.caf.com/bitstream/handle/123456789/2132/CAF_PYMES_ECUADOR.pdf" xr:uid="{17AB6E34-6C65-4C76-BB15-45DA74EAAE77}"/>
+    <hyperlink ref="F6" r:id="rId4" display="https://www.ecuadorencifras.gob.ec/canasta/" xr:uid="{23F81829-6DE3-495B-B791-0DDACB12758C}"/>
+    <hyperlink ref="F7" r:id="rId5" display="https://scioteca.caf.com/bitstream/handle/123456789/2132/CAF_PYMES_ECUADOR.pdf" xr:uid="{17AB6E34-6C65-4C76-BB15-45DA74EAAE77}"/>
     <hyperlink ref="F3" r:id="rId6" xr:uid="{B1F76C86-9796-40C3-AACF-94F7B72E481E}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{655C8D5D-FACE-46B6-851D-1DB64DCD5AC2}"/>
-    <hyperlink ref="F11" r:id="rId8" xr:uid="{9B4D130E-715A-4D9A-BFC3-426789CF9FE4}"/>
-    <hyperlink ref="F12" r:id="rId9" xr:uid="{C9FE3835-5115-4DE6-9481-2C331629D071}"/>
-    <hyperlink ref="F13" r:id="rId10" xr:uid="{5831F023-4B70-43AD-B529-698D296A23A9}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{A3D28794-8AE3-4CA8-9359-7EE83F0E49F1}"/>
-    <hyperlink ref="F17" r:id="rId12" xr:uid="{701A1368-F60B-43F6-8709-680C606B207A}"/>
-    <hyperlink ref="F18" r:id="rId13" xr:uid="{87B1AE0E-EFAD-40A0-9839-25401A0F8890}"/>
-    <hyperlink ref="F19" r:id="rId14" xr:uid="{F980E355-2A6D-4E69-A8F4-71C2E39B0032}"/>
-    <hyperlink ref="F20" r:id="rId15" xr:uid="{6AEB54F4-A2BB-4A0E-B776-0EC6A0C23B7E}"/>
-    <hyperlink ref="F21" r:id="rId16" xr:uid="{4356E839-4635-4065-A205-D29911DDA400}"/>
-    <hyperlink ref="F22" r:id="rId17" xr:uid="{85605F5C-0E22-4BC8-A9D1-0F5E50926FF2}"/>
-    <hyperlink ref="F23" r:id="rId18" xr:uid="{12E332EE-E9E0-4E24-BDEB-3960D6C81F69}"/>
-    <hyperlink ref="F25" r:id="rId19" xr:uid="{D7FDE972-E190-4F3E-983F-6023D5BCFB5F}"/>
-    <hyperlink ref="F26" r:id="rId20" xr:uid="{34C1B85D-B41A-4F33-AFB6-50514BB42EFF}"/>
-    <hyperlink ref="F27" r:id="rId21" xr:uid="{3BB4A1D5-418B-49A7-AF70-AA7EC410B1CD}"/>
-    <hyperlink ref="F28" r:id="rId22" xr:uid="{919BD1D8-A07B-4079-B7C0-44F7BB3419DE}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{655C8D5D-FACE-46B6-851D-1DB64DCD5AC2}"/>
+    <hyperlink ref="F10" r:id="rId8" xr:uid="{9B4D130E-715A-4D9A-BFC3-426789CF9FE4}"/>
+    <hyperlink ref="F11" r:id="rId9" xr:uid="{C9FE3835-5115-4DE6-9481-2C331629D071}"/>
+    <hyperlink ref="F12" r:id="rId10" xr:uid="{5831F023-4B70-43AD-B529-698D296A23A9}"/>
+    <hyperlink ref="F15" r:id="rId11" xr:uid="{A3D28794-8AE3-4CA8-9359-7EE83F0E49F1}"/>
+    <hyperlink ref="F16" r:id="rId12" xr:uid="{701A1368-F60B-43F6-8709-680C606B207A}"/>
+    <hyperlink ref="F17" r:id="rId13" xr:uid="{87B1AE0E-EFAD-40A0-9839-25401A0F8890}"/>
+    <hyperlink ref="F18" r:id="rId14" xr:uid="{F980E355-2A6D-4E69-A8F4-71C2E39B0032}"/>
+    <hyperlink ref="F19" r:id="rId15" xr:uid="{6AEB54F4-A2BB-4A0E-B776-0EC6A0C23B7E}"/>
+    <hyperlink ref="F20" r:id="rId16" xr:uid="{4356E839-4635-4065-A205-D29911DDA400}"/>
+    <hyperlink ref="F21" r:id="rId17" xr:uid="{85605F5C-0E22-4BC8-A9D1-0F5E50926FF2}"/>
+    <hyperlink ref="F22" r:id="rId18" xr:uid="{12E332EE-E9E0-4E24-BDEB-3960D6C81F69}"/>
+    <hyperlink ref="F24" r:id="rId19" xr:uid="{D7FDE972-E190-4F3E-983F-6023D5BCFB5F}"/>
+    <hyperlink ref="F25" r:id="rId20" xr:uid="{34C1B85D-B41A-4F33-AFB6-50514BB42EFF}"/>
+    <hyperlink ref="F26" r:id="rId21" xr:uid="{3BB4A1D5-418B-49A7-AF70-AA7EC410B1CD}"/>
+    <hyperlink ref="F27" r:id="rId22" xr:uid="{919BD1D8-A07B-4079-B7C0-44F7BB3419DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4329,17 +4618,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="111" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F2" s="1" t="s">
@@ -4348,21 +4637,21 @@
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="107" t="s">
+      <c r="H2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="110" t="s">
+      <c r="J2" s="119" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="112"/>
+      <c r="C3" s="121"/>
       <c r="D3" s="24" t="s">
         <v>6</v>
       </c>
@@ -4375,15 +4664,15 @@
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="113" t="s">
+      <c r="B4" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="123" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="25" t="s">
@@ -4392,98 +4681,98 @@
       <c r="E4" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="65">
         <v>2</v>
       </c>
-      <c r="G4" s="67">
+      <c r="G4" s="66">
         <v>3</v>
       </c>
-      <c r="H4" s="68">
+      <c r="H4" s="67">
         <f t="shared" ref="H4:H28" si="0">F4*G4</f>
         <v>6</v>
       </c>
-      <c r="I4" s="68" t="s">
+      <c r="I4" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="68"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="112"/>
-      <c r="C5" s="112"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="25" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="65">
         <v>3</v>
       </c>
-      <c r="G5" s="69">
+      <c r="G5" s="68">
         <v>3</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="67">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I5" s="70"/>
-      <c r="J5" s="58" t="s">
+      <c r="I5" s="69"/>
+      <c r="J5" s="57" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="112"/>
-      <c r="C6" s="112"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
       <c r="D6" s="25" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="65">
         <v>3</v>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="68">
         <v>3</v>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="67">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70" t="s">
+      <c r="I6" s="69"/>
+      <c r="J6" s="69" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="112"/>
-      <c r="C7" s="112"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
       <c r="D7" s="25" t="s">
         <v>67</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="66">
+      <c r="F7" s="65">
         <v>3</v>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="68">
         <v>2</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="67">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="70"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="104" t="s">
+      <c r="C8" s="113" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="26" t="s">
@@ -4492,507 +4781,507 @@
       <c r="E8" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="70">
         <v>2</v>
       </c>
-      <c r="G8" s="71">
+      <c r="G8" s="70">
         <v>3</v>
       </c>
-      <c r="H8" s="72">
+      <c r="H8" s="71">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72" t="s">
+      <c r="I8" s="71"/>
+      <c r="J8" s="71" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="113"/>
       <c r="D9" s="26" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="71">
+      <c r="F9" s="70">
         <v>3</v>
       </c>
-      <c r="G9" s="71">
+      <c r="G9" s="70">
         <v>2</v>
       </c>
-      <c r="H9" s="72">
+      <c r="H9" s="71">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72" t="s">
+      <c r="I9" s="71"/>
+      <c r="J9" s="71" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="113"/>
       <c r="D10" s="26" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="F10" s="71">
+      <c r="F10" s="70">
         <v>2</v>
       </c>
-      <c r="G10" s="71">
+      <c r="G10" s="70">
         <v>3</v>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="71">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I10" s="73" t="s">
+      <c r="I10" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="72"/>
+      <c r="J10" s="71"/>
     </row>
     <row r="11" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="103"/>
-      <c r="C11" s="104"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="113"/>
       <c r="D11" s="26" t="s">
         <v>88</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F11" s="70">
         <v>3</v>
       </c>
-      <c r="G11" s="71">
+      <c r="G11" s="70">
         <v>2</v>
       </c>
-      <c r="H11" s="72">
+      <c r="H11" s="71">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72" t="s">
+      <c r="I11" s="71"/>
+      <c r="J11" s="71" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F12" s="73">
         <v>3</v>
       </c>
-      <c r="G12" s="74">
+      <c r="G12" s="73">
         <v>3</v>
       </c>
-      <c r="H12" s="75">
+      <c r="H12" s="74">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I12" s="75" t="s">
+      <c r="I12" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="75"/>
+      <c r="J12" s="74"/>
     </row>
     <row r="13" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="115"/>
       <c r="D13" s="27" t="s">
         <v>122</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="75">
         <v>3</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="75">
         <v>2</v>
       </c>
-      <c r="H13" s="77">
+      <c r="H13" s="76">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="77" t="s">
+      <c r="I13" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="77"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="105"/>
-      <c r="C14" s="106"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="115"/>
       <c r="D14" s="27" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="75">
         <v>2</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="75">
         <v>3</v>
       </c>
-      <c r="H14" s="77">
+      <c r="H14" s="76">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I14" s="77" t="s">
+      <c r="I14" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="J14" s="78"/>
+      <c r="J14" s="77"/>
     </row>
     <row r="15" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="27" t="s">
         <v>142</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="75">
         <v>3</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="75">
         <v>3</v>
       </c>
-      <c r="H15" s="77">
+      <c r="H15" s="76">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I15" s="77" t="s">
+      <c r="I15" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="J15" s="77"/>
+      <c r="J15" s="76"/>
     </row>
     <row r="16" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="105"/>
-      <c r="C16" s="106"/>
+      <c r="B16" s="114"/>
+      <c r="C16" s="115"/>
       <c r="D16" s="27"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
     </row>
     <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="118" t="s">
+      <c r="C17" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="50" t="s">
         <v>221</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="78">
         <v>3</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="78">
         <v>2</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="79">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I17" s="80" t="s">
+      <c r="I17" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="80"/>
+      <c r="J17" s="79"/>
     </row>
     <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="117"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="55" t="s">
+      <c r="B18" s="109"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="50" t="s">
         <v>223</v>
       </c>
-      <c r="F18" s="79">
+      <c r="F18" s="78">
         <v>2</v>
       </c>
-      <c r="G18" s="79">
+      <c r="G18" s="78">
         <v>2</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="79">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I18" s="80" t="s">
+      <c r="I18" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="81"/>
+      <c r="J18" s="80"/>
     </row>
     <row r="19" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="117"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="55" t="s">
+      <c r="B19" s="109"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="50" t="s">
         <v>225</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="78">
         <v>3</v>
       </c>
-      <c r="G19" s="79">
+      <c r="G19" s="78">
         <v>2</v>
       </c>
-      <c r="H19" s="80">
+      <c r="H19" s="79">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I19" s="80" t="s">
+      <c r="I19" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J19" s="80"/>
+      <c r="J19" s="79"/>
     </row>
     <row r="20" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="117"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="55" t="s">
+      <c r="B20" s="109"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="E20" s="124" t="s">
+      <c r="E20" s="87" t="s">
         <v>278</v>
       </c>
-      <c r="F20" s="79">
+      <c r="F20" s="78">
         <v>3</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="78">
         <v>3</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="79">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I20" s="80" t="s">
+      <c r="I20" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="80"/>
+      <c r="J20" s="79"/>
     </row>
     <row r="21" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="116" t="s">
+      <c r="C21" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="F21" s="82">
+      <c r="F21" s="81">
         <v>2</v>
       </c>
-      <c r="G21" s="82">
+      <c r="G21" s="81">
         <v>2</v>
       </c>
-      <c r="H21" s="83">
+      <c r="H21" s="82">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I21" s="83" t="s">
+      <c r="I21" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J21" s="83"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="56" t="s">
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="81">
         <v>2</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="81">
         <v>2</v>
       </c>
-      <c r="H22" s="83">
+      <c r="H22" s="82">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I22" s="84" t="s">
+      <c r="I22" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="J22" s="83"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="56" t="s">
+      <c r="B23" s="107"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="54" t="s">
+      <c r="E23" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="81">
         <v>2</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="81">
         <v>3</v>
       </c>
-      <c r="H23" s="83">
+      <c r="H23" s="82">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I23" s="83" t="s">
+      <c r="I23" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="83"/>
+      <c r="J23" s="82"/>
     </row>
     <row r="24" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="115"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="56" t="s">
+      <c r="B24" s="107"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="81">
         <v>2</v>
       </c>
-      <c r="G24" s="82">
+      <c r="G24" s="81">
         <v>2</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="82">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I24" s="83" t="s">
+      <c r="I24" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J24" s="83"/>
+      <c r="J24" s="82"/>
     </row>
     <row r="25" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="119" t="s">
+      <c r="B25" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="120" t="s">
+      <c r="C25" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="56" t="s">
         <v>182</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="61">
         <v>3</v>
       </c>
-      <c r="G25" s="62">
+      <c r="G25" s="61">
         <v>3</v>
       </c>
-      <c r="H25" s="63">
+      <c r="H25" s="62">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I25" s="63" t="s">
+      <c r="I25" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="63"/>
+      <c r="J25" s="62"/>
     </row>
     <row r="26" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="119"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="57" t="s">
+      <c r="B26" s="105"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="56" t="s">
         <v>188</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="F26" s="62">
+      <c r="F26" s="61">
         <v>3</v>
       </c>
-      <c r="G26" s="62">
+      <c r="G26" s="61">
         <v>3</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="62">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I26" s="63" t="s">
+      <c r="I26" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="63"/>
+      <c r="J26" s="62"/>
     </row>
     <row r="27" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="119"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="57" t="s">
+      <c r="B27" s="105"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="56" t="s">
         <v>190</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="F27" s="64">
+      <c r="F27" s="63">
         <v>2</v>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="61">
         <v>2</v>
       </c>
-      <c r="H27" s="63">
+      <c r="H27" s="62">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I27" s="65"/>
-      <c r="J27" s="63" t="s">
+      <c r="I27" s="64"/>
+      <c r="J27" s="62" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="119"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="57" t="s">
+      <c r="B28" s="105"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="56" t="s">
         <v>194</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="F28" s="59">
+      <c r="F28" s="58">
         <v>3</v>
       </c>
-      <c r="G28" s="60">
+      <c r="G28" s="59">
         <v>2</v>
       </c>
-      <c r="H28" s="61">
+      <c r="H28" s="60">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I28" s="61" t="s">
+      <c r="I28" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="J28" s="61"/>
+      <c r="J28" s="60"/>
     </row>
     <row r="29" spans="2:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="119"/>
-      <c r="C29" s="120"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="106"/>
       <c r="D29" s="28"/>
       <c r="E29" s="21"/>
       <c r="F29" s="34"/>
@@ -5078,10 +5367,10 @@
     <row r="104" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="85" t="s">
+      <c r="B106" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="88" t="s">
+      <c r="C106" s="91" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="9" t="s">
@@ -5092,8 +5381,8 @@
       </c>
     </row>
     <row r="107" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="86"/>
-      <c r="C107" s="86"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="89"/>
       <c r="D107" s="9" t="s">
         <v>15</v>
       </c>
@@ -5102,8 +5391,8 @@
       </c>
     </row>
     <row r="108" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="86"/>
-      <c r="C108" s="86"/>
+      <c r="B108" s="89"/>
+      <c r="C108" s="89"/>
       <c r="D108" s="9" t="s">
         <v>17</v>
       </c>
@@ -5112,8 +5401,8 @@
       </c>
     </row>
     <row r="109" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="86"/>
-      <c r="C109" s="86"/>
+      <c r="B109" s="89"/>
+      <c r="C109" s="89"/>
       <c r="D109" s="9" t="s">
         <v>19</v>
       </c>
@@ -5122,8 +5411,8 @@
       </c>
     </row>
     <row r="110" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="86"/>
-      <c r="C110" s="86"/>
+      <c r="B110" s="89"/>
+      <c r="C110" s="89"/>
       <c r="D110" s="9" t="s">
         <v>55</v>
       </c>
@@ -5132,8 +5421,8 @@
       </c>
     </row>
     <row r="111" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="86"/>
-      <c r="C111" s="86"/>
+      <c r="B111" s="89"/>
+      <c r="C111" s="89"/>
       <c r="D111" s="9" t="s">
         <v>57</v>
       </c>
@@ -5142,8 +5431,8 @@
       </c>
     </row>
     <row r="112" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="86"/>
-      <c r="C112" s="86"/>
+      <c r="B112" s="89"/>
+      <c r="C112" s="89"/>
       <c r="D112" s="9" t="s">
         <v>58</v>
       </c>
@@ -5152,8 +5441,8 @@
       </c>
     </row>
     <row r="113" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="86"/>
-      <c r="C113" s="86"/>
+      <c r="B113" s="89"/>
+      <c r="C113" s="89"/>
       <c r="D113" s="9" t="s">
         <v>60</v>
       </c>
@@ -5162,8 +5451,8 @@
       </c>
     </row>
     <row r="114" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="86"/>
-      <c r="C114" s="86"/>
+      <c r="B114" s="89"/>
+      <c r="C114" s="89"/>
       <c r="D114" s="9" t="s">
         <v>62</v>
       </c>
@@ -5172,8 +5461,8 @@
       </c>
     </row>
     <row r="115" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="86"/>
-      <c r="C115" s="86"/>
+      <c r="B115" s="89"/>
+      <c r="C115" s="89"/>
       <c r="D115" s="9" t="s">
         <v>64</v>
       </c>
@@ -5182,8 +5471,8 @@
       </c>
     </row>
     <row r="116" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="86"/>
-      <c r="C116" s="86"/>
+      <c r="B116" s="89"/>
+      <c r="C116" s="89"/>
       <c r="D116" s="9" t="s">
         <v>65</v>
       </c>
@@ -5192,8 +5481,8 @@
       </c>
     </row>
     <row r="117" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="86"/>
-      <c r="C117" s="86"/>
+      <c r="B117" s="89"/>
+      <c r="C117" s="89"/>
       <c r="D117" s="9" t="s">
         <v>67</v>
       </c>
@@ -5202,8 +5491,8 @@
       </c>
     </row>
     <row r="118" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="86"/>
-      <c r="C118" s="86"/>
+      <c r="B118" s="89"/>
+      <c r="C118" s="89"/>
       <c r="D118" s="9" t="s">
         <v>69</v>
       </c>
@@ -5212,8 +5501,8 @@
       </c>
     </row>
     <row r="119" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="86"/>
-      <c r="C119" s="86"/>
+      <c r="B119" s="89"/>
+      <c r="C119" s="89"/>
       <c r="D119" s="9" t="s">
         <v>71</v>
       </c>
@@ -5222,8 +5511,8 @@
       </c>
     </row>
     <row r="120" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="87"/>
-      <c r="C120" s="87"/>
+      <c r="B120" s="90"/>
+      <c r="C120" s="90"/>
       <c r="D120" s="9" t="s">
         <v>73</v>
       </c>
@@ -5232,10 +5521,10 @@
       </c>
     </row>
     <row r="121" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="93" t="s">
+      <c r="B121" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="C121" s="94" t="s">
+      <c r="C121" s="97" t="s">
         <v>22</v>
       </c>
       <c r="D121" s="10" t="s">
@@ -5247,8 +5536,8 @@
       <c r="H121" s="11"/>
     </row>
     <row r="122" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="86"/>
-      <c r="C122" s="86"/>
+      <c r="B122" s="89"/>
+      <c r="C122" s="89"/>
       <c r="D122" s="10" t="s">
         <v>24</v>
       </c>
@@ -5257,8 +5546,8 @@
       </c>
     </row>
     <row r="123" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="86"/>
-      <c r="C123" s="86"/>
+      <c r="B123" s="89"/>
+      <c r="C123" s="89"/>
       <c r="D123" s="10" t="s">
         <v>25</v>
       </c>
@@ -5267,8 +5556,8 @@
       </c>
     </row>
     <row r="124" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="86"/>
-      <c r="C124" s="86"/>
+      <c r="B124" s="89"/>
+      <c r="C124" s="89"/>
       <c r="D124" s="10" t="s">
         <v>26</v>
       </c>
@@ -5277,8 +5566,8 @@
       </c>
     </row>
     <row r="125" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="86"/>
-      <c r="C125" s="86"/>
+      <c r="B125" s="89"/>
+      <c r="C125" s="89"/>
       <c r="D125" s="10" t="s">
         <v>79</v>
       </c>
@@ -5287,8 +5576,8 @@
       </c>
     </row>
     <row r="126" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="86"/>
-      <c r="C126" s="86"/>
+      <c r="B126" s="89"/>
+      <c r="C126" s="89"/>
       <c r="D126" s="10" t="s">
         <v>27</v>
       </c>
@@ -5297,8 +5586,8 @@
       </c>
     </row>
     <row r="127" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="86"/>
-      <c r="C127" s="86"/>
+      <c r="B127" s="89"/>
+      <c r="C127" s="89"/>
       <c r="D127" s="10" t="s">
         <v>82</v>
       </c>
@@ -5307,8 +5596,8 @@
       </c>
     </row>
     <row r="128" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="86"/>
-      <c r="C128" s="86"/>
+      <c r="B128" s="89"/>
+      <c r="C128" s="89"/>
       <c r="D128" s="10" t="s">
         <v>84</v>
       </c>
@@ -5317,8 +5606,8 @@
       </c>
     </row>
     <row r="129" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="86"/>
-      <c r="C129" s="86"/>
+      <c r="B129" s="89"/>
+      <c r="C129" s="89"/>
       <c r="D129" s="10" t="s">
         <v>86</v>
       </c>
@@ -5327,8 +5616,8 @@
       </c>
     </row>
     <row r="130" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="86"/>
-      <c r="C130" s="86"/>
+      <c r="B130" s="89"/>
+      <c r="C130" s="89"/>
       <c r="D130" s="10" t="s">
         <v>88</v>
       </c>
@@ -5337,8 +5626,8 @@
       </c>
     </row>
     <row r="131" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="86"/>
-      <c r="C131" s="86"/>
+      <c r="B131" s="89"/>
+      <c r="C131" s="89"/>
       <c r="D131" s="10" t="s">
         <v>90</v>
       </c>
@@ -5347,8 +5636,8 @@
       </c>
     </row>
     <row r="132" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="86"/>
-      <c r="C132" s="86"/>
+      <c r="B132" s="89"/>
+      <c r="C132" s="89"/>
       <c r="D132" s="10" t="s">
         <v>92</v>
       </c>
@@ -5357,8 +5646,8 @@
       </c>
     </row>
     <row r="133" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="86"/>
-      <c r="C133" s="86"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
       <c r="D133" s="10" t="s">
         <v>94</v>
       </c>
@@ -5367,8 +5656,8 @@
       </c>
     </row>
     <row r="134" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="86"/>
-      <c r="C134" s="86"/>
+      <c r="B134" s="89"/>
+      <c r="C134" s="89"/>
       <c r="D134" s="10" t="s">
         <v>96</v>
       </c>
@@ -5377,8 +5666,8 @@
       </c>
     </row>
     <row r="135" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="86"/>
-      <c r="C135" s="86"/>
+      <c r="B135" s="89"/>
+      <c r="C135" s="89"/>
       <c r="D135" s="10" t="s">
         <v>98</v>
       </c>
@@ -5387,8 +5676,8 @@
       </c>
     </row>
     <row r="136" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="86"/>
-      <c r="C136" s="86"/>
+      <c r="B136" s="89"/>
+      <c r="C136" s="89"/>
       <c r="D136" s="10" t="s">
         <v>100</v>
       </c>
@@ -5397,8 +5686,8 @@
       </c>
     </row>
     <row r="137" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="86"/>
-      <c r="C137" s="86"/>
+      <c r="B137" s="89"/>
+      <c r="C137" s="89"/>
       <c r="D137" s="10" t="s">
         <v>102</v>
       </c>
@@ -5407,8 +5696,8 @@
       </c>
     </row>
     <row r="138" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="86"/>
-      <c r="C138" s="86"/>
+      <c r="B138" s="89"/>
+      <c r="C138" s="89"/>
       <c r="D138" s="10" t="s">
         <v>104</v>
       </c>
@@ -5417,8 +5706,8 @@
       </c>
     </row>
     <row r="139" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="86"/>
-      <c r="C139" s="86"/>
+      <c r="B139" s="89"/>
+      <c r="C139" s="89"/>
       <c r="D139" s="10" t="s">
         <v>106</v>
       </c>
@@ -5427,8 +5716,8 @@
       </c>
     </row>
     <row r="140" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="86"/>
-      <c r="C140" s="86"/>
+      <c r="B140" s="89"/>
+      <c r="C140" s="89"/>
       <c r="D140" s="10" t="s">
         <v>108</v>
       </c>
@@ -5437,8 +5726,8 @@
       </c>
     </row>
     <row r="141" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="87"/>
-      <c r="C141" s="87"/>
+      <c r="B141" s="90"/>
+      <c r="C141" s="90"/>
       <c r="D141" s="10" t="s">
         <v>110</v>
       </c>
@@ -5447,10 +5736,10 @@
       </c>
     </row>
     <row r="142" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="95" t="s">
+      <c r="B142" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C142" s="96" t="s">
+      <c r="C142" s="99" t="s">
         <v>29</v>
       </c>
       <c r="D142" s="12" t="s">
@@ -5462,8 +5751,8 @@
       <c r="H142" s="11"/>
     </row>
     <row r="143" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="86"/>
-      <c r="C143" s="86"/>
+      <c r="B143" s="89"/>
+      <c r="C143" s="89"/>
       <c r="D143" s="12" t="s">
         <v>31</v>
       </c>
@@ -5472,8 +5761,8 @@
       </c>
     </row>
     <row r="144" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="86"/>
-      <c r="C144" s="86"/>
+      <c r="B144" s="89"/>
+      <c r="C144" s="89"/>
       <c r="D144" s="12" t="s">
         <v>32</v>
       </c>
@@ -5482,8 +5771,8 @@
       </c>
     </row>
     <row r="145" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="86"/>
-      <c r="C145" s="86"/>
+      <c r="B145" s="89"/>
+      <c r="C145" s="89"/>
       <c r="D145" s="12" t="s">
         <v>33</v>
       </c>
@@ -5492,8 +5781,8 @@
       </c>
     </row>
     <row r="146" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="86"/>
-      <c r="C146" s="86"/>
+      <c r="B146" s="89"/>
+      <c r="C146" s="89"/>
       <c r="D146" s="12" t="s">
         <v>35</v>
       </c>
@@ -5502,8 +5791,8 @@
       </c>
     </row>
     <row r="147" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="86"/>
-      <c r="C147" s="86"/>
+      <c r="B147" s="89"/>
+      <c r="C147" s="89"/>
       <c r="D147" s="12" t="s">
         <v>36</v>
       </c>
@@ -5512,8 +5801,8 @@
       </c>
     </row>
     <row r="148" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="86"/>
-      <c r="C148" s="86"/>
+      <c r="B148" s="89"/>
+      <c r="C148" s="89"/>
       <c r="D148" s="12" t="s">
         <v>37</v>
       </c>
@@ -5522,8 +5811,8 @@
       </c>
     </row>
     <row r="149" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="86"/>
-      <c r="C149" s="86"/>
+      <c r="B149" s="89"/>
+      <c r="C149" s="89"/>
       <c r="D149" s="12" t="s">
         <v>38</v>
       </c>
@@ -5532,8 +5821,8 @@
       </c>
     </row>
     <row r="150" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="86"/>
-      <c r="C150" s="86"/>
+      <c r="B150" s="89"/>
+      <c r="C150" s="89"/>
       <c r="D150" s="12" t="s">
         <v>118</v>
       </c>
@@ -5542,8 +5831,8 @@
       </c>
     </row>
     <row r="151" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="86"/>
-      <c r="C151" s="86"/>
+      <c r="B151" s="89"/>
+      <c r="C151" s="89"/>
       <c r="D151" s="12" t="s">
         <v>120</v>
       </c>
@@ -5552,8 +5841,8 @@
       </c>
     </row>
     <row r="152" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="86"/>
-      <c r="C152" s="86"/>
+      <c r="B152" s="89"/>
+      <c r="C152" s="89"/>
       <c r="D152" s="12" t="s">
         <v>122</v>
       </c>
@@ -5562,8 +5851,8 @@
       </c>
     </row>
     <row r="153" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="86"/>
-      <c r="C153" s="86"/>
+      <c r="B153" s="89"/>
+      <c r="C153" s="89"/>
       <c r="D153" s="12" t="s">
         <v>124</v>
       </c>
@@ -5572,8 +5861,8 @@
       </c>
     </row>
     <row r="154" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="86"/>
-      <c r="C154" s="86"/>
+      <c r="B154" s="89"/>
+      <c r="C154" s="89"/>
       <c r="D154" s="12" t="s">
         <v>126</v>
       </c>
@@ -5582,8 +5871,8 @@
       </c>
     </row>
     <row r="155" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="86"/>
-      <c r="C155" s="86"/>
+      <c r="B155" s="89"/>
+      <c r="C155" s="89"/>
       <c r="D155" s="12" t="s">
         <v>128</v>
       </c>
@@ -5592,8 +5881,8 @@
       </c>
     </row>
     <row r="156" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="86"/>
-      <c r="C156" s="86"/>
+      <c r="B156" s="89"/>
+      <c r="C156" s="89"/>
       <c r="D156" s="12" t="s">
         <v>130</v>
       </c>
@@ -5602,8 +5891,8 @@
       </c>
     </row>
     <row r="157" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="86"/>
-      <c r="C157" s="86"/>
+      <c r="B157" s="89"/>
+      <c r="C157" s="89"/>
       <c r="D157" s="12" t="s">
         <v>132</v>
       </c>
@@ -5612,8 +5901,8 @@
       </c>
     </row>
     <row r="158" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="86"/>
-      <c r="C158" s="86"/>
+      <c r="B158" s="89"/>
+      <c r="C158" s="89"/>
       <c r="D158" s="12" t="s">
         <v>134</v>
       </c>
@@ -5622,8 +5911,8 @@
       </c>
     </row>
     <row r="159" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="86"/>
-      <c r="C159" s="86"/>
+      <c r="B159" s="89"/>
+      <c r="C159" s="89"/>
       <c r="D159" s="12" t="s">
         <v>136</v>
       </c>
@@ -5632,8 +5921,8 @@
       </c>
     </row>
     <row r="160" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="86"/>
-      <c r="C160" s="86"/>
+      <c r="B160" s="89"/>
+      <c r="C160" s="89"/>
       <c r="D160" s="12" t="s">
         <v>138</v>
       </c>
@@ -5642,8 +5931,8 @@
       </c>
     </row>
     <row r="161" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="86"/>
-      <c r="C161" s="86"/>
+      <c r="B161" s="89"/>
+      <c r="C161" s="89"/>
       <c r="D161" s="12" t="s">
         <v>140</v>
       </c>
@@ -5652,8 +5941,8 @@
       </c>
     </row>
     <row r="162" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="86"/>
-      <c r="C162" s="86"/>
+      <c r="B162" s="89"/>
+      <c r="C162" s="89"/>
       <c r="D162" s="12" t="s">
         <v>142</v>
       </c>
@@ -5662,8 +5951,8 @@
       </c>
     </row>
     <row r="163" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="86"/>
-      <c r="C163" s="86"/>
+      <c r="B163" s="89"/>
+      <c r="C163" s="89"/>
       <c r="D163" s="12" t="s">
         <v>144</v>
       </c>
@@ -5672,8 +5961,8 @@
       </c>
     </row>
     <row r="164" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="86"/>
-      <c r="C164" s="86"/>
+      <c r="B164" s="89"/>
+      <c r="C164" s="89"/>
       <c r="D164" s="12" t="s">
         <v>146</v>
       </c>
@@ -5682,8 +5971,8 @@
       </c>
     </row>
     <row r="165" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="87"/>
-      <c r="C165" s="87"/>
+      <c r="B165" s="90"/>
+      <c r="C165" s="90"/>
       <c r="D165" s="12" t="s">
         <v>148</v>
       </c>
@@ -5692,10 +5981,10 @@
       </c>
     </row>
     <row r="166" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="97" t="s">
+      <c r="B166" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="C166" s="98" t="s">
+      <c r="C166" s="101" t="s">
         <v>40</v>
       </c>
       <c r="D166" s="13" t="s">
@@ -5706,8 +5995,8 @@
       </c>
     </row>
     <row r="167" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="86"/>
-      <c r="C167" s="86"/>
+      <c r="B167" s="89"/>
+      <c r="C167" s="89"/>
       <c r="D167" s="13" t="s">
         <v>42</v>
       </c>
@@ -5716,8 +6005,8 @@
       </c>
     </row>
     <row r="168" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="86"/>
-      <c r="C168" s="86"/>
+      <c r="B168" s="89"/>
+      <c r="C168" s="89"/>
       <c r="D168" s="13" t="s">
         <v>43</v>
       </c>
@@ -5726,8 +6015,8 @@
       </c>
     </row>
     <row r="169" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="86"/>
-      <c r="C169" s="86"/>
+      <c r="B169" s="89"/>
+      <c r="C169" s="89"/>
       <c r="D169" s="13" t="s">
         <v>44</v>
       </c>
@@ -5736,8 +6025,8 @@
       </c>
     </row>
     <row r="170" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="86"/>
-      <c r="C170" s="86"/>
+      <c r="B170" s="89"/>
+      <c r="C170" s="89"/>
       <c r="D170" s="13" t="s">
         <v>41</v>
       </c>
@@ -5746,8 +6035,8 @@
       </c>
     </row>
     <row r="171" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="86"/>
-      <c r="C171" s="86"/>
+      <c r="B171" s="89"/>
+      <c r="C171" s="89"/>
       <c r="D171" s="13" t="s">
         <v>42</v>
       </c>
@@ -5756,8 +6045,8 @@
       </c>
     </row>
     <row r="172" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="86"/>
-      <c r="C172" s="86"/>
+      <c r="B172" s="89"/>
+      <c r="C172" s="89"/>
       <c r="D172" s="13" t="s">
         <v>43</v>
       </c>
@@ -5766,8 +6055,8 @@
       </c>
     </row>
     <row r="173" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="86"/>
-      <c r="C173" s="86"/>
+      <c r="B173" s="89"/>
+      <c r="C173" s="89"/>
       <c r="D173" s="13" t="s">
         <v>44</v>
       </c>
@@ -5776,8 +6065,8 @@
       </c>
     </row>
     <row r="174" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="86"/>
-      <c r="C174" s="86"/>
+      <c r="B174" s="89"/>
+      <c r="C174" s="89"/>
       <c r="D174" s="13" t="s">
         <v>41</v>
       </c>
@@ -5786,8 +6075,8 @@
       </c>
     </row>
     <row r="175" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="86"/>
-      <c r="C175" s="86"/>
+      <c r="B175" s="89"/>
+      <c r="C175" s="89"/>
       <c r="D175" s="13" t="s">
         <v>42</v>
       </c>
@@ -5796,8 +6085,8 @@
       </c>
     </row>
     <row r="176" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="87"/>
-      <c r="C176" s="87"/>
+      <c r="B176" s="90"/>
+      <c r="C176" s="90"/>
       <c r="D176" s="13" t="s">
         <v>43</v>
       </c>
@@ -5806,10 +6095,10 @@
       </c>
     </row>
     <row r="177" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="89" t="s">
+      <c r="B177" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C177" s="90" t="s">
+      <c r="C177" s="93" t="s">
         <v>46</v>
       </c>
       <c r="D177" s="14" t="s">
@@ -5820,8 +6109,8 @@
       </c>
     </row>
     <row r="178" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="86"/>
-      <c r="C178" s="86"/>
+      <c r="B178" s="89"/>
+      <c r="C178" s="89"/>
       <c r="D178" s="14" t="s">
         <v>162</v>
       </c>
@@ -5830,8 +6119,8 @@
       </c>
     </row>
     <row r="179" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="86"/>
-      <c r="C179" s="86"/>
+      <c r="B179" s="89"/>
+      <c r="C179" s="89"/>
       <c r="D179" s="14" t="s">
         <v>164</v>
       </c>
@@ -5840,8 +6129,8 @@
       </c>
     </row>
     <row r="180" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="86"/>
-      <c r="C180" s="86"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="89"/>
       <c r="D180" s="14" t="s">
         <v>166</v>
       </c>
@@ -5850,8 +6139,8 @@
       </c>
     </row>
     <row r="181" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="86"/>
-      <c r="C181" s="86"/>
+      <c r="B181" s="89"/>
+      <c r="C181" s="89"/>
       <c r="D181" s="14" t="s">
         <v>168</v>
       </c>
@@ -5860,8 +6149,8 @@
       </c>
     </row>
     <row r="182" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="86"/>
-      <c r="C182" s="86"/>
+      <c r="B182" s="89"/>
+      <c r="C182" s="89"/>
       <c r="D182" s="14" t="s">
         <v>170</v>
       </c>
@@ -5870,8 +6159,8 @@
       </c>
     </row>
     <row r="183" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="86"/>
-      <c r="C183" s="86"/>
+      <c r="B183" s="89"/>
+      <c r="C183" s="89"/>
       <c r="D183" s="14" t="s">
         <v>172</v>
       </c>
@@ -5880,8 +6169,8 @@
       </c>
     </row>
     <row r="184" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="86"/>
-      <c r="C184" s="86"/>
+      <c r="B184" s="89"/>
+      <c r="C184" s="89"/>
       <c r="D184" s="14" t="s">
         <v>174</v>
       </c>
@@ -5890,8 +6179,8 @@
       </c>
     </row>
     <row r="185" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="86"/>
-      <c r="C185" s="86"/>
+      <c r="B185" s="89"/>
+      <c r="C185" s="89"/>
       <c r="D185" s="14" t="s">
         <v>175</v>
       </c>
@@ -5900,8 +6189,8 @@
       </c>
     </row>
     <row r="186" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="87"/>
-      <c r="C186" s="87"/>
+      <c r="B186" s="90"/>
+      <c r="C186" s="90"/>
       <c r="D186" s="14" t="s">
         <v>177</v>
       </c>
@@ -5910,10 +6199,10 @@
       </c>
     </row>
     <row r="187" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="91" t="s">
+      <c r="B187" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="C187" s="92" t="s">
+      <c r="C187" s="95" t="s">
         <v>49</v>
       </c>
       <c r="D187" s="15" t="s">
@@ -5924,8 +6213,8 @@
       </c>
     </row>
     <row r="188" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="86"/>
-      <c r="C188" s="86"/>
+      <c r="B188" s="89"/>
+      <c r="C188" s="89"/>
       <c r="D188" s="15" t="s">
         <v>52</v>
       </c>
@@ -5934,8 +6223,8 @@
       </c>
     </row>
     <row r="189" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="86"/>
-      <c r="C189" s="86"/>
+      <c r="B189" s="89"/>
+      <c r="C189" s="89"/>
       <c r="D189" s="15" t="s">
         <v>181</v>
       </c>
@@ -5944,8 +6233,8 @@
       </c>
     </row>
     <row r="190" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="86"/>
-      <c r="C190" s="86"/>
+      <c r="B190" s="89"/>
+      <c r="C190" s="89"/>
       <c r="D190" s="15" t="s">
         <v>182</v>
       </c>
@@ -5954,8 +6243,8 @@
       </c>
     </row>
     <row r="191" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="86"/>
-      <c r="C191" s="86"/>
+      <c r="B191" s="89"/>
+      <c r="C191" s="89"/>
       <c r="D191" s="15" t="s">
         <v>184</v>
       </c>
@@ -5964,8 +6253,8 @@
       </c>
     </row>
     <row r="192" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="86"/>
-      <c r="C192" s="86"/>
+      <c r="B192" s="89"/>
+      <c r="C192" s="89"/>
       <c r="D192" s="15" t="s">
         <v>186</v>
       </c>
@@ -5974,8 +6263,8 @@
       </c>
     </row>
     <row r="193" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="86"/>
-      <c r="C193" s="86"/>
+      <c r="B193" s="89"/>
+      <c r="C193" s="89"/>
       <c r="D193" s="15" t="s">
         <v>188</v>
       </c>
@@ -5984,8 +6273,8 @@
       </c>
     </row>
     <row r="194" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="86"/>
-      <c r="C194" s="86"/>
+      <c r="B194" s="89"/>
+      <c r="C194" s="89"/>
       <c r="D194" s="15" t="s">
         <v>190</v>
       </c>
@@ -5994,8 +6283,8 @@
       </c>
     </row>
     <row r="195" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="86"/>
-      <c r="C195" s="86"/>
+      <c r="B195" s="89"/>
+      <c r="C195" s="89"/>
       <c r="D195" s="15" t="s">
         <v>192</v>
       </c>
@@ -6004,8 +6293,8 @@
       </c>
     </row>
     <row r="196" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="87"/>
-      <c r="C196" s="87"/>
+      <c r="B196" s="90"/>
+      <c r="C196" s="90"/>
       <c r="D196" s="15" t="s">
         <v>194</v>
       </c>
@@ -6890,6 +7179,22 @@
     <row r="1071" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="B142:B165"/>
     <mergeCell ref="B166:B176"/>
     <mergeCell ref="B177:B186"/>
     <mergeCell ref="B25:B29"/>
@@ -6903,24 +7208,366 @@
     <mergeCell ref="B121:B141"/>
     <mergeCell ref="C121:C141"/>
     <mergeCell ref="C142:C165"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="B142:B165"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A859B3F5-C2BC-495E-B10E-073478EAA67E}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="49.85546875" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="124" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="131" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="134" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="125" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="132" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="126"/>
+      <c r="B3" s="132" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="126"/>
+      <c r="B4" s="132" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="135" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="126"/>
+      <c r="B5" s="132" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="136" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="125" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="132" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="136" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="126"/>
+      <c r="B7" s="127" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="135" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="126"/>
+      <c r="B8" s="127" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="136" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="128"/>
+      <c r="B9" s="127" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="135" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="125" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="127" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="137" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="126"/>
+      <c r="B11" s="132" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="136" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="126"/>
+      <c r="B12" s="132" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="138" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="126"/>
+      <c r="B13" s="132" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="136" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="128"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="138"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="129" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="126"/>
+      <c r="B16" s="132" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="138" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="126"/>
+      <c r="B17" s="132" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="128"/>
+      <c r="B18" s="132" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" s="139" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="125" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="138" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="126"/>
+      <c r="B20" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="138" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="126"/>
+      <c r="B21" s="129" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="138" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="126"/>
+      <c r="B22" s="132" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="125" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="138" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="126"/>
+      <c r="B24" s="129" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="138" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="126"/>
+      <c r="B25" s="129" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" s="138" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="130"/>
+      <c r="B26" s="133" t="s">
+        <v>273</v>
+      </c>
+      <c r="C26" s="140" t="s">
+        <v>274</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D82152-12CB-46E2-805E-A91A51956650}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="49.28515625" customWidth="1"/>
+    <col min="3" max="3" width="72.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="141" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="141" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="141" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="142" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="142" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="142" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="142" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="142" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="142" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>